--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -3084,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058287</v>
+        <v>129058311</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,42 +3095,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436718</v>
+        <v>436530</v>
       </c>
       <c r="R26" t="n">
-        <v>6785941</v>
+        <v>6785992</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058311</v>
+        <v>129058287</v>
       </c>
       <c r="B28" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3301,34 +3293,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436530</v>
+        <v>436718</v>
       </c>
       <c r="R28" t="n">
-        <v>6785992</v>
+        <v>6785941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058319</v>
+        <v>129058288</v>
       </c>
       <c r="B31" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,26 +3612,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3639,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436378</v>
+        <v>436458</v>
       </c>
       <c r="R31" t="n">
-        <v>6786219</v>
+        <v>6786194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3688,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3900,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058288</v>
+        <v>129058319</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,31 +3915,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3943,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436458</v>
+        <v>436378</v>
       </c>
       <c r="R34" t="n">
-        <v>6786194</v>
+        <v>6786219</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,6 +3986,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058395</v>
+        <v>129058268</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
         <v>436504</v>
       </c>
       <c r="R48" t="n">
-        <v>6786102</v>
+        <v>6786023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058385</v>
+        <v>129058309</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436327</v>
+        <v>436532</v>
       </c>
       <c r="R49" t="n">
-        <v>6786086</v>
+        <v>6785994</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058268</v>
+        <v>129058395</v>
       </c>
       <c r="B50" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,21 +5489,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,7 +5516,7 @@
         <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6786023</v>
+        <v>6786102</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058386</v>
+        <v>129058385</v>
       </c>
       <c r="B51" t="n">
         <v>79034</v>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436505</v>
+        <v>436327</v>
       </c>
       <c r="R51" t="n">
-        <v>6785856</v>
+        <v>6786086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058290</v>
+        <v>129058386</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,42 +5683,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436601</v>
+        <v>436505</v>
       </c>
       <c r="R52" t="n">
-        <v>6785947</v>
+        <v>6785856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,10 +5769,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058309</v>
+        <v>129058290</v>
       </c>
       <c r="B53" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,34 +5780,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436532</v>
+        <v>436601</v>
       </c>
       <c r="R53" t="n">
-        <v>6785994</v>
+        <v>6785947</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058291</v>
+        <v>129058361</v>
       </c>
       <c r="B61" t="n">
-        <v>57720</v>
+        <v>78791</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,42 +6608,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436214</v>
+        <v>436500</v>
       </c>
       <c r="R61" t="n">
-        <v>6786222</v>
+        <v>6786018</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6702,43 +6694,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058335</v>
+        <v>129058389</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6746,10 +6732,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436360</v>
+        <v>436739</v>
       </c>
       <c r="R62" t="n">
-        <v>6786231</v>
+        <v>6785902</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6782,6 +6768,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6809,54 +6800,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058340</v>
+        <v>129058405</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436324</v>
+        <v>436227</v>
       </c>
       <c r="R63" t="n">
-        <v>6786220</v>
+        <v>6786243</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6897,7 +6879,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6916,54 +6897,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058330</v>
+        <v>129058353</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436823</v>
+        <v>436551</v>
       </c>
       <c r="R64" t="n">
-        <v>6785756</v>
+        <v>6785765</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +6976,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7023,54 +6994,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058323</v>
+        <v>129058271</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436241</v>
+        <v>436493</v>
       </c>
       <c r="R65" t="n">
-        <v>6786159</v>
+        <v>6786189</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7111,7 +7073,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7130,10 +7091,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058361</v>
+        <v>129058291</v>
       </c>
       <c r="B66" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7141,34 +7102,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436500</v>
+        <v>436214</v>
       </c>
       <c r="R66" t="n">
-        <v>6786018</v>
+        <v>6786222</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7227,37 +7196,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058389</v>
+        <v>129058335</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7265,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436739</v>
+        <v>436360</v>
       </c>
       <c r="R67" t="n">
-        <v>6785902</v>
+        <v>6786231</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7301,11 +7276,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7333,45 +7303,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058405</v>
+        <v>129058340</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436227</v>
+        <v>436324</v>
       </c>
       <c r="R68" t="n">
-        <v>6786243</v>
+        <v>6786220</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7412,6 +7391,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7430,45 +7410,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058353</v>
+        <v>129058330</v>
       </c>
       <c r="B69" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436551</v>
+        <v>436823</v>
       </c>
       <c r="R69" t="n">
-        <v>6785765</v>
+        <v>6785756</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,6 +7498,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7527,45 +7517,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058271</v>
+        <v>129058323</v>
       </c>
       <c r="B70" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436493</v>
+        <v>436241</v>
       </c>
       <c r="R70" t="n">
-        <v>6786189</v>
+        <v>6786159</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7606,6 +7605,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9991,54 +9991,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058333</v>
+        <v>129058407</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436432</v>
+        <v>436215</v>
       </c>
       <c r="R95" t="n">
-        <v>6786210</v>
+        <v>6786222</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,7 +10070,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10098,7 +10088,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058407</v>
+        <v>129058416</v>
       </c>
       <c r="B96" t="n">
         <v>79034</v>
@@ -10127,16 +10117,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436215</v>
+        <v>436491</v>
       </c>
       <c r="R96" t="n">
-        <v>6786222</v>
+        <v>6786146</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10171,12 +10164,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10195,37 +10194,43 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058416</v>
+        <v>129058345</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10233,10 +10238,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436491</v>
+        <v>436269</v>
       </c>
       <c r="R97" t="n">
-        <v>6786146</v>
+        <v>6786257</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10269,11 +10274,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10301,54 +10301,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058345</v>
+        <v>129058298</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436269</v>
+        <v>436513</v>
       </c>
       <c r="R98" t="n">
-        <v>6786257</v>
+        <v>6785845</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,7 +10380,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10408,7 +10398,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058298</v>
+        <v>129058300</v>
       </c>
       <c r="B99" t="n">
         <v>78792</v>
@@ -10443,10 +10433,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436513</v>
+        <v>436554</v>
       </c>
       <c r="R99" t="n">
-        <v>6785845</v>
+        <v>6785764</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10505,45 +10495,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058300</v>
+        <v>129058333</v>
       </c>
       <c r="B100" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436554</v>
+        <v>436432</v>
       </c>
       <c r="R100" t="n">
-        <v>6785764</v>
+        <v>6786210</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10584,6 +10583,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11087,7 +11087,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058393</v>
+        <v>129058406</v>
       </c>
       <c r="B106" t="n">
         <v>79034</v>
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436507</v>
+        <v>436222</v>
       </c>
       <c r="R106" t="n">
-        <v>6786023</v>
+        <v>6786238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11184,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058406</v>
+        <v>129058366</v>
       </c>
       <c r="B107" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11195,21 +11195,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11219,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436222</v>
+        <v>436357</v>
       </c>
       <c r="R107" t="n">
-        <v>6786238</v>
+        <v>6786208</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11281,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058366</v>
+        <v>129058393</v>
       </c>
       <c r="B108" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11292,21 +11292,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436357</v>
+        <v>436507</v>
       </c>
       <c r="R108" t="n">
-        <v>6786208</v>
+        <v>6786023</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058368</v>
+        <v>129058289</v>
       </c>
       <c r="B111" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11593,34 +11593,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436257</v>
+        <v>436486</v>
       </c>
       <c r="R111" t="n">
-        <v>6786288</v>
+        <v>6786231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11679,40 +11687,41 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058289</v>
+        <v>129058328</v>
       </c>
       <c r="B112" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11722,10 +11731,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436486</v>
+        <v>436701</v>
       </c>
       <c r="R112" t="n">
-        <v>6786231</v>
+        <v>6785838</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11766,6 +11775,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11784,54 +11794,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058328</v>
+        <v>129058368</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436701</v>
+        <v>436257</v>
       </c>
       <c r="R113" t="n">
-        <v>6785838</v>
+        <v>6786288</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11872,7 +11873,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B125" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R125" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,10 +13070,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B126" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R126" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080282</v>
+        <v>129080297</v>
       </c>
       <c r="B149" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436335</v>
+        <v>436449</v>
       </c>
       <c r="R149" t="n">
-        <v>6786163</v>
+        <v>6786210</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15609,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080297</v>
+        <v>129080282</v>
       </c>
       <c r="B152" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436449</v>
+        <v>436335</v>
       </c>
       <c r="R152" t="n">
-        <v>6786210</v>
+        <v>6786163</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16336,41 +16336,40 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080310</v>
+        <v>129080287</v>
       </c>
       <c r="B159" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16380,10 +16379,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436472</v>
+        <v>436471</v>
       </c>
       <c r="R159" t="n">
-        <v>6786160</v>
+        <v>6786165</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16424,7 +16423,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16443,40 +16441,41 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080287</v>
+        <v>129080310</v>
       </c>
       <c r="B160" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -16486,10 +16485,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436471</v>
+        <v>436472</v>
       </c>
       <c r="R160" t="n">
-        <v>6786165</v>
+        <v>6786160</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16530,6 +16529,7 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058274</v>
+        <v>129058331</v>
       </c>
       <c r="B2" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436522</v>
+        <v>436755</v>
       </c>
       <c r="R2" t="n">
-        <v>6786062</v>
+        <v>6785905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058412</v>
+        <v>129058274</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436564</v>
+        <v>436522</v>
       </c>
       <c r="R3" t="n">
-        <v>6785776</v>
+        <v>6786062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058331</v>
+        <v>129058412</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436755</v>
+        <v>436564</v>
       </c>
       <c r="R4" t="n">
-        <v>6785905</v>
+        <v>6785776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +958,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058304</v>
+        <v>129058384</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436683</v>
+        <v>436265</v>
       </c>
       <c r="R8" t="n">
-        <v>6785939</v>
+        <v>6786123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058321</v>
+        <v>129058350</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436377</v>
+        <v>436465</v>
       </c>
       <c r="R9" t="n">
-        <v>6786201</v>
+        <v>6785855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058384</v>
+        <v>129058415</v>
       </c>
       <c r="B10" t="n">
         <v>79034</v>
@@ -1500,16 +1500,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436265</v>
+        <v>436527</v>
       </c>
       <c r="R10" t="n">
-        <v>6786123</v>
+        <v>6785990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,12 +1547,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,10 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058350</v>
+        <v>129058304</v>
       </c>
       <c r="B11" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1588,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436465</v>
+        <v>436683</v>
       </c>
       <c r="R11" t="n">
-        <v>6785855</v>
+        <v>6785939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,10 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058415</v>
+        <v>129058321</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,37 +1685,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436527</v>
+        <v>436377</v>
       </c>
       <c r="R12" t="n">
-        <v>6785990</v>
+        <v>6786201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,18 +1747,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058301</v>
+        <v>129058286</v>
       </c>
       <c r="B16" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,34 +2103,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436796</v>
+        <v>436617</v>
       </c>
       <c r="R16" t="n">
-        <v>6785778</v>
+        <v>6785749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,37 +2197,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058317</v>
+        <v>129058332</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2227,10 +2241,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436356</v>
+        <v>436648</v>
       </c>
       <c r="R17" t="n">
-        <v>6786224</v>
+        <v>6785874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058307</v>
+        <v>129058382</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,21 +2315,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436597</v>
+        <v>436214</v>
       </c>
       <c r="R18" t="n">
-        <v>6785981</v>
+        <v>6786180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2387,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058308</v>
+        <v>129058403</v>
       </c>
       <c r="B19" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,21 +2412,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2422,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436545</v>
+        <v>436259</v>
       </c>
       <c r="R19" t="n">
-        <v>6785997</v>
+        <v>6786285</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058280</v>
+        <v>129058365</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>78791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2495,21 +2509,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2519,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436519</v>
+        <v>436467</v>
       </c>
       <c r="R20" t="n">
-        <v>6785988</v>
+        <v>6786236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,10 +2595,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058382</v>
+        <v>129058301</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,21 +2606,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2616,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436214</v>
+        <v>436796</v>
       </c>
       <c r="R21" t="n">
-        <v>6786180</v>
+        <v>6785778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,10 +2692,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058403</v>
+        <v>129058317</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2689,34 +2703,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436259</v>
+        <v>436356</v>
       </c>
       <c r="R22" t="n">
-        <v>6786285</v>
+        <v>6786224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,6 +2774,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2775,10 +2793,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058365</v>
+        <v>129058307</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2786,21 +2804,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2810,10 +2828,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436467</v>
+        <v>436597</v>
       </c>
       <c r="R23" t="n">
-        <v>6786236</v>
+        <v>6785981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2872,10 +2890,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058286</v>
+        <v>129058308</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2883,42 +2901,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436617</v>
+        <v>436545</v>
       </c>
       <c r="R24" t="n">
-        <v>6785749</v>
+        <v>6785997</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,54 +2987,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058332</v>
+        <v>129058280</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79624</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436648</v>
+        <v>436519</v>
       </c>
       <c r="R25" t="n">
-        <v>6785874</v>
+        <v>6785988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3065,7 +3066,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058311</v>
+        <v>129058272</v>
       </c>
       <c r="B26" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,34 +3095,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436530</v>
+        <v>436369</v>
       </c>
       <c r="R26" t="n">
-        <v>6785992</v>
+        <v>6786195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3163,6 +3166,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3181,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058272</v>
+        <v>129058287</v>
       </c>
       <c r="B27" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3192,26 +3196,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3219,10 +3228,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436369</v>
+        <v>436718</v>
       </c>
       <c r="R27" t="n">
-        <v>6786195</v>
+        <v>6785941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,7 +3272,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3282,40 +3290,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058287</v>
+        <v>129058343</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3325,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436718</v>
+        <v>436269</v>
       </c>
       <c r="R28" t="n">
-        <v>6785941</v>
+        <v>6786228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3369,6 +3378,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3387,7 +3397,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058343</v>
+        <v>129058327</v>
       </c>
       <c r="B29" t="n">
         <v>8450</v>
@@ -3431,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436269</v>
+        <v>436674</v>
       </c>
       <c r="R29" t="n">
-        <v>6786228</v>
+        <v>6785802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,54 +3504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058327</v>
+        <v>129058311</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436674</v>
+        <v>436530</v>
       </c>
       <c r="R30" t="n">
-        <v>6785802</v>
+        <v>6785992</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3582,7 +3583,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058288</v>
+        <v>129058273</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,31 +3612,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3644,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436458</v>
+        <v>436257</v>
       </c>
       <c r="R31" t="n">
-        <v>6786194</v>
+        <v>6786288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,6 +3683,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3706,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058273</v>
+        <v>129058369</v>
       </c>
       <c r="B32" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,37 +3713,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436257</v>
+        <v>436817</v>
       </c>
       <c r="R32" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,7 +3781,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3807,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058369</v>
+        <v>129058288</v>
       </c>
       <c r="B33" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,34 +3810,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436817</v>
+        <v>436458</v>
       </c>
       <c r="R33" t="n">
-        <v>6785838</v>
+        <v>6786194</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058268</v>
+        <v>129058309</v>
       </c>
       <c r="B48" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436504</v>
+        <v>436532</v>
       </c>
       <c r="R48" t="n">
-        <v>6786023</v>
+        <v>6785994</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058309</v>
+        <v>129058395</v>
       </c>
       <c r="B49" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436532</v>
+        <v>436504</v>
       </c>
       <c r="R49" t="n">
-        <v>6785994</v>
+        <v>6786102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058395</v>
+        <v>129058385</v>
       </c>
       <c r="B50" t="n">
         <v>79034</v>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R50" t="n">
-        <v>6786102</v>
+        <v>6786086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058385</v>
+        <v>129058268</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,21 +5586,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R51" t="n">
-        <v>6786086</v>
+        <v>6786023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058361</v>
+        <v>129058291</v>
       </c>
       <c r="B61" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,34 +6608,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436500</v>
+        <v>436214</v>
       </c>
       <c r="R61" t="n">
-        <v>6786018</v>
+        <v>6786222</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6694,37 +6702,43 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058389</v>
+        <v>129058335</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6732,10 +6746,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436739</v>
+        <v>436360</v>
       </c>
       <c r="R62" t="n">
-        <v>6785902</v>
+        <v>6786231</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6768,11 +6782,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6800,45 +6809,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058405</v>
+        <v>129058340</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436227</v>
+        <v>436324</v>
       </c>
       <c r="R63" t="n">
-        <v>6786243</v>
+        <v>6786220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6879,6 +6897,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6897,45 +6916,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058353</v>
+        <v>129058330</v>
       </c>
       <c r="B64" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436551</v>
+        <v>436823</v>
       </c>
       <c r="R64" t="n">
-        <v>6785765</v>
+        <v>6785756</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6976,6 +7004,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6994,45 +7023,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058271</v>
+        <v>129058323</v>
       </c>
       <c r="B65" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436493</v>
+        <v>436241</v>
       </c>
       <c r="R65" t="n">
-        <v>6786189</v>
+        <v>6786159</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,6 +7111,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7091,10 +7130,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058291</v>
+        <v>129058361</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>78791</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7102,42 +7141,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436214</v>
+        <v>436500</v>
       </c>
       <c r="R66" t="n">
-        <v>6786222</v>
+        <v>6786018</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7196,43 +7227,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058335</v>
+        <v>129058389</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7240,10 +7265,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436360</v>
+        <v>436739</v>
       </c>
       <c r="R67" t="n">
-        <v>6786231</v>
+        <v>6785902</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7276,6 +7301,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7303,54 +7333,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058340</v>
+        <v>129058405</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436324</v>
+        <v>436227</v>
       </c>
       <c r="R68" t="n">
-        <v>6786220</v>
+        <v>6786243</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7391,7 +7412,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7410,54 +7430,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058330</v>
+        <v>129058353</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436823</v>
+        <v>436551</v>
       </c>
       <c r="R69" t="n">
-        <v>6785756</v>
+        <v>6785765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7509,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7517,54 +7527,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058323</v>
+        <v>129058271</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436241</v>
+        <v>436493</v>
       </c>
       <c r="R70" t="n">
-        <v>6786159</v>
+        <v>6786189</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7605,7 +7606,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7624,45 +7624,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058267</v>
+        <v>129058334</v>
       </c>
       <c r="B71" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436524</v>
+        <v>436373</v>
       </c>
       <c r="R71" t="n">
-        <v>6785977</v>
+        <v>6786190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7703,6 +7712,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7721,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058362</v>
+        <v>129058267</v>
       </c>
       <c r="B72" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7732,21 +7742,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7756,10 +7766,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436494</v>
+        <v>436524</v>
       </c>
       <c r="R72" t="n">
-        <v>6786028</v>
+        <v>6785977</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7818,10 +7828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058264</v>
+        <v>129058362</v>
       </c>
       <c r="B73" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7829,21 +7839,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7853,10 +7863,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436599</v>
+        <v>436494</v>
       </c>
       <c r="R73" t="n">
-        <v>6785738</v>
+        <v>6786028</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7915,10 +7925,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058354</v>
+        <v>129058264</v>
       </c>
       <c r="B74" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7926,21 +7936,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7950,10 +7960,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436796</v>
+        <v>436599</v>
       </c>
       <c r="R74" t="n">
-        <v>6785778</v>
+        <v>6785738</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8012,7 +8022,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058359</v>
+        <v>129058354</v>
       </c>
       <c r="B75" t="n">
         <v>78791</v>
@@ -8047,10 +8057,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436532</v>
+        <v>436796</v>
       </c>
       <c r="R75" t="n">
-        <v>6785994</v>
+        <v>6785778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8109,7 +8119,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058367</v>
+        <v>129058359</v>
       </c>
       <c r="B76" t="n">
         <v>78791</v>
@@ -8144,10 +8154,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436371</v>
+        <v>436532</v>
       </c>
       <c r="R76" t="n">
-        <v>6786199</v>
+        <v>6785994</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,54 +8216,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058334</v>
+        <v>129058367</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436373</v>
+        <v>436371</v>
       </c>
       <c r="R77" t="n">
-        <v>6786190</v>
+        <v>6786199</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,7 +8295,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058315</v>
+        <v>129058355</v>
       </c>
       <c r="B79" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,34 +8425,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436445</v>
+        <v>436825</v>
       </c>
       <c r="R79" t="n">
-        <v>6786210</v>
+        <v>6785764</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8493,6 +8496,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8511,10 +8515,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058355</v>
+        <v>129058394</v>
       </c>
       <c r="B80" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,37 +8526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436825</v>
+        <v>436493</v>
       </c>
       <c r="R80" t="n">
-        <v>6785764</v>
+        <v>6786075</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,7 +8594,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058394</v>
+        <v>129058356</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,21 +8623,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436493</v>
+        <v>436818</v>
       </c>
       <c r="R81" t="n">
-        <v>6786075</v>
+        <v>6785831</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058356</v>
+        <v>129058282</v>
       </c>
       <c r="B82" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,34 +8720,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436818</v>
+        <v>436515</v>
       </c>
       <c r="R82" t="n">
-        <v>6785831</v>
+        <v>6786055</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8806,10 +8814,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058282</v>
+        <v>129058315</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,42 +8825,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436515</v>
+        <v>436445</v>
       </c>
       <c r="R83" t="n">
-        <v>6786055</v>
+        <v>6786210</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058314</v>
+        <v>129058346</v>
       </c>
       <c r="B90" t="n">
-        <v>78792</v>
+        <v>58093</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436510</v>
+        <v>436503</v>
       </c>
       <c r="R90" t="n">
-        <v>6786074</v>
+        <v>6786136</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058346</v>
+        <v>129058314</v>
       </c>
       <c r="B94" t="n">
-        <v>58093</v>
+        <v>78792</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436503</v>
+        <v>436510</v>
       </c>
       <c r="R94" t="n">
-        <v>6786136</v>
+        <v>6786074</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058345</v>
+        <v>129058333</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10228,7 +10228,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10238,10 +10238,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436269</v>
+        <v>436432</v>
       </c>
       <c r="R97" t="n">
-        <v>6786257</v>
+        <v>6786210</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10301,45 +10301,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058298</v>
+        <v>129058345</v>
       </c>
       <c r="B98" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436513</v>
+        <v>436269</v>
       </c>
       <c r="R98" t="n">
-        <v>6785845</v>
+        <v>6786257</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10380,6 +10389,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10398,7 +10408,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058300</v>
+        <v>129058298</v>
       </c>
       <c r="B99" t="n">
         <v>78792</v>
@@ -10433,10 +10443,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436554</v>
+        <v>436513</v>
       </c>
       <c r="R99" t="n">
-        <v>6785764</v>
+        <v>6785845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10495,54 +10505,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058333</v>
+        <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436432</v>
+        <v>436554</v>
       </c>
       <c r="R100" t="n">
-        <v>6786210</v>
+        <v>6785764</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10583,7 +10584,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11087,45 +11087,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058406</v>
+        <v>129058324</v>
       </c>
       <c r="B106" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436222</v>
+        <v>436254</v>
       </c>
       <c r="R106" t="n">
-        <v>6786238</v>
+        <v>6786130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11166,6 +11175,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11184,10 +11194,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058366</v>
+        <v>129058406</v>
       </c>
       <c r="B107" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11195,21 +11205,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11219,10 +11229,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436357</v>
+        <v>436222</v>
       </c>
       <c r="R107" t="n">
-        <v>6786208</v>
+        <v>6786238</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11281,10 +11291,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058393</v>
+        <v>129058366</v>
       </c>
       <c r="B108" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11292,21 +11302,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11316,10 +11326,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436507</v>
+        <v>436357</v>
       </c>
       <c r="R108" t="n">
-        <v>6786023</v>
+        <v>6786208</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11378,10 +11388,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058358</v>
+        <v>129058393</v>
       </c>
       <c r="B109" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11389,21 +11399,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11413,10 +11423,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436550</v>
+        <v>436507</v>
       </c>
       <c r="R109" t="n">
-        <v>6785988</v>
+        <v>6786023</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11475,54 +11485,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129058324</v>
+        <v>129058358</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436254</v>
+        <v>436550</v>
       </c>
       <c r="R110" t="n">
-        <v>6786130</v>
+        <v>6785988</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11563,7 +11564,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11687,54 +11687,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058328</v>
+        <v>129058368</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436701</v>
+        <v>436257</v>
       </c>
       <c r="R112" t="n">
-        <v>6785838</v>
+        <v>6786288</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11775,7 +11766,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11794,45 +11784,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058368</v>
+        <v>129058328</v>
       </c>
       <c r="B113" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436257</v>
+        <v>436701</v>
       </c>
       <c r="R113" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11873,6 +11872,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080295</v>
+        <v>129080277</v>
       </c>
       <c r="B120" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436815</v>
+        <v>436561</v>
       </c>
       <c r="R120" t="n">
-        <v>6785768</v>
+        <v>6785959</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12584,7 +12584,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080291</v>
+        <v>129080295</v>
       </c>
       <c r="B121" t="n">
         <v>78792</v>
@@ -12619,10 +12619,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436524</v>
+        <v>436815</v>
       </c>
       <c r="R121" t="n">
-        <v>6785865</v>
+        <v>6785768</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12681,7 +12681,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129080294</v>
+        <v>129080291</v>
       </c>
       <c r="B122" t="n">
         <v>78792</v>
@@ -12716,10 +12716,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436659</v>
+        <v>436524</v>
       </c>
       <c r="R122" t="n">
-        <v>6785808</v>
+        <v>6785865</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12778,10 +12778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080302</v>
+        <v>129080294</v>
       </c>
       <c r="B123" t="n">
-        <v>91540</v>
+        <v>78792</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12789,21 +12789,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12813,10 +12813,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436320</v>
+        <v>436659</v>
       </c>
       <c r="R123" t="n">
-        <v>6786132</v>
+        <v>6785808</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12857,7 +12857,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12876,10 +12875,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080277</v>
+        <v>129080302</v>
       </c>
       <c r="B124" t="n">
-        <v>79653</v>
+        <v>91543</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,21 +12886,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12911,10 +12910,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436561</v>
+        <v>436320</v>
       </c>
       <c r="R124" t="n">
-        <v>6785959</v>
+        <v>6786132</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12955,6 +12954,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13167,10 +13167,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129080281</v>
+        <v>129080298</v>
       </c>
       <c r="B127" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436448</v>
+        <v>436428</v>
       </c>
       <c r="R127" t="n">
-        <v>6786211</v>
+        <v>6786194</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B128" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R128" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080298</v>
+        <v>129080281</v>
       </c>
       <c r="B129" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13372,21 +13372,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436428</v>
+        <v>436448</v>
       </c>
       <c r="R129" t="n">
-        <v>6786194</v>
+        <v>6786211</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B130" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R130" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B131" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R131" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B132" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R132" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129080279</v>
+        <v>129080301</v>
       </c>
       <c r="B134" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436471</v>
+        <v>436246</v>
       </c>
       <c r="R134" t="n">
-        <v>6786142</v>
+        <v>6786298</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129080301</v>
+        <v>129080279</v>
       </c>
       <c r="B135" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436246</v>
+        <v>436471</v>
       </c>
       <c r="R135" t="n">
-        <v>6786298</v>
+        <v>6786142</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14043,7 +14043,7 @@
         <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080297</v>
+        <v>129080331</v>
       </c>
       <c r="B149" t="n">
-        <v>78792</v>
+        <v>88923</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436449</v>
+        <v>436491</v>
       </c>
       <c r="R149" t="n">
-        <v>6786210</v>
+        <v>6786094</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15390,6 +15390,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15408,10 +15409,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080331</v>
+        <v>129080283</v>
       </c>
       <c r="B150" t="n">
-        <v>88920</v>
+        <v>91523</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15419,21 +15420,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15443,10 +15444,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436491</v>
+        <v>436434</v>
       </c>
       <c r="R150" t="n">
-        <v>6786094</v>
+        <v>6786112</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15479,6 +15480,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15506,10 +15512,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080283</v>
+        <v>129080282</v>
       </c>
       <c r="B151" t="n">
-        <v>91520</v>
+        <v>79653</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15517,21 +15523,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15541,10 +15547,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436434</v>
+        <v>436335</v>
       </c>
       <c r="R151" t="n">
-        <v>6786112</v>
+        <v>6786163</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15579,18 +15585,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15609,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080282</v>
+        <v>129080297</v>
       </c>
       <c r="B152" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436335</v>
+        <v>436449</v>
       </c>
       <c r="R152" t="n">
-        <v>6786163</v>
+        <v>6786210</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058331</v>
+        <v>129058274</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436755</v>
+        <v>436522</v>
       </c>
       <c r="R2" t="n">
-        <v>6785905</v>
+        <v>6786062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058274</v>
+        <v>129058412</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436522</v>
+        <v>436564</v>
       </c>
       <c r="R3" t="n">
-        <v>6786062</v>
+        <v>6785776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058412</v>
+        <v>129058331</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436564</v>
+        <v>436755</v>
       </c>
       <c r="R4" t="n">
-        <v>6785776</v>
+        <v>6785905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,6 +957,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>129058299</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129058303</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,45 +1277,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058384</v>
+        <v>129058336</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436265</v>
+        <v>436336</v>
       </c>
       <c r="R8" t="n">
-        <v>6786123</v>
+        <v>6786183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,6 +1365,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,45 +1384,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058350</v>
+        <v>129058329</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436465</v>
+        <v>436754</v>
       </c>
       <c r="R9" t="n">
-        <v>6785855</v>
+        <v>6785822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,37 +1491,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058415</v>
+        <v>129058337</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1509,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436527</v>
+        <v>436322</v>
       </c>
       <c r="R10" t="n">
-        <v>6785990</v>
+        <v>6786198</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1545,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058304</v>
+        <v>129058384</v>
       </c>
       <c r="B11" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1612,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436683</v>
+        <v>436265</v>
       </c>
       <c r="R11" t="n">
-        <v>6785939</v>
+        <v>6786123</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058321</v>
+        <v>129058350</v>
       </c>
       <c r="B12" t="n">
         <v>78792</v>
@@ -1685,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436377</v>
+        <v>436465</v>
       </c>
       <c r="R12" t="n">
-        <v>6786201</v>
+        <v>6785855</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,43 +1792,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058336</v>
+        <v>129058415</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1815,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436336</v>
+        <v>436527</v>
       </c>
       <c r="R13" t="n">
-        <v>6786183</v>
+        <v>6785990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1878,54 +1898,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058329</v>
+        <v>129058304</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436754</v>
+        <v>436683</v>
       </c>
       <c r="R14" t="n">
-        <v>6785822</v>
+        <v>6785939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1977,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1985,54 +1995,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129058337</v>
+        <v>129058321</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436322</v>
+        <v>436377</v>
       </c>
       <c r="R15" t="n">
-        <v>6786198</v>
+        <v>6786201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,7 +2074,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>129058382</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>129058403</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129058365</v>
       </c>
       <c r="B20" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058301</v>
+        <v>129058308</v>
       </c>
       <c r="B21" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436796</v>
+        <v>436545</v>
       </c>
       <c r="R21" t="n">
-        <v>6785778</v>
+        <v>6785997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,10 +2692,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058317</v>
+        <v>129058301</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,19 +2721,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436356</v>
+        <v>436796</v>
       </c>
       <c r="R22" t="n">
-        <v>6786224</v>
+        <v>6785778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,7 +2771,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2793,10 +2789,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058307</v>
+        <v>129058317</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,16 +2818,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436597</v>
+        <v>436356</v>
       </c>
       <c r="R23" t="n">
-        <v>6785981</v>
+        <v>6786224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2872,6 +2871,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058308</v>
+        <v>129058307</v>
       </c>
       <c r="B24" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436545</v>
+        <v>436597</v>
       </c>
       <c r="R24" t="n">
-        <v>6785997</v>
+        <v>6785981</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
         <v>129058280</v>
       </c>
       <c r="B25" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058272</v>
+        <v>129058287</v>
       </c>
       <c r="B26" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,26 +3095,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3122,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436369</v>
+        <v>436718</v>
       </c>
       <c r="R26" t="n">
-        <v>6786195</v>
+        <v>6785941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3166,7 +3171,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3185,40 +3189,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058287</v>
+        <v>129058343</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3228,10 +3233,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436718</v>
+        <v>436269</v>
       </c>
       <c r="R27" t="n">
-        <v>6785941</v>
+        <v>6786228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,6 +3277,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3290,7 +3296,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058343</v>
+        <v>129058327</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3334,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436269</v>
+        <v>436674</v>
       </c>
       <c r="R28" t="n">
-        <v>6786228</v>
+        <v>6785802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,54 +3403,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058327</v>
+        <v>129058311</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436674</v>
+        <v>436530</v>
       </c>
       <c r="R29" t="n">
-        <v>6785802</v>
+        <v>6785992</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,7 +3482,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3504,10 +3500,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058311</v>
+        <v>129058272</v>
       </c>
       <c r="B30" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3515,34 +3511,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436530</v>
+        <v>436369</v>
       </c>
       <c r="R30" t="n">
-        <v>6785992</v>
+        <v>6786195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3583,6 +3582,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058273</v>
+        <v>129058288</v>
       </c>
       <c r="B31" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,26 +3612,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3639,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436257</v>
+        <v>436458</v>
       </c>
       <c r="R31" t="n">
-        <v>6786288</v>
+        <v>6786194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3688,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3702,10 +3706,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058369</v>
+        <v>129058319</v>
       </c>
       <c r="B32" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,34 +3717,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436817</v>
+        <v>436378</v>
       </c>
       <c r="R32" t="n">
-        <v>6785838</v>
+        <v>6786219</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3781,6 +3788,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3799,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058288</v>
+        <v>129058273</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3810,31 +3818,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3842,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436458</v>
+        <v>436257</v>
       </c>
       <c r="R33" t="n">
-        <v>6786194</v>
+        <v>6786288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,6 +3889,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3904,7 +3908,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058319</v>
+        <v>129058369</v>
       </c>
       <c r="B34" t="n">
         <v>78792</v>
@@ -3915,37 +3919,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436378</v>
+        <v>436817</v>
       </c>
       <c r="R34" t="n">
-        <v>6786219</v>
+        <v>6785838</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,7 +3987,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4005,10 +4005,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058262</v>
+        <v>129058278</v>
       </c>
       <c r="B35" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436534</v>
+        <v>436295</v>
       </c>
       <c r="R35" t="n">
-        <v>6785834</v>
+        <v>6786172</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4102,45 +4102,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058269</v>
+        <v>129058325</v>
       </c>
       <c r="B36" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436483</v>
+        <v>436443</v>
       </c>
       <c r="R36" t="n">
-        <v>6786017</v>
+        <v>6785940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4181,6 +4190,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4209,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058277</v>
+        <v>129058318</v>
       </c>
       <c r="B37" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4220,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4237,10 +4247,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436351</v>
+        <v>436354</v>
       </c>
       <c r="R37" t="n">
-        <v>6786185</v>
+        <v>6786212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4300,10 +4310,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058404</v>
+        <v>129058262</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4311,21 +4321,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4345,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436229</v>
+        <v>436534</v>
       </c>
       <c r="R38" t="n">
-        <v>6786238</v>
+        <v>6785834</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,10 +4407,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058348</v>
+        <v>129058269</v>
       </c>
       <c r="B39" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4408,21 +4418,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4432,10 +4442,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436266</v>
+        <v>436483</v>
       </c>
       <c r="R39" t="n">
-        <v>6786145</v>
+        <v>6786017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4494,10 +4504,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058357</v>
+        <v>129058277</v>
       </c>
       <c r="B40" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,34 +4515,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436686</v>
+        <v>436351</v>
       </c>
       <c r="R40" t="n">
-        <v>6785940</v>
+        <v>6786185</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4573,6 +4586,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4605,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058278</v>
+        <v>129058404</v>
       </c>
       <c r="B41" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4616,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4640,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436295</v>
+        <v>436229</v>
       </c>
       <c r="R41" t="n">
-        <v>6786172</v>
+        <v>6786238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4688,54 +4702,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058325</v>
+        <v>129058348</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436443</v>
+        <v>436266</v>
       </c>
       <c r="R42" t="n">
-        <v>6785940</v>
+        <v>6786145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4776,7 +4781,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4795,7 +4799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058318</v>
+        <v>129058357</v>
       </c>
       <c r="B43" t="n">
         <v>78792</v>
@@ -4806,37 +4810,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436354</v>
+        <v>436686</v>
       </c>
       <c r="R43" t="n">
-        <v>6786212</v>
+        <v>6785940</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4877,7 +4878,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>129058276</v>
       </c>
       <c r="B44" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>129058351</v>
       </c>
       <c r="B45" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>129058297</v>
       </c>
       <c r="B46" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>129058313</v>
       </c>
       <c r="B47" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058309</v>
+        <v>129058385</v>
       </c>
       <c r="B48" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436532</v>
+        <v>436327</v>
       </c>
       <c r="R48" t="n">
-        <v>6785994</v>
+        <v>6786086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058395</v>
+        <v>129058268</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,7 +5419,7 @@
         <v>436504</v>
       </c>
       <c r="R49" t="n">
-        <v>6786102</v>
+        <v>6786023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058385</v>
+        <v>129058386</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436327</v>
+        <v>436505</v>
       </c>
       <c r="R50" t="n">
-        <v>6786086</v>
+        <v>6785856</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058268</v>
+        <v>129058290</v>
       </c>
       <c r="B51" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,34 +5586,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436504</v>
+        <v>436601</v>
       </c>
       <c r="R51" t="n">
-        <v>6786023</v>
+        <v>6785947</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058386</v>
+        <v>129058309</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,21 +5691,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5707,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436505</v>
+        <v>436532</v>
       </c>
       <c r="R52" t="n">
-        <v>6785856</v>
+        <v>6785994</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5769,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058290</v>
+        <v>129058395</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5780,42 +5788,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436601</v>
+        <v>436504</v>
       </c>
       <c r="R53" t="n">
-        <v>6785947</v>
+        <v>6786102</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129058402</v>
+        <v>129058279</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5885,21 +5885,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436264</v>
+        <v>436594</v>
       </c>
       <c r="R54" t="n">
-        <v>6786282</v>
+        <v>6785915</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5948,11 +5948,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5980,10 +5975,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058396</v>
+        <v>129058306</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5991,34 +5986,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436491</v>
+        <v>436598</v>
       </c>
       <c r="R55" t="n">
-        <v>6786189</v>
+        <v>6785911</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6059,6 +6057,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6077,10 +6076,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129058392</v>
+        <v>129058402</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6115,10 +6114,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436508</v>
+        <v>436264</v>
       </c>
       <c r="R56" t="n">
-        <v>6786026</v>
+        <v>6786282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6155,7 +6154,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6183,10 +6182,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129058391</v>
+        <v>129058396</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6212,19 +6211,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436591</v>
+        <v>436491</v>
       </c>
       <c r="R57" t="n">
-        <v>6785966</v>
+        <v>6786189</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6259,18 +6255,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6289,10 +6279,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129058399</v>
+        <v>129058392</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6327,10 +6317,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436303</v>
+        <v>436508</v>
       </c>
       <c r="R58" t="n">
-        <v>6786193</v>
+        <v>6786026</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6367,7 +6357,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt med Garnlav inom en radie av 40 m</t>
+          <t>Garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6395,10 +6385,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129058279</v>
+        <v>129058391</v>
       </c>
       <c r="B59" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,21 +6396,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6433,10 +6423,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436594</v>
+        <v>436591</v>
       </c>
       <c r="R59" t="n">
-        <v>6785915</v>
+        <v>6785966</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6469,6 +6459,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6496,10 +6491,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129058306</v>
+        <v>129058399</v>
       </c>
       <c r="B60" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6507,21 +6502,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6529,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436598</v>
+        <v>436303</v>
       </c>
       <c r="R60" t="n">
-        <v>6785911</v>
+        <v>6786193</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6570,6 +6565,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7133,7 +7133,7 @@
         <v>129058361</v>
       </c>
       <c r="B66" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>129058389</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>129058405</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>129058353</v>
       </c>
       <c r="B69" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>129058271</v>
       </c>
       <c r="B70" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>129058267</v>
       </c>
       <c r="B72" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>129058362</v>
       </c>
       <c r="B73" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>129058264</v>
       </c>
       <c r="B74" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>129058354</v>
       </c>
       <c r="B75" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>129058359</v>
       </c>
       <c r="B76" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>129058367</v>
       </c>
       <c r="B77" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>129058305</v>
       </c>
       <c r="B78" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>129058355</v>
       </c>
       <c r="B79" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>129058394</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>129058356</v>
       </c>
       <c r="B81" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>129058315</v>
       </c>
       <c r="B83" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>129058352</v>
       </c>
       <c r="B84" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>129058263</v>
       </c>
       <c r="B85" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>129058414</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>129058397</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>129058383</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>129058302</v>
       </c>
       <c r="B89" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058346</v>
+        <v>129058411</v>
       </c>
       <c r="B90" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436503</v>
+        <v>436461</v>
       </c>
       <c r="R90" t="n">
-        <v>6786136</v>
+        <v>6785881</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058411</v>
+        <v>129058398</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436461</v>
+        <v>436425</v>
       </c>
       <c r="R91" t="n">
-        <v>6785881</v>
+        <v>6786210</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058398</v>
+        <v>129058387</v>
       </c>
       <c r="B92" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436425</v>
+        <v>436805</v>
       </c>
       <c r="R92" t="n">
-        <v>6786210</v>
+        <v>6785785</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058387</v>
+        <v>129058346</v>
       </c>
       <c r="B93" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436805</v>
+        <v>436503</v>
       </c>
       <c r="R93" t="n">
-        <v>6785785</v>
+        <v>6786136</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9897,7 +9897,7 @@
         <v>129058314</v>
       </c>
       <c r="B94" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9991,45 +9991,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058407</v>
+        <v>129058345</v>
       </c>
       <c r="B95" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436215</v>
+        <v>436269</v>
       </c>
       <c r="R95" t="n">
-        <v>6786222</v>
+        <v>6786257</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,6 +10079,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10088,37 +10098,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058416</v>
+        <v>129058333</v>
       </c>
       <c r="B96" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10126,10 +10142,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436491</v>
+        <v>436432</v>
       </c>
       <c r="R96" t="n">
-        <v>6786146</v>
+        <v>6786210</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10162,11 +10178,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10194,54 +10205,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058333</v>
+        <v>129058407</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436432</v>
+        <v>436215</v>
       </c>
       <c r="R97" t="n">
-        <v>6786210</v>
+        <v>6786222</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10282,7 +10284,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10301,43 +10302,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058345</v>
+        <v>129058416</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10345,10 +10340,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436269</v>
+        <v>436491</v>
       </c>
       <c r="R98" t="n">
-        <v>6786257</v>
+        <v>6786146</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10381,6 +10376,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10408,10 +10408,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058298</v>
+        <v>129058300</v>
       </c>
       <c r="B99" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436513</v>
+        <v>436554</v>
       </c>
       <c r="R99" t="n">
-        <v>6785845</v>
+        <v>6785764</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058300</v>
+        <v>129058298</v>
       </c>
       <c r="B100" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436554</v>
+        <v>436513</v>
       </c>
       <c r="R100" t="n">
-        <v>6785764</v>
+        <v>6785845</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10605,7 +10605,7 @@
         <v>129058417</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129058364</v>
+        <v>129058401</v>
       </c>
       <c r="B102" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436425</v>
+        <v>436310</v>
       </c>
       <c r="R102" t="n">
-        <v>6786192</v>
+        <v>6786196</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058401</v>
+        <v>129058390</v>
       </c>
       <c r="B103" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436310</v>
+        <v>436700</v>
       </c>
       <c r="R103" t="n">
-        <v>6786196</v>
+        <v>6785944</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058390</v>
+        <v>129058266</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10904,21 +10904,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436700</v>
+        <v>436532</v>
       </c>
       <c r="R104" t="n">
-        <v>6785944</v>
+        <v>6785994</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10990,10 +10990,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129058266</v>
+        <v>129058364</v>
       </c>
       <c r="B105" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11001,21 +11001,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436532</v>
+        <v>436425</v>
       </c>
       <c r="R105" t="n">
-        <v>6785994</v>
+        <v>6786192</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11087,54 +11087,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058324</v>
+        <v>129058406</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436254</v>
+        <v>436222</v>
       </c>
       <c r="R106" t="n">
-        <v>6786130</v>
+        <v>6786238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11175,7 +11166,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11194,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058406</v>
+        <v>129058366</v>
       </c>
       <c r="B107" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11205,21 +11195,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11229,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436222</v>
+        <v>436357</v>
       </c>
       <c r="R107" t="n">
-        <v>6786238</v>
+        <v>6786208</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11291,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058366</v>
+        <v>129058393</v>
       </c>
       <c r="B108" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11302,21 +11292,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11326,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436357</v>
+        <v>436507</v>
       </c>
       <c r="R108" t="n">
-        <v>6786208</v>
+        <v>6786023</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11388,10 +11378,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058393</v>
+        <v>129058358</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11399,21 +11389,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11423,10 +11413,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436507</v>
+        <v>436550</v>
       </c>
       <c r="R109" t="n">
-        <v>6786023</v>
+        <v>6785988</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11485,45 +11475,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129058358</v>
+        <v>129058324</v>
       </c>
       <c r="B110" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436550</v>
+        <v>436254</v>
       </c>
       <c r="R110" t="n">
-        <v>6785988</v>
+        <v>6786130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11564,6 +11563,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11582,40 +11582,41 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058289</v>
+        <v>129058328</v>
       </c>
       <c r="B111" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11625,10 +11626,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436486</v>
+        <v>436701</v>
       </c>
       <c r="R111" t="n">
-        <v>6786231</v>
+        <v>6785838</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11669,6 +11670,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11690,7 +11692,7 @@
         <v>129058368</v>
       </c>
       <c r="B112" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11784,41 +11786,40 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058328</v>
+        <v>129058289</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -11828,10 +11829,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436701</v>
+        <v>436486</v>
       </c>
       <c r="R113" t="n">
-        <v>6785838</v>
+        <v>6786231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11872,7 +11873,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>129058270</v>
       </c>
       <c r="B114" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>129058388</v>
       </c>
       <c r="B115" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>129080278</v>
       </c>
       <c r="B116" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>129080329</v>
       </c>
       <c r="B117" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>129080323</v>
       </c>
       <c r="B118" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>129080292</v>
       </c>
       <c r="B119" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080277</v>
+        <v>129080302</v>
       </c>
       <c r="B120" t="n">
-        <v>79653</v>
+        <v>91546</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436561</v>
+        <v>436320</v>
       </c>
       <c r="R120" t="n">
-        <v>6785959</v>
+        <v>6786132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,6 +12566,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12584,10 +12585,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080295</v>
+        <v>129080277</v>
       </c>
       <c r="B121" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,21 +12596,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12619,10 +12620,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436815</v>
+        <v>436561</v>
       </c>
       <c r="R121" t="n">
-        <v>6785768</v>
+        <v>6785959</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12681,10 +12682,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129080291</v>
+        <v>129080295</v>
       </c>
       <c r="B122" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12716,10 +12717,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436524</v>
+        <v>436815</v>
       </c>
       <c r="R122" t="n">
-        <v>6785865</v>
+        <v>6785768</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12781,7 +12782,7 @@
         <v>129080294</v>
       </c>
       <c r="B123" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12875,10 +12876,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080302</v>
+        <v>129080291</v>
       </c>
       <c r="B124" t="n">
-        <v>91543</v>
+        <v>78793</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12886,21 +12887,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12910,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436320</v>
+        <v>436524</v>
       </c>
       <c r="R124" t="n">
-        <v>6786132</v>
+        <v>6785865</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12954,7 +12955,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B125" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R125" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,7 +13070,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B126" t="n">
         <v>78792</v>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R126" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13170,7 +13170,7 @@
         <v>129080298</v>
       </c>
       <c r="B127" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>129080290</v>
       </c>
       <c r="B128" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>129080281</v>
       </c>
       <c r="B129" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>129080328</v>
       </c>
       <c r="B130" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>129080296</v>
       </c>
       <c r="B131" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>129080313</v>
       </c>
       <c r="B132" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>129080318</v>
       </c>
       <c r="B133" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129080301</v>
+        <v>129080279</v>
       </c>
       <c r="B134" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436246</v>
+        <v>436471</v>
       </c>
       <c r="R134" t="n">
-        <v>6786298</v>
+        <v>6786142</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129080279</v>
+        <v>129080301</v>
       </c>
       <c r="B135" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436471</v>
+        <v>436246</v>
       </c>
       <c r="R135" t="n">
-        <v>6786142</v>
+        <v>6786298</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14043,7 +14043,7 @@
         <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>129080317</v>
       </c>
       <c r="B137" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>129080316</v>
       </c>
       <c r="B138" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>129080314</v>
       </c>
       <c r="B139" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129080293</v>
       </c>
       <c r="B140" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>129080319</v>
       </c>
       <c r="B141" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>129080324</v>
       </c>
       <c r="B142" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>129080327</v>
       </c>
       <c r="B143" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14816,54 +14816,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080312</v>
+        <v>129080299</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436296</v>
+        <v>436384</v>
       </c>
       <c r="R144" t="n">
-        <v>6786185</v>
+        <v>6786203</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14904,7 +14895,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -14926,7 +14916,7 @@
         <v>129080300</v>
       </c>
       <c r="B145" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15020,45 +15010,54 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080299</v>
+        <v>129080312</v>
       </c>
       <c r="B146" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436384</v>
+        <v>436296</v>
       </c>
       <c r="R146" t="n">
-        <v>6786203</v>
+        <v>6786185</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15099,6 +15098,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15117,10 +15117,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129080315</v>
+        <v>129080280</v>
       </c>
       <c r="B147" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15128,21 +15128,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15152,10 +15152,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>436523</v>
+        <v>436461</v>
       </c>
       <c r="R147" t="n">
-        <v>6785864</v>
+        <v>6786160</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15214,10 +15214,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129080280</v>
+        <v>129080315</v>
       </c>
       <c r="B148" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15225,21 +15225,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>436461</v>
+        <v>436523</v>
       </c>
       <c r="R148" t="n">
-        <v>6786160</v>
+        <v>6785864</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080331</v>
+        <v>129080283</v>
       </c>
       <c r="B149" t="n">
-        <v>88923</v>
+        <v>91526</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436491</v>
+        <v>436434</v>
       </c>
       <c r="R149" t="n">
-        <v>6786094</v>
+        <v>6786112</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15382,6 +15382,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15409,10 +15414,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080283</v>
+        <v>129080282</v>
       </c>
       <c r="B150" t="n">
-        <v>91523</v>
+        <v>79654</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15420,21 +15425,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15444,10 +15449,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436434</v>
+        <v>436335</v>
       </c>
       <c r="R150" t="n">
-        <v>6786112</v>
+        <v>6786163</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15482,18 +15487,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15512,10 +15511,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080282</v>
+        <v>129080297</v>
       </c>
       <c r="B151" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15523,21 +15522,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15547,10 +15546,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436335</v>
+        <v>436449</v>
       </c>
       <c r="R151" t="n">
-        <v>6786163</v>
+        <v>6786210</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15609,10 +15608,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080297</v>
+        <v>129080331</v>
       </c>
       <c r="B152" t="n">
-        <v>78792</v>
+        <v>88926</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15619,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15643,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436449</v>
+        <v>436491</v>
       </c>
       <c r="R152" t="n">
-        <v>6786210</v>
+        <v>6786094</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15688,6 +15687,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>129080320</v>
       </c>
       <c r="B153" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080309</v>
+        <v>129080308</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16911,10 +16911,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436571</v>
+        <v>436807</v>
       </c>
       <c r="R164" t="n">
-        <v>6785936</v>
+        <v>6785797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16974,7 +16974,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080308</v>
+        <v>129080309</v>
       </c>
       <c r="B165" t="n">
         <v>8450</v>
@@ -17018,10 +17018,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436807</v>
+        <v>436571</v>
       </c>
       <c r="R165" t="n">
-        <v>6785797</v>
+        <v>6785936</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -869,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058331</v>
+        <v>129058299</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436755</v>
+        <v>436545</v>
       </c>
       <c r="R4" t="n">
-        <v>6785905</v>
+        <v>6785800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058341</v>
+        <v>129058303</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436278</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6786206</v>
+        <v>6785831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,45 +1063,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058299</v>
+        <v>129058331</v>
       </c>
       <c r="B6" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436545</v>
+        <v>436755</v>
       </c>
       <c r="R6" t="n">
-        <v>6785800</v>
+        <v>6785905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,45 +1170,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058303</v>
+        <v>129058341</v>
       </c>
       <c r="B7" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436818</v>
+        <v>436278</v>
       </c>
       <c r="R7" t="n">
-        <v>6785831</v>
+        <v>6786206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,54 +1277,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058336</v>
+        <v>129058384</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436336</v>
+        <v>436265</v>
       </c>
       <c r="R8" t="n">
-        <v>6786183</v>
+        <v>6786123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,54 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058329</v>
+        <v>129058350</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436754</v>
+        <v>436465</v>
       </c>
       <c r="R9" t="n">
-        <v>6785822</v>
+        <v>6785855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,43 +1471,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058337</v>
+        <v>129058415</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436322</v>
+        <v>436527</v>
       </c>
       <c r="R10" t="n">
-        <v>6786198</v>
+        <v>6785990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1545,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058384</v>
+        <v>129058321</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1588,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436265</v>
+        <v>436377</v>
       </c>
       <c r="R11" t="n">
-        <v>6786123</v>
+        <v>6786201</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058350</v>
+        <v>129058304</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1685,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436465</v>
+        <v>436683</v>
       </c>
       <c r="R12" t="n">
-        <v>6785855</v>
+        <v>6785939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,37 +1771,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058415</v>
+        <v>129058337</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1830,10 +1815,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436527</v>
+        <v>436322</v>
       </c>
       <c r="R13" t="n">
-        <v>6785990</v>
+        <v>6786198</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1851,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,45 +1878,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058304</v>
+        <v>129058329</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436683</v>
+        <v>436754</v>
       </c>
       <c r="R14" t="n">
-        <v>6785939</v>
+        <v>6785822</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,6 +1966,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1995,45 +1985,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129058321</v>
+        <v>129058336</v>
       </c>
       <c r="B15" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436377</v>
+        <v>436336</v>
       </c>
       <c r="R15" t="n">
-        <v>6786201</v>
+        <v>6786183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,6 +2073,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058286</v>
+        <v>129058382</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,42 +2103,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436617</v>
+        <v>436214</v>
       </c>
       <c r="R16" t="n">
-        <v>6785749</v>
+        <v>6786180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,54 +2189,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058332</v>
+        <v>129058403</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436648</v>
+        <v>436259</v>
       </c>
       <c r="R17" t="n">
-        <v>6785874</v>
+        <v>6786285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,7 +2268,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058382</v>
+        <v>129058365</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2339,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436214</v>
+        <v>436467</v>
       </c>
       <c r="R18" t="n">
-        <v>6786180</v>
+        <v>6786236</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058403</v>
+        <v>129058286</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2412,34 +2394,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436259</v>
+        <v>436617</v>
       </c>
       <c r="R19" t="n">
-        <v>6786285</v>
+        <v>6785749</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,10 +2488,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058365</v>
+        <v>129058308</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2509,21 +2499,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2533,10 +2523,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436467</v>
+        <v>436545</v>
       </c>
       <c r="R20" t="n">
-        <v>6786236</v>
+        <v>6785997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,7 +2585,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058308</v>
+        <v>129058317</v>
       </c>
       <c r="B21" t="n">
         <v>78793</v>
@@ -2624,16 +2614,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436545</v>
+        <v>436356</v>
       </c>
       <c r="R21" t="n">
-        <v>6785997</v>
+        <v>6786224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,6 +2667,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2692,7 +2686,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058301</v>
+        <v>129058307</v>
       </c>
       <c r="B22" t="n">
         <v>78793</v>
@@ -2727,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436796</v>
+        <v>436597</v>
       </c>
       <c r="R22" t="n">
-        <v>6785778</v>
+        <v>6785981</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058317</v>
+        <v>129058280</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2800,37 +2794,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436356</v>
+        <v>436519</v>
       </c>
       <c r="R23" t="n">
-        <v>6786224</v>
+        <v>6785988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2871,7 +2862,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2890,45 +2880,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058307</v>
+        <v>129058332</v>
       </c>
       <c r="B24" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436597</v>
+        <v>436648</v>
       </c>
       <c r="R24" t="n">
-        <v>6785981</v>
+        <v>6785874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,6 +2968,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2987,10 +2987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058280</v>
+        <v>129058301</v>
       </c>
       <c r="B25" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2998,21 +2998,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436519</v>
+        <v>436796</v>
       </c>
       <c r="R25" t="n">
-        <v>6785988</v>
+        <v>6785778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058311</v>
+        <v>129058272</v>
       </c>
       <c r="B29" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,34 +3414,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436530</v>
+        <v>436369</v>
       </c>
       <c r="R29" t="n">
-        <v>6785992</v>
+        <v>6786195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,6 +3485,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3500,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058272</v>
+        <v>129058311</v>
       </c>
       <c r="B30" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,37 +3515,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436369</v>
+        <v>436530</v>
       </c>
       <c r="R30" t="n">
-        <v>6786195</v>
+        <v>6785992</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3582,7 +3583,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058288</v>
+        <v>129058319</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,31 +3612,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3644,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436458</v>
+        <v>436378</v>
       </c>
       <c r="R31" t="n">
-        <v>6786194</v>
+        <v>6786219</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,6 +3683,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3706,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058319</v>
+        <v>129058273</v>
       </c>
       <c r="B32" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,21 +3713,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436378</v>
+        <v>436257</v>
       </c>
       <c r="R32" t="n">
-        <v>6786219</v>
+        <v>6786288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3807,10 +3803,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058273</v>
+        <v>129058369</v>
       </c>
       <c r="B33" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,37 +3814,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436257</v>
+        <v>436817</v>
       </c>
       <c r="R33" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3889,7 +3882,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3908,10 +3900,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058369</v>
+        <v>129058288</v>
       </c>
       <c r="B34" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3919,34 +3911,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436817</v>
+        <v>436458</v>
       </c>
       <c r="R34" t="n">
-        <v>6785838</v>
+        <v>6786194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058278</v>
+        <v>129058262</v>
       </c>
       <c r="B35" t="n">
         <v>79654</v>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436295</v>
+        <v>436534</v>
       </c>
       <c r="R35" t="n">
-        <v>6786172</v>
+        <v>6785834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4102,54 +4102,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058325</v>
+        <v>129058269</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436443</v>
+        <v>436483</v>
       </c>
       <c r="R36" t="n">
-        <v>6785940</v>
+        <v>6786017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4190,7 +4181,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4209,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058318</v>
+        <v>129058277</v>
       </c>
       <c r="B37" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4247,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436354</v>
+        <v>436351</v>
       </c>
       <c r="R37" t="n">
-        <v>6786212</v>
+        <v>6786185</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4310,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058262</v>
+        <v>129058404</v>
       </c>
       <c r="B38" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4321,21 +4311,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4345,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436534</v>
+        <v>436229</v>
       </c>
       <c r="R38" t="n">
-        <v>6785834</v>
+        <v>6786238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4407,10 +4397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058269</v>
+        <v>129058348</v>
       </c>
       <c r="B39" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4418,21 +4408,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4442,10 +4432,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436483</v>
+        <v>436266</v>
       </c>
       <c r="R39" t="n">
-        <v>6786017</v>
+        <v>6786145</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4504,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058277</v>
+        <v>129058357</v>
       </c>
       <c r="B40" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4515,37 +4505,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436351</v>
+        <v>436686</v>
       </c>
       <c r="R40" t="n">
-        <v>6786185</v>
+        <v>6785940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4586,7 +4573,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4605,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058404</v>
+        <v>129058278</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4616,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4640,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436229</v>
+        <v>436295</v>
       </c>
       <c r="R41" t="n">
-        <v>6786238</v>
+        <v>6786172</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4702,10 +4688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058348</v>
+        <v>129058318</v>
       </c>
       <c r="B42" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,34 +4699,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436266</v>
+        <v>436354</v>
       </c>
       <c r="R42" t="n">
-        <v>6786145</v>
+        <v>6786212</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4781,6 +4770,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4799,42 +4789,51 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058357</v>
+        <v>129058325</v>
       </c>
       <c r="B43" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436686</v>
+        <v>436443</v>
       </c>
       <c r="R43" t="n">
         <v>6785940</v>
@@ -4878,6 +4877,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058385</v>
+        <v>129058395</v>
       </c>
       <c r="B48" t="n">
         <v>79035</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R48" t="n">
-        <v>6786086</v>
+        <v>6786102</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058268</v>
+        <v>129058385</v>
       </c>
       <c r="B49" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R49" t="n">
-        <v>6786023</v>
+        <v>6786086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058386</v>
+        <v>129058268</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,21 +5489,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436505</v>
+        <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6785856</v>
+        <v>6786023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058290</v>
+        <v>129058386</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,42 +5586,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436601</v>
+        <v>436505</v>
       </c>
       <c r="R51" t="n">
-        <v>6785947</v>
+        <v>6785856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058309</v>
+        <v>129058290</v>
       </c>
       <c r="B52" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,34 +5683,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436532</v>
+        <v>436601</v>
       </c>
       <c r="R52" t="n">
-        <v>6785994</v>
+        <v>6785947</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058395</v>
+        <v>129058309</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436504</v>
+        <v>436532</v>
       </c>
       <c r="R53" t="n">
-        <v>6786102</v>
+        <v>6785994</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129058279</v>
+        <v>129058402</v>
       </c>
       <c r="B54" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5885,21 +5885,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436594</v>
+        <v>436264</v>
       </c>
       <c r="R54" t="n">
-        <v>6785915</v>
+        <v>6786282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5948,6 +5948,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5975,10 +5980,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058306</v>
+        <v>129058396</v>
       </c>
       <c r="B55" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5986,37 +5991,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436598</v>
+        <v>436491</v>
       </c>
       <c r="R55" t="n">
-        <v>6785911</v>
+        <v>6786189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6057,7 +6059,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6076,7 +6077,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129058402</v>
+        <v>129058392</v>
       </c>
       <c r="B56" t="n">
         <v>79035</v>
@@ -6114,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436264</v>
+        <v>436508</v>
       </c>
       <c r="R56" t="n">
-        <v>6786282</v>
+        <v>6786026</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6154,7 +6155,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6182,7 +6183,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129058396</v>
+        <v>129058391</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6211,16 +6212,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436491</v>
+        <v>436591</v>
       </c>
       <c r="R57" t="n">
-        <v>6786189</v>
+        <v>6785966</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6255,12 +6259,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6279,7 +6289,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129058392</v>
+        <v>129058399</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6317,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436508</v>
+        <v>436303</v>
       </c>
       <c r="R58" t="n">
-        <v>6786026</v>
+        <v>6786193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6357,7 +6367,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Garnlav inom en radie av 40m</t>
+          <t>Rikligt med Garnlav inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6385,10 +6395,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129058391</v>
+        <v>129058279</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6396,21 +6406,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6433,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436591</v>
+        <v>436594</v>
       </c>
       <c r="R59" t="n">
-        <v>6785966</v>
+        <v>6785915</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6459,11 +6469,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6491,10 +6496,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129058399</v>
+        <v>129058306</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6502,21 +6507,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6529,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436303</v>
+        <v>436598</v>
       </c>
       <c r="R60" t="n">
-        <v>6786193</v>
+        <v>6785911</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,11 +6570,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058335</v>
+        <v>129058323</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436360</v>
+        <v>436241</v>
       </c>
       <c r="R62" t="n">
-        <v>6786231</v>
+        <v>6786159</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058340</v>
+        <v>129058330</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436324</v>
+        <v>436823</v>
       </c>
       <c r="R63" t="n">
-        <v>6786220</v>
+        <v>6785756</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6916,54 +6916,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058330</v>
+        <v>129058361</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436823</v>
+        <v>436500</v>
       </c>
       <c r="R64" t="n">
-        <v>6785756</v>
+        <v>6786018</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +6995,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7023,43 +7013,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058323</v>
+        <v>129058389</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7067,10 +7051,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436241</v>
+        <v>436739</v>
       </c>
       <c r="R65" t="n">
-        <v>6786159</v>
+        <v>6785902</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7103,6 +7087,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7130,10 +7119,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058361</v>
+        <v>129058405</v>
       </c>
       <c r="B66" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7141,21 +7130,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7165,10 +7154,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436500</v>
+        <v>436227</v>
       </c>
       <c r="R66" t="n">
-        <v>6786018</v>
+        <v>6786243</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7227,10 +7216,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058389</v>
+        <v>129058353</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7238,37 +7227,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436739</v>
+        <v>436551</v>
       </c>
       <c r="R67" t="n">
-        <v>6785902</v>
+        <v>6785765</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,18 +7289,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7333,10 +7313,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058405</v>
+        <v>129058271</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7344,21 +7324,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7368,10 +7348,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436227</v>
+        <v>436493</v>
       </c>
       <c r="R68" t="n">
-        <v>6786243</v>
+        <v>6786189</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7430,45 +7410,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058353</v>
+        <v>129058340</v>
       </c>
       <c r="B69" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436551</v>
+        <v>436324</v>
       </c>
       <c r="R69" t="n">
-        <v>6785765</v>
+        <v>6786220</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,6 +7498,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7527,45 +7517,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058271</v>
+        <v>129058335</v>
       </c>
       <c r="B70" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436493</v>
+        <v>436360</v>
       </c>
       <c r="R70" t="n">
-        <v>6786189</v>
+        <v>6786231</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7606,6 +7605,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7624,54 +7624,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058334</v>
+        <v>129058267</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436373</v>
+        <v>436524</v>
       </c>
       <c r="R71" t="n">
-        <v>6786190</v>
+        <v>6785977</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7703,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7731,10 +7721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058267</v>
+        <v>129058362</v>
       </c>
       <c r="B72" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7742,21 +7732,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7766,10 +7756,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436524</v>
+        <v>436494</v>
       </c>
       <c r="R72" t="n">
-        <v>6785977</v>
+        <v>6786028</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,10 +7818,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058362</v>
+        <v>129058264</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7839,21 +7829,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7863,10 +7853,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436494</v>
+        <v>436599</v>
       </c>
       <c r="R73" t="n">
-        <v>6786028</v>
+        <v>6785738</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7925,10 +7915,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058264</v>
+        <v>129058354</v>
       </c>
       <c r="B74" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7936,21 +7926,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7960,10 +7950,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436599</v>
+        <v>436796</v>
       </c>
       <c r="R74" t="n">
-        <v>6785738</v>
+        <v>6785778</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8022,7 +8012,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058354</v>
+        <v>129058359</v>
       </c>
       <c r="B75" t="n">
         <v>78792</v>
@@ -8057,10 +8047,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436796</v>
+        <v>436532</v>
       </c>
       <c r="R75" t="n">
-        <v>6785778</v>
+        <v>6785994</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8119,7 +8109,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058359</v>
+        <v>129058367</v>
       </c>
       <c r="B76" t="n">
         <v>78792</v>
@@ -8154,10 +8144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436532</v>
+        <v>436371</v>
       </c>
       <c r="R76" t="n">
-        <v>6785994</v>
+        <v>6786199</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8216,10 +8206,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058367</v>
+        <v>129058305</v>
       </c>
       <c r="B77" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8227,34 +8217,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436371</v>
+        <v>436680</v>
       </c>
       <c r="R77" t="n">
-        <v>6786199</v>
+        <v>6785902</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8295,6 +8288,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8313,37 +8307,43 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058305</v>
+        <v>129058334</v>
       </c>
       <c r="B78" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436680</v>
+        <v>436373</v>
       </c>
       <c r="R78" t="n">
-        <v>6785902</v>
+        <v>6786190</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058355</v>
+        <v>129058315</v>
       </c>
       <c r="B79" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,37 +8425,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436825</v>
+        <v>436445</v>
       </c>
       <c r="R79" t="n">
-        <v>6785764</v>
+        <v>6786210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8496,7 +8493,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8515,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058394</v>
+        <v>129058355</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,34 +8522,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436493</v>
+        <v>436825</v>
       </c>
       <c r="R80" t="n">
-        <v>6786075</v>
+        <v>6785764</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8594,6 +8593,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058356</v>
+        <v>129058394</v>
       </c>
       <c r="B81" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,21 +8623,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436818</v>
+        <v>436493</v>
       </c>
       <c r="R81" t="n">
-        <v>6785831</v>
+        <v>6786075</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058282</v>
+        <v>129058356</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,42 +8720,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436515</v>
+        <v>436818</v>
       </c>
       <c r="R82" t="n">
-        <v>6786055</v>
+        <v>6785831</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8814,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058315</v>
+        <v>129058282</v>
       </c>
       <c r="B83" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8825,34 +8817,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436445</v>
+        <v>436515</v>
       </c>
       <c r="R83" t="n">
-        <v>6786210</v>
+        <v>6786055</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9991,54 +9991,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058345</v>
+        <v>129058407</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436269</v>
+        <v>436215</v>
       </c>
       <c r="R95" t="n">
-        <v>6786257</v>
+        <v>6786222</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,7 +10070,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10098,43 +10088,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058333</v>
+        <v>129058416</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10142,10 +10126,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436432</v>
+        <v>436491</v>
       </c>
       <c r="R96" t="n">
-        <v>6786210</v>
+        <v>6786146</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10178,6 +10162,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10205,10 +10194,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058407</v>
+        <v>129058300</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10216,21 +10205,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10240,10 +10229,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436215</v>
+        <v>436554</v>
       </c>
       <c r="R97" t="n">
-        <v>6786222</v>
+        <v>6785764</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10302,10 +10291,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058416</v>
+        <v>129058298</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10313,37 +10302,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436491</v>
+        <v>436513</v>
       </c>
       <c r="R98" t="n">
-        <v>6786146</v>
+        <v>6785845</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10378,18 +10364,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10408,45 +10388,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058300</v>
+        <v>129058333</v>
       </c>
       <c r="B99" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436554</v>
+        <v>436432</v>
       </c>
       <c r="R99" t="n">
-        <v>6785764</v>
+        <v>6786210</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10487,6 +10476,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10505,45 +10495,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058298</v>
+        <v>129058345</v>
       </c>
       <c r="B100" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436513</v>
+        <v>436269</v>
       </c>
       <c r="R100" t="n">
-        <v>6785845</v>
+        <v>6786257</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10584,6 +10583,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129058401</v>
+        <v>129058364</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436310</v>
+        <v>436425</v>
       </c>
       <c r="R102" t="n">
-        <v>6786196</v>
+        <v>6786192</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058390</v>
+        <v>129058401</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436700</v>
+        <v>436310</v>
       </c>
       <c r="R103" t="n">
-        <v>6785944</v>
+        <v>6786196</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058266</v>
+        <v>129058390</v>
       </c>
       <c r="B104" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10904,21 +10904,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436532</v>
+        <v>436700</v>
       </c>
       <c r="R104" t="n">
-        <v>6785994</v>
+        <v>6785944</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10990,10 +10990,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129058364</v>
+        <v>129058266</v>
       </c>
       <c r="B105" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11001,21 +11001,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436425</v>
+        <v>436532</v>
       </c>
       <c r="R105" t="n">
-        <v>6786192</v>
+        <v>6785994</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080302</v>
+        <v>129080295</v>
       </c>
       <c r="B120" t="n">
-        <v>91546</v>
+        <v>78793</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436320</v>
+        <v>436815</v>
       </c>
       <c r="R120" t="n">
-        <v>6786132</v>
+        <v>6785768</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,7 +12566,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12585,10 +12584,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080277</v>
+        <v>129080294</v>
       </c>
       <c r="B121" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12596,21 +12595,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12620,10 +12619,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436561</v>
+        <v>436659</v>
       </c>
       <c r="R121" t="n">
-        <v>6785959</v>
+        <v>6785808</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12682,7 +12681,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129080295</v>
+        <v>129080291</v>
       </c>
       <c r="B122" t="n">
         <v>78793</v>
@@ -12717,10 +12716,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436815</v>
+        <v>436524</v>
       </c>
       <c r="R122" t="n">
-        <v>6785768</v>
+        <v>6785865</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12779,10 +12778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080294</v>
+        <v>129080302</v>
       </c>
       <c r="B123" t="n">
-        <v>78793</v>
+        <v>91546</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12790,21 +12789,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12814,10 +12813,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436659</v>
+        <v>436320</v>
       </c>
       <c r="R123" t="n">
-        <v>6785808</v>
+        <v>6786132</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12858,6 +12857,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12876,10 +12876,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080291</v>
+        <v>129080277</v>
       </c>
       <c r="B124" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,21 +12887,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436524</v>
+        <v>436561</v>
       </c>
       <c r="R124" t="n">
-        <v>6785865</v>
+        <v>6785959</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13167,10 +13167,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129080298</v>
+        <v>129080281</v>
       </c>
       <c r="B127" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436428</v>
+        <v>436448</v>
       </c>
       <c r="R127" t="n">
-        <v>6786194</v>
+        <v>6786211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B128" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R128" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080281</v>
+        <v>129080298</v>
       </c>
       <c r="B129" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13372,21 +13372,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436448</v>
+        <v>436428</v>
       </c>
       <c r="R129" t="n">
-        <v>6786211</v>
+        <v>6786194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R130" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14040,10 +14040,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129080284</v>
+        <v>129080317</v>
       </c>
       <c r="B136" t="n">
-        <v>91546</v>
+        <v>78792</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>436494</v>
+        <v>436816</v>
       </c>
       <c r="R136" t="n">
-        <v>6785930</v>
+        <v>6785768</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14137,7 +14137,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080317</v>
+        <v>129080316</v>
       </c>
       <c r="B137" t="n">
         <v>78792</v>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436816</v>
+        <v>436532</v>
       </c>
       <c r="R137" t="n">
-        <v>6785768</v>
+        <v>6785867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,10 +14234,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080316</v>
+        <v>129080284</v>
       </c>
       <c r="B138" t="n">
-        <v>78792</v>
+        <v>91546</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436532</v>
+        <v>436494</v>
       </c>
       <c r="R138" t="n">
-        <v>6785867</v>
+        <v>6785930</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15117,10 +15117,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129080280</v>
+        <v>129080315</v>
       </c>
       <c r="B147" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15128,21 +15128,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15152,10 +15152,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>436461</v>
+        <v>436523</v>
       </c>
       <c r="R147" t="n">
-        <v>6786160</v>
+        <v>6785864</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15214,10 +15214,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129080315</v>
+        <v>129080280</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15225,21 +15225,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>436523</v>
+        <v>436461</v>
       </c>
       <c r="R148" t="n">
-        <v>6785864</v>
+        <v>6786160</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080283</v>
+        <v>129080297</v>
       </c>
       <c r="B149" t="n">
-        <v>91526</v>
+        <v>78793</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436434</v>
+        <v>436449</v>
       </c>
       <c r="R149" t="n">
-        <v>6786112</v>
+        <v>6786210</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15384,18 +15384,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15414,10 +15408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080282</v>
+        <v>129080331</v>
       </c>
       <c r="B150" t="n">
-        <v>79654</v>
+        <v>88926</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15425,21 +15419,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15449,10 +15443,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436335</v>
+        <v>436491</v>
       </c>
       <c r="R150" t="n">
-        <v>6786163</v>
+        <v>6786094</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15493,6 +15487,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15511,10 +15506,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080297</v>
+        <v>129080283</v>
       </c>
       <c r="B151" t="n">
-        <v>78793</v>
+        <v>91526</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15522,21 +15517,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15546,10 +15541,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436449</v>
+        <v>436434</v>
       </c>
       <c r="R151" t="n">
-        <v>6786210</v>
+        <v>6786112</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15584,12 +15579,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15608,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080331</v>
+        <v>129080282</v>
       </c>
       <c r="B152" t="n">
-        <v>88926</v>
+        <v>79654</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15619,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15643,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436491</v>
+        <v>436335</v>
       </c>
       <c r="R152" t="n">
-        <v>6786094</v>
+        <v>6786163</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15687,7 +15688,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16441,7 +16441,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080310</v>
+        <v>129080311</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16485,10 +16485,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436472</v>
+        <v>436449</v>
       </c>
       <c r="R160" t="n">
-        <v>6786160</v>
+        <v>6786212</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16655,7 +16655,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080311</v>
+        <v>129080310</v>
       </c>
       <c r="B162" t="n">
         <v>8450</v>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436449</v>
+        <v>436472</v>
       </c>
       <c r="R162" t="n">
-        <v>6786212</v>
+        <v>6786160</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16762,40 +16762,41 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080286</v>
+        <v>129080308</v>
       </c>
       <c r="B163" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16805,10 +16806,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436572</v>
+        <v>436807</v>
       </c>
       <c r="R163" t="n">
-        <v>6785762</v>
+        <v>6785797</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16849,6 +16850,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16867,41 +16869,40 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080308</v>
+        <v>129080286</v>
       </c>
       <c r="B164" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -16911,10 +16912,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436807</v>
+        <v>436572</v>
       </c>
       <c r="R164" t="n">
-        <v>6785797</v>
+        <v>6785762</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16955,7 +16956,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058274</v>
+        <v>129058331</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436522</v>
+        <v>436755</v>
       </c>
       <c r="R2" t="n">
-        <v>6786062</v>
+        <v>6785905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058412</v>
+        <v>129058341</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436564</v>
+        <v>436278</v>
       </c>
       <c r="R3" t="n">
-        <v>6785776</v>
+        <v>6786206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058299</v>
+        <v>129058274</v>
       </c>
       <c r="B4" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436545</v>
+        <v>436522</v>
       </c>
       <c r="R4" t="n">
-        <v>6785800</v>
+        <v>6786062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058303</v>
+        <v>129058412</v>
       </c>
       <c r="B5" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>436564</v>
       </c>
       <c r="R5" t="n">
-        <v>6785831</v>
+        <v>6785776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,54 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058331</v>
+        <v>129058299</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436755</v>
+        <v>436545</v>
       </c>
       <c r="R6" t="n">
-        <v>6785905</v>
+        <v>6785800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1170,54 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058341</v>
+        <v>129058303</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436278</v>
+        <v>436818</v>
       </c>
       <c r="R7" t="n">
-        <v>6786206</v>
+        <v>6785831</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,7 +1259,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2585,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058317</v>
+        <v>129058301</v>
       </c>
       <c r="B21" t="n">
         <v>78793</v>
@@ -2614,19 +2614,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436356</v>
+        <v>436796</v>
       </c>
       <c r="R21" t="n">
-        <v>6786224</v>
+        <v>6785778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2667,7 +2664,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2682,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058307</v>
+        <v>129058317</v>
       </c>
       <c r="B22" t="n">
         <v>78793</v>
@@ -2715,16 +2711,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436597</v>
+        <v>436356</v>
       </c>
       <c r="R22" t="n">
-        <v>6785981</v>
+        <v>6786224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2765,6 +2764,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058280</v>
+        <v>129058307</v>
       </c>
       <c r="B23" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436519</v>
+        <v>436597</v>
       </c>
       <c r="R23" t="n">
-        <v>6785988</v>
+        <v>6785981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2880,54 +2880,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058332</v>
+        <v>129058280</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436648</v>
+        <v>436519</v>
       </c>
       <c r="R24" t="n">
-        <v>6785874</v>
+        <v>6785988</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2968,7 +2959,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2987,45 +2977,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058301</v>
+        <v>129058332</v>
       </c>
       <c r="B25" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436796</v>
+        <v>436648</v>
       </c>
       <c r="R25" t="n">
-        <v>6785778</v>
+        <v>6785874</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,6 +3065,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058287</v>
+        <v>129058272</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,31 +3095,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3127,10 +3122,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436718</v>
+        <v>436369</v>
       </c>
       <c r="R26" t="n">
-        <v>6785941</v>
+        <v>6786195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3189,41 +3185,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058343</v>
+        <v>129058287</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3233,10 +3228,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436269</v>
+        <v>436718</v>
       </c>
       <c r="R27" t="n">
-        <v>6786228</v>
+        <v>6785941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3277,7 +3272,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3296,7 +3290,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058327</v>
+        <v>129058343</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3340,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436674</v>
+        <v>436269</v>
       </c>
       <c r="R28" t="n">
-        <v>6785802</v>
+        <v>6786228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3403,37 +3397,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058272</v>
+        <v>129058327</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436369</v>
+        <v>436674</v>
       </c>
       <c r="R29" t="n">
-        <v>6786195</v>
+        <v>6785802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058395</v>
+        <v>129058290</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,34 +5295,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436504</v>
+        <v>436601</v>
       </c>
       <c r="R48" t="n">
-        <v>6786102</v>
+        <v>6785947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,7 +5389,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058385</v>
+        <v>129058395</v>
       </c>
       <c r="B49" t="n">
         <v>79035</v>
@@ -5416,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R49" t="n">
-        <v>6786086</v>
+        <v>6786102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058268</v>
+        <v>129058385</v>
       </c>
       <c r="B50" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5513,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R50" t="n">
-        <v>6786023</v>
+        <v>6786086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058386</v>
+        <v>129058268</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5610,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436505</v>
+        <v>436504</v>
       </c>
       <c r="R51" t="n">
-        <v>6785856</v>
+        <v>6786023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058290</v>
+        <v>129058386</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,42 +5691,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436601</v>
+        <v>436505</v>
       </c>
       <c r="R52" t="n">
-        <v>6785947</v>
+        <v>6785856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7624,45 +7624,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058267</v>
+        <v>129058334</v>
       </c>
       <c r="B71" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436524</v>
+        <v>436373</v>
       </c>
       <c r="R71" t="n">
-        <v>6785977</v>
+        <v>6786190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7703,6 +7712,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7721,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058362</v>
+        <v>129058267</v>
       </c>
       <c r="B72" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7732,21 +7742,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7756,10 +7766,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436494</v>
+        <v>436524</v>
       </c>
       <c r="R72" t="n">
-        <v>6786028</v>
+        <v>6785977</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7818,10 +7828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058264</v>
+        <v>129058362</v>
       </c>
       <c r="B73" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7829,21 +7839,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7853,10 +7863,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436599</v>
+        <v>436494</v>
       </c>
       <c r="R73" t="n">
-        <v>6785738</v>
+        <v>6786028</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7915,10 +7925,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058354</v>
+        <v>129058264</v>
       </c>
       <c r="B74" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7926,21 +7936,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7950,10 +7960,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436796</v>
+        <v>436599</v>
       </c>
       <c r="R74" t="n">
-        <v>6785778</v>
+        <v>6785738</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8012,7 +8022,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058359</v>
+        <v>129058354</v>
       </c>
       <c r="B75" t="n">
         <v>78792</v>
@@ -8047,10 +8057,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436532</v>
+        <v>436796</v>
       </c>
       <c r="R75" t="n">
-        <v>6785994</v>
+        <v>6785778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8109,7 +8119,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058367</v>
+        <v>129058359</v>
       </c>
       <c r="B76" t="n">
         <v>78792</v>
@@ -8144,10 +8154,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436371</v>
+        <v>436532</v>
       </c>
       <c r="R76" t="n">
-        <v>6786199</v>
+        <v>6785994</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,10 +8216,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058305</v>
+        <v>129058367</v>
       </c>
       <c r="B77" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8217,37 +8227,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436680</v>
+        <v>436371</v>
       </c>
       <c r="R77" t="n">
-        <v>6785902</v>
+        <v>6786199</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8288,7 +8295,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8307,43 +8313,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058334</v>
+        <v>129058305</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436373</v>
+        <v>436680</v>
       </c>
       <c r="R78" t="n">
-        <v>6786190</v>
+        <v>6785902</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058346</v>
+        <v>129058314</v>
       </c>
       <c r="B93" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436503</v>
+        <v>436510</v>
       </c>
       <c r="R93" t="n">
-        <v>6786136</v>
+        <v>6786074</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058314</v>
+        <v>129058346</v>
       </c>
       <c r="B94" t="n">
-        <v>78793</v>
+        <v>58093</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436510</v>
+        <v>436503</v>
       </c>
       <c r="R94" t="n">
-        <v>6786074</v>
+        <v>6786136</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11582,41 +11582,40 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058328</v>
+        <v>129058289</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11626,10 +11625,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436701</v>
+        <v>436486</v>
       </c>
       <c r="R111" t="n">
-        <v>6785838</v>
+        <v>6786231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11670,7 +11669,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11689,45 +11687,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058368</v>
+        <v>129058328</v>
       </c>
       <c r="B112" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436257</v>
+        <v>436701</v>
       </c>
       <c r="R112" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11768,6 +11775,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11786,10 +11794,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058289</v>
+        <v>129058368</v>
       </c>
       <c r="B113" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11797,42 +11805,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436486</v>
+        <v>436257</v>
       </c>
       <c r="R113" t="n">
-        <v>6786231</v>
+        <v>6786288</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080295</v>
+        <v>129080277</v>
       </c>
       <c r="B120" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436815</v>
+        <v>436561</v>
       </c>
       <c r="R120" t="n">
-        <v>6785768</v>
+        <v>6785959</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12584,10 +12584,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080294</v>
+        <v>129080302</v>
       </c>
       <c r="B121" t="n">
-        <v>78793</v>
+        <v>91546</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,21 +12595,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12619,10 +12619,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436659</v>
+        <v>436320</v>
       </c>
       <c r="R121" t="n">
-        <v>6785808</v>
+        <v>6786132</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,6 +12663,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12681,7 +12682,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129080291</v>
+        <v>129080295</v>
       </c>
       <c r="B122" t="n">
         <v>78793</v>
@@ -12716,10 +12717,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436524</v>
+        <v>436815</v>
       </c>
       <c r="R122" t="n">
-        <v>6785865</v>
+        <v>6785768</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12778,10 +12779,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080302</v>
+        <v>129080294</v>
       </c>
       <c r="B123" t="n">
-        <v>91546</v>
+        <v>78793</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12789,21 +12790,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12813,10 +12814,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436320</v>
+        <v>436659</v>
       </c>
       <c r="R123" t="n">
-        <v>6786132</v>
+        <v>6785808</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12857,7 +12858,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12876,10 +12876,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080277</v>
+        <v>129080291</v>
       </c>
       <c r="B124" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,21 +12887,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436561</v>
+        <v>436524</v>
       </c>
       <c r="R124" t="n">
-        <v>6785959</v>
+        <v>6785865</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B125" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R125" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,10 +13070,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B126" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R126" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B131" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R131" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B132" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R132" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058331</v>
+        <v>129058412</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436755</v>
+        <v>436564</v>
       </c>
       <c r="R2" t="n">
-        <v>6785905</v>
+        <v>6785776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058341</v>
+        <v>129058274</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436278</v>
+        <v>436522</v>
       </c>
       <c r="R3" t="n">
-        <v>6786206</v>
+        <v>6786062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058274</v>
+        <v>129058331</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436522</v>
+        <v>436755</v>
       </c>
       <c r="R4" t="n">
-        <v>6786062</v>
+        <v>6785905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +957,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,45 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058412</v>
+        <v>129058341</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436564</v>
+        <v>436278</v>
       </c>
       <c r="R5" t="n">
-        <v>6785776</v>
+        <v>6786206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1064,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1277,45 +1277,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058384</v>
+        <v>129058336</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436265</v>
+        <v>436336</v>
       </c>
       <c r="R8" t="n">
-        <v>6786123</v>
+        <v>6786183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,6 +1365,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,45 +1384,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058350</v>
+        <v>129058329</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436465</v>
+        <v>436754</v>
       </c>
       <c r="R9" t="n">
-        <v>6785855</v>
+        <v>6785822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,37 +1491,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058415</v>
+        <v>129058337</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1509,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436527</v>
+        <v>436322</v>
       </c>
       <c r="R10" t="n">
-        <v>6785990</v>
+        <v>6786198</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1545,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058321</v>
+        <v>129058304</v>
       </c>
       <c r="B11" t="n">
         <v>78793</v>
@@ -1612,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436377</v>
+        <v>436683</v>
       </c>
       <c r="R11" t="n">
-        <v>6786201</v>
+        <v>6785939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058304</v>
+        <v>129058321</v>
       </c>
       <c r="B12" t="n">
         <v>78793</v>
@@ -1709,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436683</v>
+        <v>436377</v>
       </c>
       <c r="R12" t="n">
-        <v>6785939</v>
+        <v>6786201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,54 +1792,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058337</v>
+        <v>129058350</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436322</v>
+        <v>436465</v>
       </c>
       <c r="R13" t="n">
-        <v>6786198</v>
+        <v>6785855</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,7 +1871,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1878,54 +1889,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058329</v>
+        <v>129058384</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436754</v>
+        <v>436265</v>
       </c>
       <c r="R14" t="n">
-        <v>6785822</v>
+        <v>6786123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,7 +1968,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1985,43 +1986,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129058336</v>
+        <v>129058415</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2029,10 +2024,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436336</v>
+        <v>436527</v>
       </c>
       <c r="R15" t="n">
-        <v>6786183</v>
+        <v>6785990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,6 +2060,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058403</v>
+        <v>129058365</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436259</v>
+        <v>436467</v>
       </c>
       <c r="R17" t="n">
-        <v>6786285</v>
+        <v>6786236</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,45 +2286,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058365</v>
+        <v>129058332</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436467</v>
+        <v>436648</v>
       </c>
       <c r="R18" t="n">
-        <v>6786236</v>
+        <v>6785874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,6 +2374,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2383,10 +2393,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058286</v>
+        <v>129058301</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,42 +2404,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436617</v>
+        <v>436796</v>
       </c>
       <c r="R19" t="n">
-        <v>6785749</v>
+        <v>6785778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,7 +2490,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058308</v>
+        <v>129058317</v>
       </c>
       <c r="B20" t="n">
         <v>78793</v>
@@ -2517,16 +2519,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436545</v>
+        <v>436356</v>
       </c>
       <c r="R20" t="n">
-        <v>6785997</v>
+        <v>6786224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2567,6 +2572,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2591,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058301</v>
+        <v>129058307</v>
       </c>
       <c r="B21" t="n">
         <v>78793</v>
@@ -2620,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436796</v>
+        <v>436597</v>
       </c>
       <c r="R21" t="n">
-        <v>6785778</v>
+        <v>6785981</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2682,7 +2688,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058317</v>
+        <v>129058308</v>
       </c>
       <c r="B22" t="n">
         <v>78793</v>
@@ -2711,19 +2717,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436356</v>
+        <v>436545</v>
       </c>
       <c r="R22" t="n">
-        <v>6786224</v>
+        <v>6785997</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,7 +2767,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2783,10 +2785,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058307</v>
+        <v>129058280</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,21 +2796,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2818,10 +2820,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436597</v>
+        <v>436519</v>
       </c>
       <c r="R23" t="n">
-        <v>6785981</v>
+        <v>6785988</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2880,10 +2882,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058280</v>
+        <v>129058403</v>
       </c>
       <c r="B24" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2891,21 +2893,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2915,10 +2917,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436519</v>
+        <v>436259</v>
       </c>
       <c r="R24" t="n">
-        <v>6785988</v>
+        <v>6786285</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,41 +2979,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058332</v>
+        <v>129058286</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3021,10 +3022,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436648</v>
+        <v>436617</v>
       </c>
       <c r="R25" t="n">
-        <v>6785874</v>
+        <v>6785749</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3065,7 +3066,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3084,37 +3084,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058272</v>
+        <v>129058343</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3122,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436369</v>
+        <v>436269</v>
       </c>
       <c r="R26" t="n">
-        <v>6786195</v>
+        <v>6786228</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,40 +3191,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058287</v>
+        <v>129058327</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3228,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436718</v>
+        <v>436674</v>
       </c>
       <c r="R27" t="n">
-        <v>6785941</v>
+        <v>6785802</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,6 +3279,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3290,54 +3298,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058343</v>
+        <v>129058311</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436269</v>
+        <v>436530</v>
       </c>
       <c r="R28" t="n">
-        <v>6786228</v>
+        <v>6785992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3378,7 +3377,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3397,43 +3395,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058327</v>
+        <v>129058272</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3441,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436674</v>
+        <v>436369</v>
       </c>
       <c r="R29" t="n">
-        <v>6785802</v>
+        <v>6786195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,10 +3496,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058311</v>
+        <v>129058287</v>
       </c>
       <c r="B30" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3515,34 +3507,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436530</v>
+        <v>436718</v>
       </c>
       <c r="R30" t="n">
-        <v>6785992</v>
+        <v>6785941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058319</v>
+        <v>129058273</v>
       </c>
       <c r="B31" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436378</v>
+        <v>436257</v>
       </c>
       <c r="R31" t="n">
-        <v>6786219</v>
+        <v>6786288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058273</v>
+        <v>129058369</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,37 +3713,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436257</v>
+        <v>436817</v>
       </c>
       <c r="R32" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,7 +3781,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3803,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058369</v>
+        <v>129058319</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3814,34 +3810,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436817</v>
+        <v>436378</v>
       </c>
       <c r="R33" t="n">
-        <v>6785838</v>
+        <v>6786219</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3882,6 +3881,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058404</v>
+        <v>129058348</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4311,21 +4311,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436229</v>
+        <v>436266</v>
       </c>
       <c r="R38" t="n">
-        <v>6786238</v>
+        <v>6786145</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,10 +4397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058348</v>
+        <v>129058278</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4408,21 +4408,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436266</v>
+        <v>436295</v>
       </c>
       <c r="R39" t="n">
-        <v>6786145</v>
+        <v>6786172</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058357</v>
+        <v>129058404</v>
       </c>
       <c r="B40" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436686</v>
+        <v>436229</v>
       </c>
       <c r="R40" t="n">
-        <v>6785940</v>
+        <v>6786238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,45 +4591,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058278</v>
+        <v>129058325</v>
       </c>
       <c r="B41" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436295</v>
+        <v>436443</v>
       </c>
       <c r="R41" t="n">
-        <v>6786172</v>
+        <v>6785940</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4670,6 +4679,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4789,51 +4799,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058325</v>
+        <v>129058357</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436443</v>
+        <v>436686</v>
       </c>
       <c r="R43" t="n">
         <v>6785940</v>
@@ -4877,7 +4878,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129058351</v>
+        <v>129058297</v>
       </c>
       <c r="B45" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436516</v>
+        <v>436509</v>
       </c>
       <c r="R45" t="n">
         <v>6785859</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129058297</v>
+        <v>129058313</v>
       </c>
       <c r="B46" t="n">
         <v>78793</v>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436509</v>
+        <v>436504</v>
       </c>
       <c r="R46" t="n">
-        <v>6785859</v>
+        <v>6786023</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129058313</v>
+        <v>129058351</v>
       </c>
       <c r="B47" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436504</v>
+        <v>436516</v>
       </c>
       <c r="R47" t="n">
-        <v>6786023</v>
+        <v>6785859</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058290</v>
+        <v>129058309</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,42 +5295,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436601</v>
+        <v>436532</v>
       </c>
       <c r="R48" t="n">
-        <v>6785947</v>
+        <v>6785994</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5389,7 +5381,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058395</v>
+        <v>129058385</v>
       </c>
       <c r="B49" t="n">
         <v>79035</v>
@@ -5424,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R49" t="n">
-        <v>6786102</v>
+        <v>6786086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058385</v>
+        <v>129058395</v>
       </c>
       <c r="B50" t="n">
         <v>79035</v>
@@ -5521,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6786086</v>
+        <v>6786102</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058268</v>
+        <v>129058386</v>
       </c>
       <c r="B51" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5586,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436504</v>
+        <v>436505</v>
       </c>
       <c r="R51" t="n">
-        <v>6786023</v>
+        <v>6785856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058386</v>
+        <v>129058268</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5683,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5707,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436505</v>
+        <v>436504</v>
       </c>
       <c r="R52" t="n">
-        <v>6785856</v>
+        <v>6786023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,10 +5769,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058309</v>
+        <v>129058290</v>
       </c>
       <c r="B53" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,34 +5780,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436532</v>
+        <v>436601</v>
       </c>
       <c r="R53" t="n">
-        <v>6785994</v>
+        <v>6785947</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129058402</v>
+        <v>129058396</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -5903,19 +5903,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436264</v>
+        <v>436491</v>
       </c>
       <c r="R54" t="n">
-        <v>6786282</v>
+        <v>6786189</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5950,18 +5947,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5980,7 +5971,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058396</v>
+        <v>129058402</v>
       </c>
       <c r="B55" t="n">
         <v>79035</v>
@@ -6009,16 +6000,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436491</v>
+        <v>436264</v>
       </c>
       <c r="R55" t="n">
-        <v>6786189</v>
+        <v>6786282</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,12 +6047,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058291</v>
+        <v>129058389</v>
       </c>
       <c r="B61" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,31 +6608,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6640,10 +6635,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436214</v>
+        <v>436739</v>
       </c>
       <c r="R61" t="n">
-        <v>6786222</v>
+        <v>6785902</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6678,12 +6673,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6702,54 +6703,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058323</v>
+        <v>129058405</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436241</v>
+        <v>436227</v>
       </c>
       <c r="R62" t="n">
-        <v>6786159</v>
+        <v>6786243</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6790,7 +6782,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6809,54 +6800,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058330</v>
+        <v>129058353</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436823</v>
+        <v>436551</v>
       </c>
       <c r="R63" t="n">
-        <v>6785756</v>
+        <v>6785765</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6897,7 +6879,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7013,10 +6994,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058389</v>
+        <v>129058271</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7024,37 +7005,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436739</v>
+        <v>436493</v>
       </c>
       <c r="R65" t="n">
-        <v>6785902</v>
+        <v>6786189</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7089,18 +7067,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7119,10 +7091,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058405</v>
+        <v>129058291</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7130,34 +7102,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436227</v>
+        <v>436214</v>
       </c>
       <c r="R66" t="n">
-        <v>6786243</v>
+        <v>6786222</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7216,45 +7196,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058353</v>
+        <v>129058335</v>
       </c>
       <c r="B67" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436551</v>
+        <v>436360</v>
       </c>
       <c r="R67" t="n">
-        <v>6785765</v>
+        <v>6786231</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7295,6 +7284,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7313,45 +7303,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058271</v>
+        <v>129058340</v>
       </c>
       <c r="B68" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436493</v>
+        <v>436324</v>
       </c>
       <c r="R68" t="n">
-        <v>6786189</v>
+        <v>6786220</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,6 +7391,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058340</v>
+        <v>129058330</v>
       </c>
       <c r="B69" t="n">
         <v>8450</v>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436324</v>
+        <v>436823</v>
       </c>
       <c r="R69" t="n">
-        <v>6786220</v>
+        <v>6785756</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058335</v>
+        <v>129058323</v>
       </c>
       <c r="B70" t="n">
         <v>8450</v>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436360</v>
+        <v>436241</v>
       </c>
       <c r="R70" t="n">
-        <v>6786231</v>
+        <v>6786159</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7624,43 +7624,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058334</v>
+        <v>129058305</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7668,10 +7662,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436373</v>
+        <v>436680</v>
       </c>
       <c r="R71" t="n">
-        <v>6786190</v>
+        <v>6785902</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7731,45 +7725,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058267</v>
+        <v>129058334</v>
       </c>
       <c r="B72" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436524</v>
+        <v>436373</v>
       </c>
       <c r="R72" t="n">
-        <v>6785977</v>
+        <v>6786190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7810,6 +7813,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7828,7 +7832,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058362</v>
+        <v>129058354</v>
       </c>
       <c r="B73" t="n">
         <v>78792</v>
@@ -7863,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436494</v>
+        <v>436796</v>
       </c>
       <c r="R73" t="n">
-        <v>6786028</v>
+        <v>6785778</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7925,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058264</v>
+        <v>129058359</v>
       </c>
       <c r="B74" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7936,21 +7940,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7960,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436599</v>
+        <v>436532</v>
       </c>
       <c r="R74" t="n">
-        <v>6785738</v>
+        <v>6785994</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8022,7 +8026,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058354</v>
+        <v>129058367</v>
       </c>
       <c r="B75" t="n">
         <v>78792</v>
@@ -8057,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436796</v>
+        <v>436371</v>
       </c>
       <c r="R75" t="n">
-        <v>6785778</v>
+        <v>6786199</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8119,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058359</v>
+        <v>129058267</v>
       </c>
       <c r="B76" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8130,21 +8134,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8154,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436532</v>
+        <v>436524</v>
       </c>
       <c r="R76" t="n">
-        <v>6785994</v>
+        <v>6785977</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8216,7 +8220,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058367</v>
+        <v>129058362</v>
       </c>
       <c r="B77" t="n">
         <v>78792</v>
@@ -8251,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436371</v>
+        <v>436494</v>
       </c>
       <c r="R77" t="n">
-        <v>6786199</v>
+        <v>6786028</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8313,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058305</v>
+        <v>129058264</v>
       </c>
       <c r="B78" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,37 +8328,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436680</v>
+        <v>436599</v>
       </c>
       <c r="R78" t="n">
-        <v>6785902</v>
+        <v>6785738</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8395,7 +8396,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058315</v>
+        <v>129058355</v>
       </c>
       <c r="B79" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,34 +8425,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436445</v>
+        <v>436825</v>
       </c>
       <c r="R79" t="n">
-        <v>6786210</v>
+        <v>6785764</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8493,6 +8496,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8511,7 +8515,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058355</v>
+        <v>129058356</v>
       </c>
       <c r="B80" t="n">
         <v>78792</v>
@@ -8540,19 +8544,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436825</v>
+        <v>436818</v>
       </c>
       <c r="R80" t="n">
-        <v>6785764</v>
+        <v>6785831</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,7 +8594,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058356</v>
+        <v>129058282</v>
       </c>
       <c r="B82" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,34 +8720,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436818</v>
+        <v>436515</v>
       </c>
       <c r="R82" t="n">
-        <v>6785831</v>
+        <v>6786055</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8806,10 +8814,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058282</v>
+        <v>129058315</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,42 +8825,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436515</v>
+        <v>436445</v>
       </c>
       <c r="R83" t="n">
-        <v>6786055</v>
+        <v>6786210</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9008,10 +9008,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129058263</v>
+        <v>129058414</v>
       </c>
       <c r="B85" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9019,34 +9019,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436559</v>
+        <v>436671</v>
       </c>
       <c r="R85" t="n">
-        <v>6785783</v>
+        <v>6785810</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9081,12 +9084,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9105,7 +9114,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129058414</v>
+        <v>129058397</v>
       </c>
       <c r="B86" t="n">
         <v>79035</v>
@@ -9143,10 +9152,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436671</v>
+        <v>436446</v>
       </c>
       <c r="R86" t="n">
-        <v>6785810</v>
+        <v>6786249</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9179,11 +9188,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9211,7 +9215,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058397</v>
+        <v>129058383</v>
       </c>
       <c r="B87" t="n">
         <v>79035</v>
@@ -9240,19 +9244,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436446</v>
+        <v>436263</v>
       </c>
       <c r="R87" t="n">
-        <v>6786249</v>
+        <v>6786145</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9293,7 +9294,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129058383</v>
+        <v>129058302</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9323,21 +9323,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436263</v>
+        <v>436825</v>
       </c>
       <c r="R88" t="n">
-        <v>6786145</v>
+        <v>6785764</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129058302</v>
+        <v>129058263</v>
       </c>
       <c r="B89" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9420,21 +9420,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436825</v>
+        <v>436559</v>
       </c>
       <c r="R89" t="n">
-        <v>6785764</v>
+        <v>6785783</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9603,7 +9603,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058398</v>
+        <v>129058387</v>
       </c>
       <c r="B91" t="n">
         <v>79035</v>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436425</v>
+        <v>436805</v>
       </c>
       <c r="R91" t="n">
-        <v>6786210</v>
+        <v>6785785</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,7 +9700,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058387</v>
+        <v>129058398</v>
       </c>
       <c r="B92" t="n">
         <v>79035</v>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436805</v>
+        <v>436425</v>
       </c>
       <c r="R92" t="n">
-        <v>6785785</v>
+        <v>6786210</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058314</v>
+        <v>129058346</v>
       </c>
       <c r="B93" t="n">
-        <v>78793</v>
+        <v>58093</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436510</v>
+        <v>436503</v>
       </c>
       <c r="R93" t="n">
-        <v>6786074</v>
+        <v>6786136</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058346</v>
+        <v>129058314</v>
       </c>
       <c r="B94" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436503</v>
+        <v>436510</v>
       </c>
       <c r="R94" t="n">
-        <v>6786136</v>
+        <v>6786074</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10194,45 +10194,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058300</v>
+        <v>129058345</v>
       </c>
       <c r="B97" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436554</v>
+        <v>436269</v>
       </c>
       <c r="R97" t="n">
-        <v>6785764</v>
+        <v>6786257</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,6 +10282,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10291,45 +10301,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058298</v>
+        <v>129058333</v>
       </c>
       <c r="B98" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436513</v>
+        <v>436432</v>
       </c>
       <c r="R98" t="n">
-        <v>6785845</v>
+        <v>6786210</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10370,6 +10389,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10388,54 +10408,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058333</v>
+        <v>129058298</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436432</v>
+        <v>436513</v>
       </c>
       <c r="R99" t="n">
-        <v>6786210</v>
+        <v>6785845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10476,7 +10487,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10495,54 +10505,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058345</v>
+        <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436269</v>
+        <v>436554</v>
       </c>
       <c r="R100" t="n">
-        <v>6786257</v>
+        <v>6785764</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10583,7 +10584,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058401</v>
+        <v>129058266</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436310</v>
+        <v>436532</v>
       </c>
       <c r="R103" t="n">
-        <v>6786196</v>
+        <v>6785994</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,7 +10893,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058390</v>
+        <v>129058401</v>
       </c>
       <c r="B104" t="n">
         <v>79035</v>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436700</v>
+        <v>436310</v>
       </c>
       <c r="R104" t="n">
-        <v>6785944</v>
+        <v>6786196</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10990,10 +10990,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129058266</v>
+        <v>129058390</v>
       </c>
       <c r="B105" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11001,21 +11001,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436532</v>
+        <v>436700</v>
       </c>
       <c r="R105" t="n">
-        <v>6785994</v>
+        <v>6785944</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11087,10 +11087,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058406</v>
+        <v>129058366</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11098,21 +11098,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436222</v>
+        <v>436357</v>
       </c>
       <c r="R106" t="n">
-        <v>6786238</v>
+        <v>6786208</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11184,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058366</v>
+        <v>129058393</v>
       </c>
       <c r="B107" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11195,21 +11195,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11219,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436357</v>
+        <v>436507</v>
       </c>
       <c r="R107" t="n">
-        <v>6786208</v>
+        <v>6786023</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11281,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058393</v>
+        <v>129058358</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11292,21 +11292,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436507</v>
+        <v>436550</v>
       </c>
       <c r="R108" t="n">
-        <v>6786023</v>
+        <v>6785988</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11378,10 +11378,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058358</v>
+        <v>129058406</v>
       </c>
       <c r="B109" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11389,21 +11389,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436550</v>
+        <v>436222</v>
       </c>
       <c r="R109" t="n">
-        <v>6785988</v>
+        <v>6786238</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11687,54 +11687,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058328</v>
+        <v>129058368</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436701</v>
+        <v>436257</v>
       </c>
       <c r="R112" t="n">
-        <v>6785838</v>
+        <v>6786288</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11775,7 +11766,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11794,45 +11784,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058368</v>
+        <v>129058328</v>
       </c>
       <c r="B113" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436257</v>
+        <v>436701</v>
       </c>
       <c r="R113" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11873,6 +11872,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129080278</v>
+        <v>129080292</v>
       </c>
       <c r="B116" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,21 +12105,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436513</v>
+        <v>436532</v>
       </c>
       <c r="R116" t="n">
-        <v>6785962</v>
+        <v>6785865</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12191,10 +12191,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080329</v>
+        <v>129080278</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12202,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436247</v>
+        <v>436513</v>
       </c>
       <c r="R117" t="n">
-        <v>6786289</v>
+        <v>6785962</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,11 +12262,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12293,10 +12288,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080323</v>
+        <v>129080329</v>
       </c>
       <c r="B118" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12304,21 +12299,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12328,10 +12323,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436382</v>
+        <v>436247</v>
       </c>
       <c r="R118" t="n">
-        <v>6786202</v>
+        <v>6786289</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,6 +12359,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12390,10 +12390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129080292</v>
+        <v>129080323</v>
       </c>
       <c r="B119" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,21 +12401,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436532</v>
+        <v>436382</v>
       </c>
       <c r="R119" t="n">
-        <v>6785865</v>
+        <v>6786202</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080277</v>
+        <v>129080302</v>
       </c>
       <c r="B120" t="n">
-        <v>79654</v>
+        <v>91546</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436561</v>
+        <v>436320</v>
       </c>
       <c r="R120" t="n">
-        <v>6785959</v>
+        <v>6786132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,6 +12566,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12584,10 +12585,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080302</v>
+        <v>129080277</v>
       </c>
       <c r="B121" t="n">
-        <v>91546</v>
+        <v>79654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,21 +12596,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12619,10 +12620,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436320</v>
+        <v>436561</v>
       </c>
       <c r="R121" t="n">
-        <v>6786132</v>
+        <v>6785959</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,7 +12664,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12779,7 +12779,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080294</v>
+        <v>129080291</v>
       </c>
       <c r="B123" t="n">
         <v>78793</v>
@@ -12814,10 +12814,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436659</v>
+        <v>436524</v>
       </c>
       <c r="R123" t="n">
-        <v>6785808</v>
+        <v>6785865</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080291</v>
+        <v>129080294</v>
       </c>
       <c r="B124" t="n">
         <v>78793</v>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436524</v>
+        <v>436659</v>
       </c>
       <c r="R124" t="n">
-        <v>6785865</v>
+        <v>6785808</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080328</v>
+        <v>129080298</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436438</v>
+        <v>436428</v>
       </c>
       <c r="R128" t="n">
-        <v>6786185</v>
+        <v>6786194</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,7 +13361,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080298</v>
+        <v>129080290</v>
       </c>
       <c r="B129" t="n">
         <v>78793</v>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436428</v>
+        <v>436545</v>
       </c>
       <c r="R129" t="n">
-        <v>6786194</v>
+        <v>6785882</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B130" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R130" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14816,45 +14816,54 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080299</v>
+        <v>129080312</v>
       </c>
       <c r="B144" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436384</v>
+        <v>436296</v>
       </c>
       <c r="R144" t="n">
-        <v>6786203</v>
+        <v>6786185</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14895,6 +14904,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15010,54 +15020,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080312</v>
+        <v>129080299</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436296</v>
+        <v>436384</v>
       </c>
       <c r="R146" t="n">
-        <v>6786185</v>
+        <v>6786203</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15098,7 +15099,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15117,10 +15117,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129080315</v>
+        <v>129080280</v>
       </c>
       <c r="B147" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15128,21 +15128,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15152,10 +15152,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>436523</v>
+        <v>436461</v>
       </c>
       <c r="R147" t="n">
-        <v>6785864</v>
+        <v>6786160</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15214,10 +15214,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129080280</v>
+        <v>129080315</v>
       </c>
       <c r="B148" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15225,21 +15225,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>436461</v>
+        <v>436523</v>
       </c>
       <c r="R148" t="n">
-        <v>6786160</v>
+        <v>6785864</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080297</v>
+        <v>129080283</v>
       </c>
       <c r="B149" t="n">
-        <v>78793</v>
+        <v>91526</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436449</v>
+        <v>436434</v>
       </c>
       <c r="R149" t="n">
-        <v>6786210</v>
+        <v>6786112</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15384,12 +15384,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15506,10 +15512,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080283</v>
+        <v>129080282</v>
       </c>
       <c r="B151" t="n">
-        <v>91526</v>
+        <v>79654</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15517,21 +15523,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15541,10 +15547,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436434</v>
+        <v>436335</v>
       </c>
       <c r="R151" t="n">
-        <v>6786112</v>
+        <v>6786163</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15579,18 +15585,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15609,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080282</v>
+        <v>129080297</v>
       </c>
       <c r="B152" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436335</v>
+        <v>436449</v>
       </c>
       <c r="R152" t="n">
-        <v>6786163</v>
+        <v>6786210</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16441,7 +16441,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080311</v>
+        <v>129080310</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16485,10 +16485,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436449</v>
+        <v>436472</v>
       </c>
       <c r="R160" t="n">
-        <v>6786212</v>
+        <v>6786160</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16655,7 +16655,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080310</v>
+        <v>129080311</v>
       </c>
       <c r="B162" t="n">
         <v>8450</v>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436472</v>
+        <v>436449</v>
       </c>
       <c r="R162" t="n">
-        <v>6786160</v>
+        <v>6786212</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16762,41 +16762,40 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080308</v>
+        <v>129080286</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16806,10 +16805,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436807</v>
+        <v>436572</v>
       </c>
       <c r="R163" t="n">
-        <v>6785797</v>
+        <v>6785762</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16850,7 +16849,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16869,40 +16867,41 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080286</v>
+        <v>129080309</v>
       </c>
       <c r="B164" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -16912,10 +16911,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436572</v>
+        <v>436571</v>
       </c>
       <c r="R164" t="n">
-        <v>6785762</v>
+        <v>6785936</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16956,6 +16955,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -16974,7 +16974,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080309</v>
+        <v>129080308</v>
       </c>
       <c r="B165" t="n">
         <v>8450</v>
@@ -17018,10 +17018,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436571</v>
+        <v>436807</v>
       </c>
       <c r="R165" t="n">
-        <v>6785936</v>
+        <v>6785797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058412</v>
+        <v>129058274</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436564</v>
+        <v>436522</v>
       </c>
       <c r="R2" t="n">
-        <v>6785776</v>
+        <v>6786062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058274</v>
+        <v>129058412</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436522</v>
+        <v>436564</v>
       </c>
       <c r="R3" t="n">
-        <v>6786062</v>
+        <v>6785776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058331</v>
+        <v>129058299</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436755</v>
+        <v>436545</v>
       </c>
       <c r="R4" t="n">
-        <v>6785905</v>
+        <v>6785800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058341</v>
+        <v>129058303</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436278</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6786206</v>
+        <v>6785831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,45 +1063,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058299</v>
+        <v>129058331</v>
       </c>
       <c r="B6" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436545</v>
+        <v>436755</v>
       </c>
       <c r="R6" t="n">
-        <v>6785800</v>
+        <v>6785905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,45 +1170,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058303</v>
+        <v>129058341</v>
       </c>
       <c r="B7" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436818</v>
+        <v>436278</v>
       </c>
       <c r="R7" t="n">
-        <v>6785831</v>
+        <v>6786206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058336</v>
+        <v>129058337</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1311,7 +1311,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436336</v>
+        <v>436322</v>
       </c>
       <c r="R8" t="n">
-        <v>6786183</v>
+        <v>6786198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058337</v>
+        <v>129058336</v>
       </c>
       <c r="B10" t="n">
         <v>8450</v>
@@ -1525,7 +1525,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436322</v>
+        <v>436336</v>
       </c>
       <c r="R10" t="n">
-        <v>6786198</v>
+        <v>6786183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058304</v>
+        <v>129058384</v>
       </c>
       <c r="B11" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436683</v>
+        <v>436265</v>
       </c>
       <c r="R11" t="n">
-        <v>6785939</v>
+        <v>6786123</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058321</v>
+        <v>129058350</v>
       </c>
       <c r="B12" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436377</v>
+        <v>436465</v>
       </c>
       <c r="R12" t="n">
-        <v>6786201</v>
+        <v>6785855</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058350</v>
+        <v>129058415</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436465</v>
+        <v>436527</v>
       </c>
       <c r="R13" t="n">
-        <v>6785855</v>
+        <v>6785990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,12 +1868,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1889,10 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058384</v>
+        <v>129058304</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,21 +1909,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436265</v>
+        <v>436683</v>
       </c>
       <c r="R14" t="n">
-        <v>6786123</v>
+        <v>6785939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,10 +1995,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129058415</v>
+        <v>129058321</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,37 +2006,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436527</v>
+        <v>436377</v>
       </c>
       <c r="R15" t="n">
-        <v>6785990</v>
+        <v>6786201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,18 +2068,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>129058382</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058365</v>
+        <v>129058403</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436467</v>
+        <v>436259</v>
       </c>
       <c r="R17" t="n">
-        <v>6786236</v>
+        <v>6786285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,54 +2286,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058332</v>
+        <v>129058365</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436648</v>
+        <v>436467</v>
       </c>
       <c r="R18" t="n">
-        <v>6785874</v>
+        <v>6786236</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,7 +2365,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2393,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058301</v>
+        <v>129058286</v>
       </c>
       <c r="B19" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2404,34 +2394,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436796</v>
+        <v>436617</v>
       </c>
       <c r="R19" t="n">
-        <v>6785778</v>
+        <v>6785749</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,37 +2488,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058317</v>
+        <v>129058332</v>
       </c>
       <c r="B20" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2528,10 +2532,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436356</v>
+        <v>436648</v>
       </c>
       <c r="R20" t="n">
-        <v>6786224</v>
+        <v>6785874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,10 +2595,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058307</v>
+        <v>129058301</v>
       </c>
       <c r="B21" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436597</v>
+        <v>436796</v>
       </c>
       <c r="R21" t="n">
-        <v>6785981</v>
+        <v>6785778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,10 +2692,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058308</v>
+        <v>129058317</v>
       </c>
       <c r="B22" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,16 +2721,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436545</v>
+        <v>436356</v>
       </c>
       <c r="R22" t="n">
-        <v>6785997</v>
+        <v>6786224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2767,6 +2774,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2785,10 +2793,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058280</v>
+        <v>129058307</v>
       </c>
       <c r="B23" t="n">
-        <v>79625</v>
+        <v>78797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2796,21 +2804,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2820,10 +2828,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436519</v>
+        <v>436597</v>
       </c>
       <c r="R23" t="n">
-        <v>6785988</v>
+        <v>6785981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,10 +2890,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058403</v>
+        <v>129058308</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,21 +2901,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2917,10 +2925,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436259</v>
+        <v>436545</v>
       </c>
       <c r="R24" t="n">
-        <v>6786285</v>
+        <v>6785997</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,10 +2987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058286</v>
+        <v>129058280</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2990,42 +2998,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436617</v>
+        <v>436519</v>
       </c>
       <c r="R25" t="n">
-        <v>6785749</v>
+        <v>6785988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
         <v>129058311</v>
       </c>
       <c r="B28" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>129058272</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>129058287</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>129058273</v>
       </c>
       <c r="B31" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>129058369</v>
       </c>
       <c r="B32" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058319</v>
+        <v>129058288</v>
       </c>
       <c r="B33" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3810,26 +3810,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3837,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436378</v>
+        <v>436458</v>
       </c>
       <c r="R33" t="n">
-        <v>6786219</v>
+        <v>6786194</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,7 +3886,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3900,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058288</v>
+        <v>129058319</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,31 +3915,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3943,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436458</v>
+        <v>436378</v>
       </c>
       <c r="R34" t="n">
-        <v>6786194</v>
+        <v>6786219</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,6 +3986,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>129058262</v>
       </c>
       <c r="B35" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>129058269</v>
       </c>
       <c r="B36" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>129058277</v>
       </c>
       <c r="B37" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058348</v>
+        <v>129058404</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4311,21 +4311,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436266</v>
+        <v>436229</v>
       </c>
       <c r="R38" t="n">
-        <v>6786145</v>
+        <v>6786238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,10 +4397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058278</v>
+        <v>129058348</v>
       </c>
       <c r="B39" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4408,21 +4408,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436295</v>
+        <v>436266</v>
       </c>
       <c r="R39" t="n">
-        <v>6786172</v>
+        <v>6786145</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058404</v>
+        <v>129058357</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436229</v>
+        <v>436686</v>
       </c>
       <c r="R40" t="n">
-        <v>6786238</v>
+        <v>6785940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,54 +4591,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058325</v>
+        <v>129058278</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436443</v>
+        <v>436295</v>
       </c>
       <c r="R41" t="n">
-        <v>6785940</v>
+        <v>6786172</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4679,7 +4670,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4698,37 +4688,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058318</v>
+        <v>129058325</v>
       </c>
       <c r="B42" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4736,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436354</v>
+        <v>436443</v>
       </c>
       <c r="R42" t="n">
-        <v>6786212</v>
+        <v>6785940</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,10 +4795,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058357</v>
+        <v>129058318</v>
       </c>
       <c r="B43" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4810,34 +4806,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436686</v>
+        <v>436354</v>
       </c>
       <c r="R43" t="n">
-        <v>6785940</v>
+        <v>6786212</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4878,6 +4877,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>129058276</v>
       </c>
       <c r="B44" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129058297</v>
+        <v>129058351</v>
       </c>
       <c r="B45" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436509</v>
+        <v>436516</v>
       </c>
       <c r="R45" t="n">
         <v>6785859</v>
@@ -5090,10 +5090,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129058313</v>
+        <v>129058297</v>
       </c>
       <c r="B46" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436504</v>
+        <v>436509</v>
       </c>
       <c r="R46" t="n">
-        <v>6786023</v>
+        <v>6785859</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129058351</v>
+        <v>129058313</v>
       </c>
       <c r="B47" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436516</v>
+        <v>436504</v>
       </c>
       <c r="R47" t="n">
-        <v>6785859</v>
+        <v>6786023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058309</v>
+        <v>129058385</v>
       </c>
       <c r="B48" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436532</v>
+        <v>436327</v>
       </c>
       <c r="R48" t="n">
-        <v>6785994</v>
+        <v>6786086</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058385</v>
+        <v>129058268</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R49" t="n">
-        <v>6786086</v>
+        <v>6786023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058395</v>
+        <v>129058386</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436504</v>
+        <v>436505</v>
       </c>
       <c r="R50" t="n">
-        <v>6786102</v>
+        <v>6785856</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058386</v>
+        <v>129058290</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,34 +5586,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436505</v>
+        <v>436601</v>
       </c>
       <c r="R51" t="n">
-        <v>6785856</v>
+        <v>6785947</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058268</v>
+        <v>129058395</v>
       </c>
       <c r="B52" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,21 +5691,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5710,7 +5718,7 @@
         <v>436504</v>
       </c>
       <c r="R52" t="n">
-        <v>6786023</v>
+        <v>6786102</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5769,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058290</v>
+        <v>129058309</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5780,42 +5788,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436601</v>
+        <v>436532</v>
       </c>
       <c r="R53" t="n">
-        <v>6785947</v>
+        <v>6785994</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129058396</v>
+        <v>129058402</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,16 +5903,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436491</v>
+        <v>436264</v>
       </c>
       <c r="R54" t="n">
-        <v>6786189</v>
+        <v>6786282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5947,12 +5950,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5971,10 +5980,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058402</v>
+        <v>129058396</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6000,19 +6009,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436264</v>
+        <v>436491</v>
       </c>
       <c r="R55" t="n">
-        <v>6786282</v>
+        <v>6786189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6047,18 +6053,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>129058392</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>129058391</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>129058399</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>129058279</v>
       </c>
       <c r="B59" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129058306</v>
       </c>
       <c r="B60" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058389</v>
+        <v>129058361</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,37 +6608,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436739</v>
+        <v>436500</v>
       </c>
       <c r="R61" t="n">
-        <v>6785902</v>
+        <v>6786018</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,18 +6670,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6703,10 +6694,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058405</v>
+        <v>129058389</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6732,16 +6723,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436227</v>
+        <v>436739</v>
       </c>
       <c r="R62" t="n">
-        <v>6786243</v>
+        <v>6785902</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6776,12 +6770,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058353</v>
+        <v>129058405</v>
       </c>
       <c r="B63" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6811,21 +6811,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436551</v>
+        <v>436227</v>
       </c>
       <c r="R63" t="n">
-        <v>6785765</v>
+        <v>6786243</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058361</v>
+        <v>129058353</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436500</v>
+        <v>436551</v>
       </c>
       <c r="R64" t="n">
-        <v>6786018</v>
+        <v>6785765</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6997,7 +6997,7 @@
         <v>129058271</v>
       </c>
       <c r="B65" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>129058291</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058335</v>
+        <v>129058323</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436360</v>
+        <v>436241</v>
       </c>
       <c r="R67" t="n">
-        <v>6786231</v>
+        <v>6786159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058340</v>
+        <v>129058330</v>
       </c>
       <c r="B68" t="n">
         <v>8450</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436324</v>
+        <v>436823</v>
       </c>
       <c r="R68" t="n">
-        <v>6786220</v>
+        <v>6785756</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058330</v>
+        <v>129058340</v>
       </c>
       <c r="B69" t="n">
         <v>8450</v>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436823</v>
+        <v>436324</v>
       </c>
       <c r="R69" t="n">
-        <v>6785756</v>
+        <v>6786220</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058323</v>
+        <v>129058335</v>
       </c>
       <c r="B70" t="n">
         <v>8450</v>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436241</v>
+        <v>436360</v>
       </c>
       <c r="R70" t="n">
-        <v>6786159</v>
+        <v>6786231</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7624,37 +7624,43 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058305</v>
+        <v>129058334</v>
       </c>
       <c r="B71" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7662,10 +7668,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436680</v>
+        <v>436373</v>
       </c>
       <c r="R71" t="n">
-        <v>6785902</v>
+        <v>6786190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7725,43 +7731,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058334</v>
+        <v>129058305</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436373</v>
+        <v>436680</v>
       </c>
       <c r="R72" t="n">
-        <v>6786190</v>
+        <v>6785902</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058354</v>
+        <v>129058267</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,21 +7843,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436796</v>
+        <v>436524</v>
       </c>
       <c r="R73" t="n">
-        <v>6785778</v>
+        <v>6785977</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058359</v>
+        <v>129058362</v>
       </c>
       <c r="B74" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436532</v>
+        <v>436494</v>
       </c>
       <c r="R74" t="n">
-        <v>6785994</v>
+        <v>6786028</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058367</v>
+        <v>129058264</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,21 +8037,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436371</v>
+        <v>436599</v>
       </c>
       <c r="R75" t="n">
-        <v>6786199</v>
+        <v>6785738</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058267</v>
+        <v>129058354</v>
       </c>
       <c r="B76" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8134,21 +8134,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436524</v>
+        <v>436796</v>
       </c>
       <c r="R76" t="n">
-        <v>6785977</v>
+        <v>6785778</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,10 +8220,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058362</v>
+        <v>129058359</v>
       </c>
       <c r="B77" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436494</v>
+        <v>436532</v>
       </c>
       <c r="R77" t="n">
-        <v>6786028</v>
+        <v>6785994</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058264</v>
+        <v>129058367</v>
       </c>
       <c r="B78" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436599</v>
+        <v>436371</v>
       </c>
       <c r="R78" t="n">
-        <v>6785738</v>
+        <v>6786199</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8417,7 +8417,7 @@
         <v>129058355</v>
       </c>
       <c r="B79" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8515,10 +8515,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058356</v>
+        <v>129058394</v>
       </c>
       <c r="B80" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,21 +8526,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8550,10 +8550,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436818</v>
+        <v>436493</v>
       </c>
       <c r="R80" t="n">
-        <v>6785831</v>
+        <v>6786075</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058394</v>
+        <v>129058356</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,21 +8623,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436493</v>
+        <v>436818</v>
       </c>
       <c r="R81" t="n">
-        <v>6786075</v>
+        <v>6785831</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058282</v>
+        <v>129058315</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>78797</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,42 +8720,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436515</v>
+        <v>436445</v>
       </c>
       <c r="R82" t="n">
-        <v>6786055</v>
+        <v>6786210</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8814,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058315</v>
+        <v>129058282</v>
       </c>
       <c r="B83" t="n">
-        <v>78793</v>
+        <v>57725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8825,34 +8817,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436445</v>
+        <v>436515</v>
       </c>
       <c r="R83" t="n">
-        <v>6786210</v>
+        <v>6786055</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8914,7 +8914,7 @@
         <v>129058352</v>
       </c>
       <c r="B84" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9008,10 +9008,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129058414</v>
+        <v>129058263</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9019,37 +9019,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436671</v>
+        <v>436559</v>
       </c>
       <c r="R85" t="n">
-        <v>6785810</v>
+        <v>6785783</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9084,18 +9081,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9114,10 +9105,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129058397</v>
+        <v>129058414</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9152,10 +9143,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436446</v>
+        <v>436671</v>
       </c>
       <c r="R86" t="n">
-        <v>6786249</v>
+        <v>6785810</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9188,6 +9179,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9215,10 +9211,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058383</v>
+        <v>129058397</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9244,16 +9240,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436263</v>
+        <v>436446</v>
       </c>
       <c r="R87" t="n">
-        <v>6786145</v>
+        <v>6786249</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9294,6 +9293,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129058302</v>
+        <v>129058383</v>
       </c>
       <c r="B88" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9323,21 +9323,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436825</v>
+        <v>436263</v>
       </c>
       <c r="R88" t="n">
-        <v>6785764</v>
+        <v>6786145</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129058263</v>
+        <v>129058302</v>
       </c>
       <c r="B89" t="n">
-        <v>79654</v>
+        <v>78797</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9420,21 +9420,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436559</v>
+        <v>436825</v>
       </c>
       <c r="R89" t="n">
-        <v>6785783</v>
+        <v>6785764</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9509,7 +9509,7 @@
         <v>129058411</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058387</v>
+        <v>129058398</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436805</v>
+        <v>436425</v>
       </c>
       <c r="R91" t="n">
-        <v>6785785</v>
+        <v>6786210</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058398</v>
+        <v>129058387</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436425</v>
+        <v>436805</v>
       </c>
       <c r="R92" t="n">
-        <v>6786210</v>
+        <v>6785785</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9800,7 +9800,7 @@
         <v>129058346</v>
       </c>
       <c r="B93" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>129058314</v>
       </c>
       <c r="B94" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9991,45 +9991,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058407</v>
+        <v>129058333</v>
       </c>
       <c r="B95" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436215</v>
+        <v>436432</v>
       </c>
       <c r="R95" t="n">
-        <v>6786222</v>
+        <v>6786210</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,6 +10079,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10088,37 +10098,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058416</v>
+        <v>129058345</v>
       </c>
       <c r="B96" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10126,10 +10142,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436491</v>
+        <v>436269</v>
       </c>
       <c r="R96" t="n">
-        <v>6786146</v>
+        <v>6786257</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10162,11 +10178,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10194,54 +10205,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058345</v>
+        <v>129058407</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436269</v>
+        <v>436215</v>
       </c>
       <c r="R97" t="n">
-        <v>6786257</v>
+        <v>6786222</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10282,7 +10284,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10301,43 +10302,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058333</v>
+        <v>129058416</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10345,10 +10340,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436432</v>
+        <v>436491</v>
       </c>
       <c r="R98" t="n">
-        <v>6786210</v>
+        <v>6786146</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10381,6 +10376,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10411,7 +10411,7 @@
         <v>129058298</v>
       </c>
       <c r="B99" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>129058417</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>129058364</v>
       </c>
       <c r="B102" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058266</v>
+        <v>129058401</v>
       </c>
       <c r="B103" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436532</v>
+        <v>436310</v>
       </c>
       <c r="R103" t="n">
-        <v>6785994</v>
+        <v>6786196</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058401</v>
+        <v>129058390</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436310</v>
+        <v>436700</v>
       </c>
       <c r="R104" t="n">
-        <v>6786196</v>
+        <v>6785944</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10990,10 +10990,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129058390</v>
+        <v>129058266</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11001,21 +11001,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436700</v>
+        <v>436532</v>
       </c>
       <c r="R105" t="n">
-        <v>6785944</v>
+        <v>6785994</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11087,10 +11087,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058366</v>
+        <v>129058406</v>
       </c>
       <c r="B106" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11098,21 +11098,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436357</v>
+        <v>436222</v>
       </c>
       <c r="R106" t="n">
-        <v>6786208</v>
+        <v>6786238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11184,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058393</v>
+        <v>129058366</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11195,21 +11195,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11219,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436507</v>
+        <v>436357</v>
       </c>
       <c r="R107" t="n">
-        <v>6786023</v>
+        <v>6786208</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11281,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058358</v>
+        <v>129058393</v>
       </c>
       <c r="B108" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11292,21 +11292,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436550</v>
+        <v>436507</v>
       </c>
       <c r="R108" t="n">
-        <v>6785988</v>
+        <v>6786023</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11378,10 +11378,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058406</v>
+        <v>129058358</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11389,21 +11389,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11413,10 +11413,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436222</v>
+        <v>436550</v>
       </c>
       <c r="R109" t="n">
-        <v>6786238</v>
+        <v>6785988</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058289</v>
+        <v>129058368</v>
       </c>
       <c r="B111" t="n">
-        <v>57720</v>
+        <v>78796</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11593,42 +11593,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436486</v>
+        <v>436257</v>
       </c>
       <c r="R111" t="n">
-        <v>6786231</v>
+        <v>6786288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11687,10 +11679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058368</v>
+        <v>129058289</v>
       </c>
       <c r="B112" t="n">
-        <v>78792</v>
+        <v>57722</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11698,34 +11690,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436257</v>
+        <v>436486</v>
       </c>
       <c r="R112" t="n">
-        <v>6786288</v>
+        <v>6786231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11894,7 +11894,7 @@
         <v>129058270</v>
       </c>
       <c r="B114" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>129058388</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129080292</v>
+        <v>129080278</v>
       </c>
       <c r="B116" t="n">
-        <v>78793</v>
+        <v>79658</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,21 +12105,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436532</v>
+        <v>436513</v>
       </c>
       <c r="R116" t="n">
-        <v>6785865</v>
+        <v>6785962</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12191,10 +12191,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080278</v>
+        <v>129080329</v>
       </c>
       <c r="B117" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12202,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436513</v>
+        <v>436247</v>
       </c>
       <c r="R117" t="n">
-        <v>6785962</v>
+        <v>6786289</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,6 +12262,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12288,10 +12293,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080329</v>
+        <v>129080323</v>
       </c>
       <c r="B118" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12299,21 +12304,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12323,10 +12328,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436247</v>
+        <v>436382</v>
       </c>
       <c r="R118" t="n">
-        <v>6786289</v>
+        <v>6786202</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,11 +12364,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12390,10 +12390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129080323</v>
+        <v>129080292</v>
       </c>
       <c r="B119" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,21 +12401,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436382</v>
+        <v>436532</v>
       </c>
       <c r="R119" t="n">
-        <v>6786202</v>
+        <v>6785865</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12490,7 +12490,7 @@
         <v>129080302</v>
       </c>
       <c r="B120" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>129080277</v>
       </c>
       <c r="B121" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>129080295</v>
       </c>
       <c r="B122" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>129080291</v>
       </c>
       <c r="B123" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>129080294</v>
       </c>
       <c r="B124" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B125" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R125" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,10 +13070,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B126" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R126" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13170,7 +13170,7 @@
         <v>129080281</v>
       </c>
       <c r="B127" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080298</v>
+        <v>129080328</v>
       </c>
       <c r="B128" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436428</v>
+        <v>436438</v>
       </c>
       <c r="R128" t="n">
-        <v>6786194</v>
+        <v>6786185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080290</v>
+        <v>129080298</v>
       </c>
       <c r="B129" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436545</v>
+        <v>436428</v>
       </c>
       <c r="R129" t="n">
-        <v>6785882</v>
+        <v>6786194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R130" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B131" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R131" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B132" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R132" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13752,7 +13752,7 @@
         <v>129080318</v>
       </c>
       <c r="B133" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>129080279</v>
       </c>
       <c r="B134" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>129080301</v>
       </c>
       <c r="B135" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129080317</v>
+        <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>78792</v>
+        <v>91553</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>436816</v>
+        <v>436494</v>
       </c>
       <c r="R136" t="n">
-        <v>6785768</v>
+        <v>6785930</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14137,10 +14137,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080316</v>
+        <v>129080317</v>
       </c>
       <c r="B137" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436532</v>
+        <v>436816</v>
       </c>
       <c r="R137" t="n">
-        <v>6785867</v>
+        <v>6785768</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,10 +14234,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080284</v>
+        <v>129080316</v>
       </c>
       <c r="B138" t="n">
-        <v>91546</v>
+        <v>78796</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436494</v>
+        <v>436532</v>
       </c>
       <c r="R138" t="n">
-        <v>6785930</v>
+        <v>6785867</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14334,7 +14334,7 @@
         <v>129080314</v>
       </c>
       <c r="B139" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129080293</v>
       </c>
       <c r="B140" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>129080319</v>
       </c>
       <c r="B141" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>129080324</v>
       </c>
       <c r="B142" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14719,45 +14719,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080327</v>
+        <v>129080312</v>
       </c>
       <c r="B143" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436653</v>
+        <v>436296</v>
       </c>
       <c r="R143" t="n">
-        <v>6785861</v>
+        <v>6786185</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14798,6 +14807,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14816,54 +14826,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080312</v>
+        <v>129080327</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436296</v>
+        <v>436653</v>
       </c>
       <c r="R144" t="n">
-        <v>6786185</v>
+        <v>6785861</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14904,7 +14905,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -14926,7 +14926,7 @@
         <v>129080300</v>
       </c>
       <c r="B145" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>129080299</v>
       </c>
       <c r="B146" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15117,10 +15117,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129080280</v>
+        <v>129080315</v>
       </c>
       <c r="B147" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15128,21 +15128,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15152,10 +15152,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>436461</v>
+        <v>436523</v>
       </c>
       <c r="R147" t="n">
-        <v>6786160</v>
+        <v>6785864</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15214,10 +15214,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129080315</v>
+        <v>129080280</v>
       </c>
       <c r="B148" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15225,21 +15225,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>436523</v>
+        <v>436461</v>
       </c>
       <c r="R148" t="n">
-        <v>6785864</v>
+        <v>6786160</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080283</v>
+        <v>129080282</v>
       </c>
       <c r="B149" t="n">
-        <v>91526</v>
+        <v>79658</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436434</v>
+        <v>436335</v>
       </c>
       <c r="R149" t="n">
-        <v>6786112</v>
+        <v>6786163</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15384,18 +15384,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15417,7 +15411,7 @@
         <v>129080331</v>
       </c>
       <c r="B150" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15512,10 +15506,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080282</v>
+        <v>129080283</v>
       </c>
       <c r="B151" t="n">
-        <v>79654</v>
+        <v>91533</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15523,21 +15517,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15547,10 +15541,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436335</v>
+        <v>436434</v>
       </c>
       <c r="R151" t="n">
-        <v>6786163</v>
+        <v>6786112</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15585,12 +15579,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15612,7 +15612,7 @@
         <v>129080297</v>
       </c>
       <c r="B152" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>129080320</v>
       </c>
       <c r="B153" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>129080288</v>
       </c>
       <c r="B155" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16336,40 +16336,41 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080287</v>
+        <v>129080311</v>
       </c>
       <c r="B159" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16379,10 +16380,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436471</v>
+        <v>436449</v>
       </c>
       <c r="R159" t="n">
-        <v>6786165</v>
+        <v>6786212</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16423,6 +16424,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16441,7 +16443,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080310</v>
+        <v>129080305</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16485,10 +16487,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436472</v>
+        <v>436474</v>
       </c>
       <c r="R160" t="n">
-        <v>6786160</v>
+        <v>6785946</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16548,7 +16550,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129080305</v>
+        <v>129080310</v>
       </c>
       <c r="B161" t="n">
         <v>8450</v>
@@ -16592,10 +16594,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>436474</v>
+        <v>436472</v>
       </c>
       <c r="R161" t="n">
-        <v>6785946</v>
+        <v>6786160</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16655,41 +16657,40 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080311</v>
+        <v>129080287</v>
       </c>
       <c r="B162" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16699,10 +16700,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436449</v>
+        <v>436471</v>
       </c>
       <c r="R162" t="n">
-        <v>6786212</v>
+        <v>6786165</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16743,7 +16744,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -16762,40 +16762,41 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080286</v>
+        <v>129080309</v>
       </c>
       <c r="B163" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16805,10 +16806,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436572</v>
+        <v>436571</v>
       </c>
       <c r="R163" t="n">
-        <v>6785762</v>
+        <v>6785936</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16849,6 +16850,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16867,7 +16869,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080309</v>
+        <v>129080308</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16911,10 +16913,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436571</v>
+        <v>436807</v>
       </c>
       <c r="R164" t="n">
-        <v>6785936</v>
+        <v>6785797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16974,41 +16976,40 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080308</v>
+        <v>129080286</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17018,10 +17019,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436807</v>
+        <v>436572</v>
       </c>
       <c r="R165" t="n">
-        <v>6785797</v>
+        <v>6785762</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17062,7 +17063,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17084,7 +17084,7 @@
         <v>129080285</v>
       </c>
       <c r="B166" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -1277,54 +1277,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058337</v>
+        <v>129058384</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436322</v>
+        <v>436265</v>
       </c>
       <c r="R8" t="n">
-        <v>6786198</v>
+        <v>6786123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,54 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058329</v>
+        <v>129058350</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436754</v>
+        <v>436465</v>
       </c>
       <c r="R9" t="n">
-        <v>6785822</v>
+        <v>6785855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,43 +1471,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058336</v>
+        <v>129058415</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436336</v>
+        <v>436527</v>
       </c>
       <c r="R10" t="n">
-        <v>6786183</v>
+        <v>6785990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1545,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,45 +1577,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058384</v>
+        <v>129058337</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436265</v>
+        <v>436322</v>
       </c>
       <c r="R11" t="n">
-        <v>6786123</v>
+        <v>6786198</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1695,45 +1684,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058350</v>
+        <v>129058329</v>
       </c>
       <c r="B12" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436465</v>
+        <v>436754</v>
       </c>
       <c r="R12" t="n">
-        <v>6785855</v>
+        <v>6785822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,6 +1772,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1792,37 +1791,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058415</v>
+        <v>129058336</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1830,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436527</v>
+        <v>436336</v>
       </c>
       <c r="R13" t="n">
-        <v>6785990</v>
+        <v>6786183</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,11 +1871,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058273</v>
+        <v>129058288</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>57722</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,26 +3612,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3639,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436257</v>
+        <v>436458</v>
       </c>
       <c r="R31" t="n">
-        <v>6786288</v>
+        <v>6786194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3688,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3702,10 +3706,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058369</v>
+        <v>129058319</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,34 +3717,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436817</v>
+        <v>436378</v>
       </c>
       <c r="R32" t="n">
-        <v>6785838</v>
+        <v>6786219</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3781,6 +3788,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3799,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058288</v>
+        <v>129058273</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3810,31 +3818,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3842,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436458</v>
+        <v>436257</v>
       </c>
       <c r="R33" t="n">
-        <v>6786194</v>
+        <v>6786288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,6 +3889,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3904,10 +3908,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058319</v>
+        <v>129058369</v>
       </c>
       <c r="B34" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,37 +3919,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436378</v>
+        <v>436817</v>
       </c>
       <c r="R34" t="n">
-        <v>6786219</v>
+        <v>6785838</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,7 +3987,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -7624,54 +7624,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058334</v>
+        <v>129058267</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436373</v>
+        <v>436524</v>
       </c>
       <c r="R71" t="n">
-        <v>6786190</v>
+        <v>6785977</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7703,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7731,10 +7721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058305</v>
+        <v>129058362</v>
       </c>
       <c r="B72" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7742,37 +7732,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436680</v>
+        <v>436494</v>
       </c>
       <c r="R72" t="n">
-        <v>6785902</v>
+        <v>6786028</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7813,7 +7800,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7832,7 +7818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058267</v>
+        <v>129058264</v>
       </c>
       <c r="B73" t="n">
         <v>79658</v>
@@ -7867,10 +7853,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436524</v>
+        <v>436599</v>
       </c>
       <c r="R73" t="n">
-        <v>6785977</v>
+        <v>6785738</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,7 +7915,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058362</v>
+        <v>129058354</v>
       </c>
       <c r="B74" t="n">
         <v>78796</v>
@@ -7964,10 +7950,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436494</v>
+        <v>436796</v>
       </c>
       <c r="R74" t="n">
-        <v>6786028</v>
+        <v>6785778</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8026,10 +8012,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058264</v>
+        <v>129058359</v>
       </c>
       <c r="B75" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,21 +8023,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8047,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436599</v>
+        <v>436532</v>
       </c>
       <c r="R75" t="n">
-        <v>6785738</v>
+        <v>6785994</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,7 +8109,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058354</v>
+        <v>129058367</v>
       </c>
       <c r="B76" t="n">
         <v>78796</v>
@@ -8158,10 +8144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436796</v>
+        <v>436371</v>
       </c>
       <c r="R76" t="n">
-        <v>6785778</v>
+        <v>6786199</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8206,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058359</v>
+        <v>129058334</v>
       </c>
       <c r="B77" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436532</v>
+        <v>436373</v>
       </c>
       <c r="R77" t="n">
-        <v>6785994</v>
+        <v>6786190</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8299,6 +8294,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8317,10 +8313,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058367</v>
+        <v>129058305</v>
       </c>
       <c r="B78" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,34 +8324,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436371</v>
+        <v>436680</v>
       </c>
       <c r="R78" t="n">
-        <v>6786199</v>
+        <v>6785902</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8396,6 +8395,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9991,54 +9991,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058333</v>
+        <v>129058298</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436432</v>
+        <v>436513</v>
       </c>
       <c r="R95" t="n">
-        <v>6786210</v>
+        <v>6785845</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,7 +10070,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10098,54 +10088,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058345</v>
+        <v>129058300</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436269</v>
+        <v>436554</v>
       </c>
       <c r="R96" t="n">
-        <v>6786257</v>
+        <v>6785764</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10186,7 +10167,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10205,45 +10185,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058407</v>
+        <v>129058333</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436215</v>
+        <v>436432</v>
       </c>
       <c r="R97" t="n">
-        <v>6786222</v>
+        <v>6786210</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10284,6 +10273,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10302,37 +10292,43 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058416</v>
+        <v>129058345</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10340,10 +10336,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436491</v>
+        <v>436269</v>
       </c>
       <c r="R98" t="n">
-        <v>6786146</v>
+        <v>6786257</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10376,11 +10372,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10408,10 +10399,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058298</v>
+        <v>129058407</v>
       </c>
       <c r="B99" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10419,21 +10410,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10443,10 +10434,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436513</v>
+        <v>436215</v>
       </c>
       <c r="R99" t="n">
-        <v>6785845</v>
+        <v>6786222</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10505,10 +10496,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058300</v>
+        <v>129058416</v>
       </c>
       <c r="B100" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10516,34 +10507,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436554</v>
+        <v>436491</v>
       </c>
       <c r="R100" t="n">
-        <v>6785764</v>
+        <v>6786146</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10578,12 +10572,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B125" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R125" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,10 +13070,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B126" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R126" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14719,54 +14719,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080312</v>
+        <v>129080327</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436296</v>
+        <v>436653</v>
       </c>
       <c r="R143" t="n">
-        <v>6786185</v>
+        <v>6785861</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14807,7 +14798,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14826,10 +14816,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080327</v>
+        <v>129080300</v>
       </c>
       <c r="B144" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14837,21 +14827,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14861,10 +14851,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436653</v>
+        <v>436333</v>
       </c>
       <c r="R144" t="n">
-        <v>6785861</v>
+        <v>6786167</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14923,7 +14913,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129080300</v>
+        <v>129080299</v>
       </c>
       <c r="B145" t="n">
         <v>78797</v>
@@ -14958,10 +14948,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>436333</v>
+        <v>436384</v>
       </c>
       <c r="R145" t="n">
-        <v>6786167</v>
+        <v>6786203</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15020,45 +15010,54 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080299</v>
+        <v>129080312</v>
       </c>
       <c r="B146" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436384</v>
+        <v>436296</v>
       </c>
       <c r="R146" t="n">
-        <v>6786203</v>
+        <v>6786185</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15099,6 +15098,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16762,41 +16762,40 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080309</v>
+        <v>129080286</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16806,10 +16805,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436571</v>
+        <v>436572</v>
       </c>
       <c r="R163" t="n">
-        <v>6785936</v>
+        <v>6785762</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16850,7 +16849,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16869,7 +16867,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080308</v>
+        <v>129080309</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16913,10 +16911,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436807</v>
+        <v>436571</v>
       </c>
       <c r="R164" t="n">
-        <v>6785797</v>
+        <v>6785936</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16976,40 +16974,41 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080286</v>
+        <v>129080308</v>
       </c>
       <c r="B165" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17019,10 +17018,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436572</v>
+        <v>436807</v>
       </c>
       <c r="R165" t="n">
-        <v>6785762</v>
+        <v>6785797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17063,6 +17062,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -869,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058299</v>
+        <v>129058331</v>
       </c>
       <c r="B4" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436545</v>
+        <v>436755</v>
       </c>
       <c r="R4" t="n">
-        <v>6785800</v>
+        <v>6785905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +957,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,45 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058303</v>
+        <v>129058341</v>
       </c>
       <c r="B5" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>436278</v>
       </c>
       <c r="R5" t="n">
-        <v>6785831</v>
+        <v>6786206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1064,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,54 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058331</v>
+        <v>129058299</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436755</v>
+        <v>436545</v>
       </c>
       <c r="R6" t="n">
-        <v>6785905</v>
+        <v>6785800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1170,54 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058341</v>
+        <v>129058303</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436278</v>
+        <v>436818</v>
       </c>
       <c r="R7" t="n">
-        <v>6786206</v>
+        <v>6785831</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,7 +1259,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,45 +1277,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058384</v>
+        <v>129058337</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436265</v>
+        <v>436322</v>
       </c>
       <c r="R8" t="n">
-        <v>6786123</v>
+        <v>6786198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,6 +1365,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,45 +1384,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058350</v>
+        <v>129058329</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436465</v>
+        <v>436754</v>
       </c>
       <c r="R9" t="n">
-        <v>6785855</v>
+        <v>6785822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,37 +1491,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058415</v>
+        <v>129058336</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1509,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436527</v>
+        <v>436336</v>
       </c>
       <c r="R10" t="n">
-        <v>6785990</v>
+        <v>6786183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1545,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,54 +1598,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058337</v>
+        <v>129058350</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436322</v>
+        <v>436465</v>
       </c>
       <c r="R11" t="n">
-        <v>6786198</v>
+        <v>6785855</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1677,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,54 +1695,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058329</v>
+        <v>129058384</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436754</v>
+        <v>436265</v>
       </c>
       <c r="R12" t="n">
-        <v>6785822</v>
+        <v>6786123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,7 +1774,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1791,43 +1792,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058336</v>
+        <v>129058415</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1835,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436336</v>
+        <v>436527</v>
       </c>
       <c r="R13" t="n">
-        <v>6786183</v>
+        <v>6785990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,6 +1866,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058382</v>
+        <v>129058365</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,21 +2103,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436214</v>
+        <v>436467</v>
       </c>
       <c r="R16" t="n">
-        <v>6786180</v>
+        <v>6786236</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058403</v>
+        <v>129058382</v>
       </c>
       <c r="B17" t="n">
         <v>79039</v>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436259</v>
+        <v>436214</v>
       </c>
       <c r="R17" t="n">
-        <v>6786285</v>
+        <v>6786180</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058365</v>
+        <v>129058403</v>
       </c>
       <c r="B18" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436467</v>
+        <v>436259</v>
       </c>
       <c r="R18" t="n">
-        <v>6786236</v>
+        <v>6786285</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3084,41 +3084,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058343</v>
+        <v>129058287</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3128,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436269</v>
+        <v>436718</v>
       </c>
       <c r="R26" t="n">
-        <v>6786228</v>
+        <v>6785941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3172,7 +3171,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3191,43 +3189,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058327</v>
+        <v>129058272</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3235,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436674</v>
+        <v>436369</v>
       </c>
       <c r="R27" t="n">
-        <v>6785802</v>
+        <v>6786195</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,45 +3290,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058311</v>
+        <v>129058343</v>
       </c>
       <c r="B28" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436530</v>
+        <v>436269</v>
       </c>
       <c r="R28" t="n">
-        <v>6785992</v>
+        <v>6786228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3377,6 +3378,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3395,37 +3397,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058272</v>
+        <v>129058327</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3433,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436369</v>
+        <v>436674</v>
       </c>
       <c r="R29" t="n">
-        <v>6786195</v>
+        <v>6785802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3496,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058287</v>
+        <v>129058311</v>
       </c>
       <c r="B30" t="n">
-        <v>57722</v>
+        <v>78797</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3507,42 +3515,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436718</v>
+        <v>436530</v>
       </c>
       <c r="R30" t="n">
-        <v>6785941</v>
+        <v>6785992</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058288</v>
+        <v>129058273</v>
       </c>
       <c r="B31" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,31 +3612,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3644,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436458</v>
+        <v>436257</v>
       </c>
       <c r="R31" t="n">
-        <v>6786194</v>
+        <v>6786288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,6 +3683,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3706,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058319</v>
+        <v>129058369</v>
       </c>
       <c r="B32" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,37 +3713,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436378</v>
+        <v>436817</v>
       </c>
       <c r="R32" t="n">
-        <v>6786219</v>
+        <v>6785838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,7 +3781,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3807,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058273</v>
+        <v>129058319</v>
       </c>
       <c r="B33" t="n">
-        <v>79658</v>
+        <v>78797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3810,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3837,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436257</v>
+        <v>436378</v>
       </c>
       <c r="R33" t="n">
-        <v>6786288</v>
+        <v>6786219</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3908,10 +3900,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058369</v>
+        <v>129058288</v>
       </c>
       <c r="B34" t="n">
-        <v>78796</v>
+        <v>57722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3919,34 +3911,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436817</v>
+        <v>436458</v>
       </c>
       <c r="R34" t="n">
-        <v>6785838</v>
+        <v>6786194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058262</v>
+        <v>129058269</v>
       </c>
       <c r="B35" t="n">
         <v>79658</v>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436534</v>
+        <v>436483</v>
       </c>
       <c r="R35" t="n">
-        <v>6785834</v>
+        <v>6786017</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058269</v>
+        <v>129058357</v>
       </c>
       <c r="B36" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436483</v>
+        <v>436686</v>
       </c>
       <c r="R36" t="n">
-        <v>6786017</v>
+        <v>6785940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,7 +4199,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058277</v>
+        <v>129058278</v>
       </c>
       <c r="B37" t="n">
         <v>79658</v>
@@ -4228,19 +4228,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436351</v>
+        <v>436295</v>
       </c>
       <c r="R37" t="n">
-        <v>6786185</v>
+        <v>6786172</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4278,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4300,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058404</v>
+        <v>129058348</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4311,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436229</v>
+        <v>436266</v>
       </c>
       <c r="R38" t="n">
-        <v>6786238</v>
+        <v>6786145</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,10 +4393,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058348</v>
+        <v>129058277</v>
       </c>
       <c r="B39" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4408,34 +4404,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436266</v>
+        <v>436351</v>
       </c>
       <c r="R39" t="n">
-        <v>6786145</v>
+        <v>6786185</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,6 +4475,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058357</v>
+        <v>129058262</v>
       </c>
       <c r="B40" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436686</v>
+        <v>436534</v>
       </c>
       <c r="R40" t="n">
-        <v>6785940</v>
+        <v>6785834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058278</v>
+        <v>129058404</v>
       </c>
       <c r="B41" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436295</v>
+        <v>436229</v>
       </c>
       <c r="R41" t="n">
-        <v>6786172</v>
+        <v>6786238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058385</v>
+        <v>129058290</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,34 +5295,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436327</v>
+        <v>436601</v>
       </c>
       <c r="R48" t="n">
-        <v>6786086</v>
+        <v>6785947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,7 +5486,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058386</v>
+        <v>129058395</v>
       </c>
       <c r="B50" t="n">
         <v>79039</v>
@@ -5513,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436505</v>
+        <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6785856</v>
+        <v>6786102</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058290</v>
+        <v>129058385</v>
       </c>
       <c r="B51" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,42 +5594,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436601</v>
+        <v>436327</v>
       </c>
       <c r="R51" t="n">
-        <v>6785947</v>
+        <v>6786086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058395</v>
+        <v>129058386</v>
       </c>
       <c r="B52" t="n">
         <v>79039</v>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436504</v>
+        <v>436505</v>
       </c>
       <c r="R52" t="n">
-        <v>6786102</v>
+        <v>6785856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6597,45 +6597,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058361</v>
+        <v>129058323</v>
       </c>
       <c r="B61" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436500</v>
+        <v>436241</v>
       </c>
       <c r="R61" t="n">
-        <v>6786018</v>
+        <v>6786159</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6676,6 +6685,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6694,37 +6704,43 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058389</v>
+        <v>129058330</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6732,10 +6748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436739</v>
+        <v>436823</v>
       </c>
       <c r="R62" t="n">
-        <v>6785902</v>
+        <v>6785756</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6768,11 +6784,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6800,45 +6811,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058405</v>
+        <v>129058340</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436227</v>
+        <v>436324</v>
       </c>
       <c r="R63" t="n">
-        <v>6786243</v>
+        <v>6786220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6879,6 +6899,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6897,45 +6918,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058353</v>
+        <v>129058335</v>
       </c>
       <c r="B64" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436551</v>
+        <v>436360</v>
       </c>
       <c r="R64" t="n">
-        <v>6785765</v>
+        <v>6786231</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6976,6 +7006,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7091,10 +7122,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058291</v>
+        <v>129058361</v>
       </c>
       <c r="B66" t="n">
-        <v>57722</v>
+        <v>78796</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7102,42 +7133,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436214</v>
+        <v>436500</v>
       </c>
       <c r="R66" t="n">
-        <v>6786222</v>
+        <v>6786018</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7196,54 +7219,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058323</v>
+        <v>129058353</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436241</v>
+        <v>436551</v>
       </c>
       <c r="R67" t="n">
-        <v>6786159</v>
+        <v>6785765</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7284,7 +7298,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7303,43 +7316,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058330</v>
+        <v>129058389</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7347,10 +7354,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436823</v>
+        <v>436739</v>
       </c>
       <c r="R68" t="n">
-        <v>6785756</v>
+        <v>6785902</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7383,6 +7390,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7410,54 +7422,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058340</v>
+        <v>129058405</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436324</v>
+        <v>436227</v>
       </c>
       <c r="R69" t="n">
-        <v>6786220</v>
+        <v>6786243</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7501,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7517,41 +7519,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058335</v>
+        <v>129058291</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7561,10 +7562,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436360</v>
+        <v>436214</v>
       </c>
       <c r="R70" t="n">
-        <v>6786231</v>
+        <v>6786222</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7605,7 +7606,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058267</v>
+        <v>129058362</v>
       </c>
       <c r="B71" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7635,21 +7635,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436524</v>
+        <v>436494</v>
       </c>
       <c r="R71" t="n">
-        <v>6785977</v>
+        <v>6786028</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058362</v>
+        <v>129058354</v>
       </c>
       <c r="B72" t="n">
         <v>78796</v>
@@ -7756,10 +7756,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436494</v>
+        <v>436796</v>
       </c>
       <c r="R72" t="n">
-        <v>6786028</v>
+        <v>6785778</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7818,10 +7818,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058264</v>
+        <v>129058359</v>
       </c>
       <c r="B73" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7829,21 +7829,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436599</v>
+        <v>436532</v>
       </c>
       <c r="R73" t="n">
-        <v>6785738</v>
+        <v>6785994</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7915,10 +7915,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058354</v>
+        <v>129058264</v>
       </c>
       <c r="B74" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7926,21 +7926,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436796</v>
+        <v>436599</v>
       </c>
       <c r="R74" t="n">
-        <v>6785778</v>
+        <v>6785738</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058359</v>
+        <v>129058367</v>
       </c>
       <c r="B75" t="n">
         <v>78796</v>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436532</v>
+        <v>436371</v>
       </c>
       <c r="R75" t="n">
-        <v>6785994</v>
+        <v>6786199</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8109,10 +8109,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058367</v>
+        <v>129058267</v>
       </c>
       <c r="B76" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8120,21 +8120,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436371</v>
+        <v>436524</v>
       </c>
       <c r="R76" t="n">
-        <v>6786199</v>
+        <v>6785977</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8515,10 +8515,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058394</v>
+        <v>129058356</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,21 +8526,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8550,10 +8550,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436493</v>
+        <v>436818</v>
       </c>
       <c r="R80" t="n">
-        <v>6786075</v>
+        <v>6785831</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058356</v>
+        <v>129058282</v>
       </c>
       <c r="B81" t="n">
-        <v>78796</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,34 +8623,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436818</v>
+        <v>436515</v>
       </c>
       <c r="R81" t="n">
-        <v>6785831</v>
+        <v>6786055</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8806,10 +8814,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058282</v>
+        <v>129058394</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,42 +8825,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436515</v>
+        <v>436493</v>
       </c>
       <c r="R83" t="n">
-        <v>6786055</v>
+        <v>6786075</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058411</v>
+        <v>129058346</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436461</v>
+        <v>436503</v>
       </c>
       <c r="R90" t="n">
-        <v>6785881</v>
+        <v>6786136</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058398</v>
+        <v>129058314</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436425</v>
+        <v>436510</v>
       </c>
       <c r="R91" t="n">
-        <v>6786210</v>
+        <v>6786074</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058346</v>
+        <v>129058411</v>
       </c>
       <c r="B93" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436503</v>
+        <v>436461</v>
       </c>
       <c r="R93" t="n">
-        <v>6786136</v>
+        <v>6785881</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058314</v>
+        <v>129058398</v>
       </c>
       <c r="B94" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436510</v>
+        <v>436425</v>
       </c>
       <c r="R94" t="n">
-        <v>6786074</v>
+        <v>6786210</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9991,45 +9991,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058298</v>
+        <v>129058333</v>
       </c>
       <c r="B95" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436513</v>
+        <v>436432</v>
       </c>
       <c r="R95" t="n">
-        <v>6785845</v>
+        <v>6786210</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,6 +10079,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10088,10 +10098,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058300</v>
+        <v>129058416</v>
       </c>
       <c r="B96" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,34 +10109,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436554</v>
+        <v>436491</v>
       </c>
       <c r="R96" t="n">
-        <v>6785764</v>
+        <v>6786146</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10161,12 +10174,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10185,54 +10204,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058333</v>
+        <v>129058407</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436432</v>
+        <v>436215</v>
       </c>
       <c r="R97" t="n">
-        <v>6786210</v>
+        <v>6786222</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,7 +10283,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10399,10 +10408,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058407</v>
+        <v>129058298</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10410,21 +10419,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10434,10 +10443,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436215</v>
+        <v>436513</v>
       </c>
       <c r="R99" t="n">
-        <v>6786222</v>
+        <v>6785845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10496,10 +10505,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058416</v>
+        <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10507,37 +10516,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436491</v>
+        <v>436554</v>
       </c>
       <c r="R100" t="n">
-        <v>6786146</v>
+        <v>6785764</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10572,18 +10578,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129058364</v>
+        <v>129058401</v>
       </c>
       <c r="B102" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436425</v>
+        <v>436310</v>
       </c>
       <c r="R102" t="n">
-        <v>6786192</v>
+        <v>6786196</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058401</v>
+        <v>129058390</v>
       </c>
       <c r="B103" t="n">
         <v>79039</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436310</v>
+        <v>436700</v>
       </c>
       <c r="R103" t="n">
-        <v>6786196</v>
+        <v>6785944</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058390</v>
+        <v>129058364</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10904,21 +10904,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436700</v>
+        <v>436425</v>
       </c>
       <c r="R104" t="n">
-        <v>6785944</v>
+        <v>6786192</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11087,45 +11087,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058406</v>
+        <v>129058324</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436222</v>
+        <v>436254</v>
       </c>
       <c r="R106" t="n">
-        <v>6786238</v>
+        <v>6786130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11166,6 +11175,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11184,7 +11194,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058366</v>
+        <v>129058358</v>
       </c>
       <c r="B107" t="n">
         <v>78796</v>
@@ -11219,10 +11229,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436357</v>
+        <v>436550</v>
       </c>
       <c r="R107" t="n">
-        <v>6786208</v>
+        <v>6785988</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11281,10 +11291,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058393</v>
+        <v>129058366</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11292,21 +11302,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11316,10 +11326,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436507</v>
+        <v>436357</v>
       </c>
       <c r="R108" t="n">
-        <v>6786023</v>
+        <v>6786208</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11378,10 +11388,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058358</v>
+        <v>129058393</v>
       </c>
       <c r="B109" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11389,21 +11399,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11413,10 +11423,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436550</v>
+        <v>436507</v>
       </c>
       <c r="R109" t="n">
-        <v>6785988</v>
+        <v>6786023</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11475,54 +11485,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129058324</v>
+        <v>129058406</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436254</v>
+        <v>436222</v>
       </c>
       <c r="R110" t="n">
-        <v>6786130</v>
+        <v>6786238</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11563,7 +11564,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129080278</v>
+        <v>129080323</v>
       </c>
       <c r="B116" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,21 +12105,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436513</v>
+        <v>436382</v>
       </c>
       <c r="R116" t="n">
-        <v>6785962</v>
+        <v>6786202</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12191,10 +12191,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080329</v>
+        <v>129080278</v>
       </c>
       <c r="B117" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12202,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436247</v>
+        <v>436513</v>
       </c>
       <c r="R117" t="n">
-        <v>6786289</v>
+        <v>6785962</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,11 +12262,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12293,10 +12288,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080323</v>
+        <v>129080329</v>
       </c>
       <c r="B118" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12304,21 +12299,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12328,10 +12323,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436382</v>
+        <v>436247</v>
       </c>
       <c r="R118" t="n">
-        <v>6786202</v>
+        <v>6786289</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,6 +12359,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12490,7 +12490,7 @@
         <v>129080302</v>
       </c>
       <c r="B120" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B131" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R131" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B132" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R132" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14043,7 +14043,7 @@
         <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080317</v>
+        <v>129080316</v>
       </c>
       <c r="B137" t="n">
         <v>78796</v>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436816</v>
+        <v>436532</v>
       </c>
       <c r="R137" t="n">
-        <v>6785768</v>
+        <v>6785867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,7 +14234,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080316</v>
+        <v>129080317</v>
       </c>
       <c r="B138" t="n">
         <v>78796</v>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436532</v>
+        <v>436816</v>
       </c>
       <c r="R138" t="n">
-        <v>6785867</v>
+        <v>6785768</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14719,45 +14719,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080327</v>
+        <v>129080312</v>
       </c>
       <c r="B143" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436653</v>
+        <v>436296</v>
       </c>
       <c r="R143" t="n">
-        <v>6785861</v>
+        <v>6786185</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14798,6 +14807,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14816,10 +14826,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080300</v>
+        <v>129080327</v>
       </c>
       <c r="B144" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14827,21 +14837,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14851,10 +14861,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436333</v>
+        <v>436653</v>
       </c>
       <c r="R144" t="n">
-        <v>6786167</v>
+        <v>6785861</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14913,7 +14923,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129080299</v>
+        <v>129080300</v>
       </c>
       <c r="B145" t="n">
         <v>78797</v>
@@ -14948,10 +14958,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>436384</v>
+        <v>436333</v>
       </c>
       <c r="R145" t="n">
-        <v>6786203</v>
+        <v>6786167</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15010,54 +15020,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080312</v>
+        <v>129080299</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436296</v>
+        <v>436384</v>
       </c>
       <c r="R146" t="n">
-        <v>6786185</v>
+        <v>6786203</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15098,7 +15099,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080282</v>
+        <v>129080331</v>
       </c>
       <c r="B149" t="n">
-        <v>79658</v>
+        <v>88937</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436335</v>
+        <v>436491</v>
       </c>
       <c r="R149" t="n">
-        <v>6786163</v>
+        <v>6786094</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15390,6 +15390,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15408,10 +15409,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080331</v>
+        <v>129080283</v>
       </c>
       <c r="B150" t="n">
-        <v>88930</v>
+        <v>91540</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15419,21 +15420,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15443,10 +15444,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436491</v>
+        <v>436434</v>
       </c>
       <c r="R150" t="n">
-        <v>6786094</v>
+        <v>6786112</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15479,6 +15480,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15506,10 +15512,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080283</v>
+        <v>129080282</v>
       </c>
       <c r="B151" t="n">
-        <v>91533</v>
+        <v>79658</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15517,21 +15523,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15541,10 +15547,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436434</v>
+        <v>436335</v>
       </c>
       <c r="R151" t="n">
-        <v>6786112</v>
+        <v>6786163</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15579,18 +15585,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16336,41 +16336,40 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080311</v>
+        <v>129080287</v>
       </c>
       <c r="B159" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16380,10 +16379,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436449</v>
+        <v>436471</v>
       </c>
       <c r="R159" t="n">
-        <v>6786212</v>
+        <v>6786165</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16424,7 +16423,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16443,7 +16441,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080305</v>
+        <v>129080311</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16487,10 +16485,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436474</v>
+        <v>436449</v>
       </c>
       <c r="R160" t="n">
-        <v>6785946</v>
+        <v>6786212</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16550,7 +16548,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129080310</v>
+        <v>129080305</v>
       </c>
       <c r="B161" t="n">
         <v>8450</v>
@@ -16594,10 +16592,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>436472</v>
+        <v>436474</v>
       </c>
       <c r="R161" t="n">
-        <v>6786160</v>
+        <v>6785946</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16657,40 +16655,41 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080287</v>
+        <v>129080310</v>
       </c>
       <c r="B162" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16700,10 +16699,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436471</v>
+        <v>436472</v>
       </c>
       <c r="R162" t="n">
-        <v>6786165</v>
+        <v>6786160</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16744,6 +16743,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -16762,40 +16762,41 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080286</v>
+        <v>129080309</v>
       </c>
       <c r="B163" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16805,10 +16806,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436572</v>
+        <v>436571</v>
       </c>
       <c r="R163" t="n">
-        <v>6785762</v>
+        <v>6785936</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16849,6 +16850,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16867,7 +16869,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080309</v>
+        <v>129080308</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16911,10 +16913,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436571</v>
+        <v>436807</v>
       </c>
       <c r="R164" t="n">
-        <v>6785936</v>
+        <v>6785797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16974,41 +16976,40 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080308</v>
+        <v>129080286</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17018,10 +17019,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436807</v>
+        <v>436572</v>
       </c>
       <c r="R165" t="n">
-        <v>6785797</v>
+        <v>6785762</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17062,7 +17063,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129058274</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129058412</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -976,54 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058341</v>
+        <v>129058303</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436278</v>
+        <v>436818</v>
       </c>
       <c r="R5" t="n">
-        <v>6786206</v>
+        <v>6785831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1055,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,45 +1073,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058299</v>
+        <v>129058341</v>
       </c>
       <c r="B6" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436545</v>
+        <v>436278</v>
       </c>
       <c r="R6" t="n">
-        <v>6785800</v>
+        <v>6786206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1161,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058303</v>
+        <v>129058299</v>
       </c>
       <c r="B7" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436818</v>
+        <v>436545</v>
       </c>
       <c r="R7" t="n">
-        <v>6785831</v>
+        <v>6785800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058337</v>
+        <v>129058336</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1311,7 +1311,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436322</v>
+        <v>436336</v>
       </c>
       <c r="R8" t="n">
-        <v>6786198</v>
+        <v>6786183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058336</v>
+        <v>129058337</v>
       </c>
       <c r="B10" t="n">
         <v>8450</v>
@@ -1525,7 +1525,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436336</v>
+        <v>436322</v>
       </c>
       <c r="R10" t="n">
-        <v>6786183</v>
+        <v>6786198</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058350</v>
+        <v>129058304</v>
       </c>
       <c r="B11" t="n">
-        <v>78796</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436465</v>
+        <v>436683</v>
       </c>
       <c r="R11" t="n">
-        <v>6785855</v>
+        <v>6785939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058384</v>
+        <v>129058321</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436265</v>
+        <v>436377</v>
       </c>
       <c r="R12" t="n">
-        <v>6786123</v>
+        <v>6786201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058415</v>
+        <v>129058350</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,37 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436527</v>
+        <v>436465</v>
       </c>
       <c r="R13" t="n">
-        <v>6785990</v>
+        <v>6785855</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,18 +1865,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1898,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058304</v>
+        <v>129058384</v>
       </c>
       <c r="B14" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1909,21 +1900,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1933,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436683</v>
+        <v>436265</v>
       </c>
       <c r="R14" t="n">
-        <v>6785939</v>
+        <v>6786123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129058321</v>
+        <v>129058415</v>
       </c>
       <c r="B15" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2006,34 +1997,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436377</v>
+        <v>436527</v>
       </c>
       <c r="R15" t="n">
-        <v>6786201</v>
+        <v>6785990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,12 +2062,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058365</v>
+        <v>129058286</v>
       </c>
       <c r="B16" t="n">
-        <v>78796</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,34 +2103,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436467</v>
+        <v>436617</v>
       </c>
       <c r="R16" t="n">
-        <v>6786236</v>
+        <v>6785749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,7 +2200,7 @@
         <v>129058382</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,10 +2294,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058403</v>
+        <v>129058365</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2305,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436259</v>
+        <v>436467</v>
       </c>
       <c r="R18" t="n">
-        <v>6786285</v>
+        <v>6786236</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,10 +2391,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058286</v>
+        <v>129058403</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,42 +2402,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436617</v>
+        <v>436259</v>
       </c>
       <c r="R19" t="n">
-        <v>6785749</v>
+        <v>6786285</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
         <v>129058301</v>
       </c>
       <c r="B21" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>129058317</v>
       </c>
       <c r="B22" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>129058307</v>
       </c>
       <c r="B23" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>129058308</v>
       </c>
       <c r="B24" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>129058280</v>
       </c>
       <c r="B25" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,40 +3084,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058287</v>
+        <v>129058343</v>
       </c>
       <c r="B26" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3127,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436718</v>
+        <v>436269</v>
       </c>
       <c r="R26" t="n">
-        <v>6785941</v>
+        <v>6786228</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3172,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3189,37 +3191,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058272</v>
+        <v>129058327</v>
       </c>
       <c r="B27" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3227,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436369</v>
+        <v>436674</v>
       </c>
       <c r="R27" t="n">
-        <v>6786195</v>
+        <v>6785802</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,54 +3298,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058343</v>
+        <v>129058311</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436269</v>
+        <v>436530</v>
       </c>
       <c r="R28" t="n">
-        <v>6786228</v>
+        <v>6785992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3378,7 +3377,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3397,43 +3395,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058327</v>
+        <v>129058272</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3441,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436674</v>
+        <v>436369</v>
       </c>
       <c r="R29" t="n">
-        <v>6785802</v>
+        <v>6786195</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,10 +3496,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058311</v>
+        <v>129058287</v>
       </c>
       <c r="B30" t="n">
-        <v>78797</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3515,34 +3507,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436530</v>
+        <v>436718</v>
       </c>
       <c r="R30" t="n">
-        <v>6785992</v>
+        <v>6785941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058273</v>
+        <v>129058288</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,26 +3612,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3639,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436257</v>
+        <v>436458</v>
       </c>
       <c r="R31" t="n">
-        <v>6786288</v>
+        <v>6786194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,7 +3688,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3702,10 +3706,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058369</v>
+        <v>129058273</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,34 +3717,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436817</v>
+        <v>436257</v>
       </c>
       <c r="R32" t="n">
-        <v>6785838</v>
+        <v>6786288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3781,6 +3788,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3799,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058319</v>
+        <v>129058369</v>
       </c>
       <c r="B33" t="n">
-        <v>78797</v>
+        <v>78798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3810,37 +3818,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436378</v>
+        <v>436817</v>
       </c>
       <c r="R33" t="n">
-        <v>6786219</v>
+        <v>6785838</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,7 +3886,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3900,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058288</v>
+        <v>129058319</v>
       </c>
       <c r="B34" t="n">
-        <v>57722</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,31 +3915,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3943,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436458</v>
+        <v>436378</v>
       </c>
       <c r="R34" t="n">
-        <v>6786194</v>
+        <v>6786219</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,6 +3986,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4005,10 +4005,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058269</v>
+        <v>129058404</v>
       </c>
       <c r="B35" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4016,21 +4016,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436483</v>
+        <v>436229</v>
       </c>
       <c r="R35" t="n">
-        <v>6786017</v>
+        <v>6786238</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4102,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058357</v>
+        <v>129058269</v>
       </c>
       <c r="B36" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,21 +4113,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436686</v>
+        <v>436483</v>
       </c>
       <c r="R36" t="n">
-        <v>6785940</v>
+        <v>6786017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058278</v>
+        <v>129058357</v>
       </c>
       <c r="B37" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436295</v>
+        <v>436686</v>
       </c>
       <c r="R37" t="n">
-        <v>6786172</v>
+        <v>6785940</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058348</v>
+        <v>129058278</v>
       </c>
       <c r="B38" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436266</v>
+        <v>436295</v>
       </c>
       <c r="R38" t="n">
-        <v>6786145</v>
+        <v>6786172</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058277</v>
+        <v>129058348</v>
       </c>
       <c r="B39" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,37 +4404,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436351</v>
+        <v>436266</v>
       </c>
       <c r="R39" t="n">
-        <v>6786185</v>
+        <v>6786145</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4475,7 +4472,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058262</v>
+        <v>129058277</v>
       </c>
       <c r="B40" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4523,16 +4519,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436534</v>
+        <v>436351</v>
       </c>
       <c r="R40" t="n">
-        <v>6785834</v>
+        <v>6786185</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4573,6 +4572,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058404</v>
+        <v>129058262</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436229</v>
+        <v>436534</v>
       </c>
       <c r="R41" t="n">
-        <v>6786238</v>
+        <v>6785834</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,7 +4798,7 @@
         <v>129058318</v>
       </c>
       <c r="B43" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>129058276</v>
       </c>
       <c r="B44" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>129058351</v>
       </c>
       <c r="B45" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>129058297</v>
       </c>
       <c r="B46" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>129058313</v>
       </c>
       <c r="B47" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058290</v>
+        <v>129058386</v>
       </c>
       <c r="B48" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,42 +5295,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436601</v>
+        <v>436505</v>
       </c>
       <c r="R48" t="n">
-        <v>6785947</v>
+        <v>6785856</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,7 +5384,7 @@
         <v>129058268</v>
       </c>
       <c r="B49" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5481,7 @@
         <v>129058395</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5578,7 @@
         <v>129058385</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5680,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058386</v>
+        <v>129058290</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,34 +5683,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436505</v>
+        <v>436601</v>
       </c>
       <c r="R52" t="n">
-        <v>6785856</v>
+        <v>6785947</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
         <v>129058309</v>
       </c>
       <c r="B53" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129058402</v>
+        <v>129058399</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436264</v>
+        <v>436303</v>
       </c>
       <c r="R54" t="n">
-        <v>6786282</v>
+        <v>6786193</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med Garnlav inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058396</v>
+        <v>129058391</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6009,16 +6009,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436491</v>
+        <v>436591</v>
       </c>
       <c r="R55" t="n">
-        <v>6786189</v>
+        <v>6785966</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,12 +6056,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6077,10 +6086,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129058392</v>
+        <v>129058402</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6115,10 +6124,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436508</v>
+        <v>436264</v>
       </c>
       <c r="R56" t="n">
-        <v>6786026</v>
+        <v>6786282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6155,7 +6164,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6183,10 +6192,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129058391</v>
+        <v>129058392</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6221,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436591</v>
+        <v>436508</v>
       </c>
       <c r="R57" t="n">
-        <v>6785966</v>
+        <v>6786026</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6261,7 +6270,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
+          <t>Garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6289,10 +6298,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129058399</v>
+        <v>129058396</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6318,19 +6327,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436303</v>
+        <v>436491</v>
       </c>
       <c r="R58" t="n">
-        <v>6786193</v>
+        <v>6786189</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6365,18 +6371,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>129058279</v>
       </c>
       <c r="B59" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129058306</v>
       </c>
       <c r="B60" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,54 +6597,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058323</v>
+        <v>129058271</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436241</v>
+        <v>436493</v>
       </c>
       <c r="R61" t="n">
-        <v>6786159</v>
+        <v>6786189</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6685,7 +6676,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6704,54 +6694,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058330</v>
+        <v>129058361</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436823</v>
+        <v>436500</v>
       </c>
       <c r="R62" t="n">
-        <v>6785756</v>
+        <v>6786018</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6792,7 +6773,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6811,54 +6791,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058340</v>
+        <v>129058353</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436324</v>
+        <v>436551</v>
       </c>
       <c r="R63" t="n">
-        <v>6786220</v>
+        <v>6785765</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,7 +6870,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6918,43 +6888,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058335</v>
+        <v>129058389</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6962,10 +6926,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436360</v>
+        <v>436739</v>
       </c>
       <c r="R64" t="n">
-        <v>6786231</v>
+        <v>6785902</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6998,6 +6962,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7025,10 +6994,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058271</v>
+        <v>129058405</v>
       </c>
       <c r="B65" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7036,21 +7005,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7060,10 +7029,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436493</v>
+        <v>436227</v>
       </c>
       <c r="R65" t="n">
-        <v>6786189</v>
+        <v>6786243</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7122,45 +7091,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058361</v>
+        <v>129058335</v>
       </c>
       <c r="B66" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436500</v>
+        <v>436360</v>
       </c>
       <c r="R66" t="n">
-        <v>6786018</v>
+        <v>6786231</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7201,6 +7179,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7219,45 +7198,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058353</v>
+        <v>129058340</v>
       </c>
       <c r="B67" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436551</v>
+        <v>436324</v>
       </c>
       <c r="R67" t="n">
-        <v>6785765</v>
+        <v>6786220</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7298,6 +7286,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7316,37 +7305,43 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058389</v>
+        <v>129058330</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7354,10 +7349,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436739</v>
+        <v>436823</v>
       </c>
       <c r="R68" t="n">
-        <v>6785902</v>
+        <v>6785756</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7390,11 +7385,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7422,45 +7412,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058405</v>
+        <v>129058323</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436227</v>
+        <v>436241</v>
       </c>
       <c r="R69" t="n">
-        <v>6786243</v>
+        <v>6786159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7501,6 +7500,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>129058291</v>
       </c>
       <c r="B70" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>129058362</v>
       </c>
       <c r="B71" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>129058354</v>
       </c>
       <c r="B72" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>129058359</v>
       </c>
       <c r="B73" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>129058264</v>
       </c>
       <c r="B74" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>129058367</v>
       </c>
       <c r="B75" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>129058267</v>
       </c>
       <c r="B76" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>129058305</v>
       </c>
       <c r="B78" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058355</v>
+        <v>129058282</v>
       </c>
       <c r="B79" t="n">
-        <v>78796</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,26 +8425,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8452,10 +8457,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436825</v>
+        <v>436515</v>
       </c>
       <c r="R79" t="n">
-        <v>6785764</v>
+        <v>6786055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8496,7 +8501,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8515,10 +8519,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058356</v>
+        <v>129058394</v>
       </c>
       <c r="B80" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,21 +8530,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8550,10 +8554,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436818</v>
+        <v>436493</v>
       </c>
       <c r="R80" t="n">
-        <v>6785831</v>
+        <v>6786075</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8612,10 +8616,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058282</v>
+        <v>129058355</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>78798</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,31 +8627,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8655,10 +8654,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436515</v>
+        <v>436825</v>
       </c>
       <c r="R81" t="n">
-        <v>6786055</v>
+        <v>6785764</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8699,6 +8698,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8717,10 +8717,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058315</v>
+        <v>129058356</v>
       </c>
       <c r="B82" t="n">
-        <v>78797</v>
+        <v>78798</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8728,21 +8728,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436445</v>
+        <v>436818</v>
       </c>
       <c r="R82" t="n">
-        <v>6786210</v>
+        <v>6785831</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8814,10 +8814,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058394</v>
+        <v>129058315</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436493</v>
+        <v>436445</v>
       </c>
       <c r="R83" t="n">
-        <v>6786075</v>
+        <v>6786210</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129058352</v>
+        <v>129058397</v>
       </c>
       <c r="B84" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8922,34 +8922,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436515</v>
+        <v>436446</v>
       </c>
       <c r="R84" t="n">
-        <v>6785847</v>
+        <v>6786249</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8990,6 +8993,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9008,10 +9012,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129058263</v>
+        <v>129058383</v>
       </c>
       <c r="B85" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9019,21 +9023,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,10 +9047,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436559</v>
+        <v>436263</v>
       </c>
       <c r="R85" t="n">
-        <v>6785783</v>
+        <v>6786145</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9105,10 +9109,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129058414</v>
+        <v>129058352</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9116,37 +9120,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436671</v>
+        <v>436515</v>
       </c>
       <c r="R86" t="n">
-        <v>6785810</v>
+        <v>6785847</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9181,18 +9182,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9211,10 +9206,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058397</v>
+        <v>129058263</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9222,37 +9217,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436446</v>
+        <v>436559</v>
       </c>
       <c r="R87" t="n">
-        <v>6786249</v>
+        <v>6785783</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9293,7 +9285,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9312,10 +9303,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129058383</v>
+        <v>129058414</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9341,16 +9332,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436263</v>
+        <v>436671</v>
       </c>
       <c r="R88" t="n">
-        <v>6786145</v>
+        <v>6785810</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9385,12 +9379,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>129058302</v>
       </c>
       <c r="B89" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058346</v>
+        <v>129058387</v>
       </c>
       <c r="B90" t="n">
-        <v>58095</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436503</v>
+        <v>436805</v>
       </c>
       <c r="R90" t="n">
-        <v>6786136</v>
+        <v>6785785</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058314</v>
+        <v>129058398</v>
       </c>
       <c r="B91" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436510</v>
+        <v>436425</v>
       </c>
       <c r="R91" t="n">
-        <v>6786074</v>
+        <v>6786210</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058387</v>
+        <v>129058314</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9711,21 +9711,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436805</v>
+        <v>436510</v>
       </c>
       <c r="R92" t="n">
-        <v>6785785</v>
+        <v>6786074</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9800,7 +9800,7 @@
         <v>129058411</v>
       </c>
       <c r="B93" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058398</v>
+        <v>129058346</v>
       </c>
       <c r="B94" t="n">
-        <v>79039</v>
+        <v>58097</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436425</v>
+        <v>436503</v>
       </c>
       <c r="R94" t="n">
-        <v>6786210</v>
+        <v>6786136</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058333</v>
+        <v>129058345</v>
       </c>
       <c r="B95" t="n">
         <v>8450</v>
@@ -10025,7 +10025,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436432</v>
+        <v>436269</v>
       </c>
       <c r="R95" t="n">
-        <v>6786210</v>
+        <v>6786257</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10098,37 +10098,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058416</v>
+        <v>129058333</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10136,10 +10142,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436491</v>
+        <v>436432</v>
       </c>
       <c r="R96" t="n">
-        <v>6786146</v>
+        <v>6786210</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10172,11 +10178,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10204,10 +10205,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058407</v>
+        <v>129058300</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10215,21 +10216,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10239,10 +10240,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436215</v>
+        <v>436554</v>
       </c>
       <c r="R97" t="n">
-        <v>6786222</v>
+        <v>6785764</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10301,54 +10302,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058345</v>
+        <v>129058407</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436269</v>
+        <v>436215</v>
       </c>
       <c r="R98" t="n">
-        <v>6786257</v>
+        <v>6786222</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,7 +10381,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10408,10 +10399,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058298</v>
+        <v>129058416</v>
       </c>
       <c r="B99" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10419,34 +10410,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436513</v>
+        <v>436491</v>
       </c>
       <c r="R99" t="n">
-        <v>6785845</v>
+        <v>6786146</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10481,12 +10475,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058300</v>
+        <v>129058298</v>
       </c>
       <c r="B100" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436554</v>
+        <v>436513</v>
       </c>
       <c r="R100" t="n">
-        <v>6785764</v>
+        <v>6785845</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10605,7 +10605,7 @@
         <v>129058417</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129058401</v>
+        <v>129058390</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436310</v>
+        <v>436700</v>
       </c>
       <c r="R102" t="n">
-        <v>6786196</v>
+        <v>6785944</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058390</v>
+        <v>129058364</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436700</v>
+        <v>436425</v>
       </c>
       <c r="R103" t="n">
-        <v>6785944</v>
+        <v>6786192</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058364</v>
+        <v>129058401</v>
       </c>
       <c r="B104" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10904,21 +10904,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436425</v>
+        <v>436310</v>
       </c>
       <c r="R104" t="n">
-        <v>6786192</v>
+        <v>6786196</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10993,7 +10993,7 @@
         <v>129058266</v>
       </c>
       <c r="B105" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>129058358</v>
       </c>
       <c r="B107" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>129058366</v>
       </c>
       <c r="B108" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058393</v>
+        <v>129058406</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436507</v>
+        <v>436222</v>
       </c>
       <c r="R109" t="n">
-        <v>6786023</v>
+        <v>6786238</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11485,10 +11485,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129058406</v>
+        <v>129058393</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436222</v>
+        <v>436507</v>
       </c>
       <c r="R110" t="n">
-        <v>6786238</v>
+        <v>6786023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058368</v>
+        <v>129058289</v>
       </c>
       <c r="B111" t="n">
-        <v>78796</v>
+        <v>57724</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11593,34 +11593,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436257</v>
+        <v>436486</v>
       </c>
       <c r="R111" t="n">
-        <v>6786288</v>
+        <v>6786231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11679,10 +11687,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058289</v>
+        <v>129058368</v>
       </c>
       <c r="B112" t="n">
-        <v>57722</v>
+        <v>78798</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11690,42 +11698,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436486</v>
+        <v>436257</v>
       </c>
       <c r="R112" t="n">
-        <v>6786231</v>
+        <v>6786288</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11894,7 +11894,7 @@
         <v>129058270</v>
       </c>
       <c r="B114" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>129058388</v>
       </c>
       <c r="B115" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>129080323</v>
       </c>
       <c r="B116" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>129080278</v>
       </c>
       <c r="B117" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>129080329</v>
       </c>
       <c r="B118" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>129080292</v>
       </c>
       <c r="B119" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080302</v>
+        <v>129080295</v>
       </c>
       <c r="B120" t="n">
-        <v>91560</v>
+        <v>78799</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436320</v>
+        <v>436815</v>
       </c>
       <c r="R120" t="n">
-        <v>6786132</v>
+        <v>6785768</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,7 +12566,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12585,10 +12584,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080277</v>
+        <v>129080291</v>
       </c>
       <c r="B121" t="n">
-        <v>79658</v>
+        <v>78799</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12596,21 +12595,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12620,10 +12619,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436561</v>
+        <v>436524</v>
       </c>
       <c r="R121" t="n">
-        <v>6785959</v>
+        <v>6785865</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12682,10 +12681,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129080295</v>
+        <v>129080294</v>
       </c>
       <c r="B122" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12717,10 +12716,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436815</v>
+        <v>436659</v>
       </c>
       <c r="R122" t="n">
-        <v>6785768</v>
+        <v>6785808</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12779,10 +12778,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080291</v>
+        <v>129080302</v>
       </c>
       <c r="B123" t="n">
-        <v>78797</v>
+        <v>91562</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12790,21 +12789,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12814,10 +12813,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436524</v>
+        <v>436320</v>
       </c>
       <c r="R123" t="n">
-        <v>6785865</v>
+        <v>6786132</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12858,6 +12857,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12876,10 +12876,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080294</v>
+        <v>129080277</v>
       </c>
       <c r="B124" t="n">
-        <v>78797</v>
+        <v>79660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,21 +12887,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436659</v>
+        <v>436561</v>
       </c>
       <c r="R124" t="n">
-        <v>6785808</v>
+        <v>6785959</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12976,7 +12976,7 @@
         <v>129080322</v>
       </c>
       <c r="B125" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>129080289</v>
       </c>
       <c r="B126" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>129080281</v>
       </c>
       <c r="B127" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>129080328</v>
       </c>
       <c r="B128" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>129080298</v>
       </c>
       <c r="B129" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>129080290</v>
       </c>
       <c r="B130" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>129080313</v>
       </c>
       <c r="B131" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>129080296</v>
       </c>
       <c r="B132" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>129080318</v>
       </c>
       <c r="B133" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129080279</v>
+        <v>129080301</v>
       </c>
       <c r="B134" t="n">
-        <v>79658</v>
+        <v>78799</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436471</v>
+        <v>436246</v>
       </c>
       <c r="R134" t="n">
-        <v>6786142</v>
+        <v>6786298</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129080301</v>
+        <v>129080279</v>
       </c>
       <c r="B135" t="n">
-        <v>78797</v>
+        <v>79660</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436246</v>
+        <v>436471</v>
       </c>
       <c r="R135" t="n">
-        <v>6786298</v>
+        <v>6786142</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14043,7 +14043,7 @@
         <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>129080316</v>
       </c>
       <c r="B137" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>129080317</v>
       </c>
       <c r="B138" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>129080314</v>
       </c>
       <c r="B139" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129080293</v>
       </c>
       <c r="B140" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>129080319</v>
       </c>
       <c r="B141" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>129080324</v>
       </c>
       <c r="B142" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14826,10 +14826,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080327</v>
+        <v>129080300</v>
       </c>
       <c r="B144" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14837,21 +14837,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14861,10 +14861,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436653</v>
+        <v>436333</v>
       </c>
       <c r="R144" t="n">
-        <v>6785861</v>
+        <v>6786167</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14923,10 +14923,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129080300</v>
+        <v>129080299</v>
       </c>
       <c r="B145" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14958,10 +14958,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>436333</v>
+        <v>436384</v>
       </c>
       <c r="R145" t="n">
-        <v>6786167</v>
+        <v>6786203</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15020,10 +15020,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080299</v>
+        <v>129080327</v>
       </c>
       <c r="B146" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15031,21 +15031,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436384</v>
+        <v>436653</v>
       </c>
       <c r="R146" t="n">
-        <v>6786203</v>
+        <v>6785861</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15120,7 +15120,7 @@
         <v>129080315</v>
       </c>
       <c r="B147" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>129080280</v>
       </c>
       <c r="B148" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080331</v>
+        <v>129080283</v>
       </c>
       <c r="B149" t="n">
-        <v>88937</v>
+        <v>91542</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436491</v>
+        <v>436434</v>
       </c>
       <c r="R149" t="n">
-        <v>6786094</v>
+        <v>6786112</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15382,6 +15382,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15409,10 +15414,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080283</v>
+        <v>129080297</v>
       </c>
       <c r="B150" t="n">
-        <v>91540</v>
+        <v>78799</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15420,21 +15425,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15444,10 +15449,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436434</v>
+        <v>436449</v>
       </c>
       <c r="R150" t="n">
-        <v>6786112</v>
+        <v>6786210</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15482,18 +15487,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15512,10 +15511,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080282</v>
+        <v>129080331</v>
       </c>
       <c r="B151" t="n">
-        <v>79658</v>
+        <v>88939</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15523,21 +15522,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15547,10 +15546,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436335</v>
+        <v>436491</v>
       </c>
       <c r="R151" t="n">
-        <v>6786163</v>
+        <v>6786094</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15591,6 +15590,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15609,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080297</v>
+        <v>129080282</v>
       </c>
       <c r="B152" t="n">
-        <v>78797</v>
+        <v>79660</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436449</v>
+        <v>436335</v>
       </c>
       <c r="R152" t="n">
-        <v>6786210</v>
+        <v>6786163</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15709,7 +15709,7 @@
         <v>129080320</v>
       </c>
       <c r="B153" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>129080288</v>
       </c>
       <c r="B155" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16336,40 +16336,41 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080287</v>
+        <v>129080310</v>
       </c>
       <c r="B159" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16379,10 +16380,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436471</v>
+        <v>436472</v>
       </c>
       <c r="R159" t="n">
-        <v>6786165</v>
+        <v>6786160</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16423,6 +16424,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16441,7 +16443,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080311</v>
+        <v>129080305</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16485,10 +16487,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436449</v>
+        <v>436474</v>
       </c>
       <c r="R160" t="n">
-        <v>6786212</v>
+        <v>6785946</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16548,7 +16550,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129080305</v>
+        <v>129080311</v>
       </c>
       <c r="B161" t="n">
         <v>8450</v>
@@ -16592,10 +16594,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>436474</v>
+        <v>436449</v>
       </c>
       <c r="R161" t="n">
-        <v>6785946</v>
+        <v>6786212</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16655,41 +16657,40 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080310</v>
+        <v>129080287</v>
       </c>
       <c r="B162" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16699,10 +16700,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436472</v>
+        <v>436471</v>
       </c>
       <c r="R162" t="n">
-        <v>6786160</v>
+        <v>6786165</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16743,7 +16744,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -16762,41 +16762,40 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080309</v>
+        <v>129080286</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16806,10 +16805,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436571</v>
+        <v>436572</v>
       </c>
       <c r="R163" t="n">
-        <v>6785936</v>
+        <v>6785762</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16850,7 +16849,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16976,40 +16974,41 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080286</v>
+        <v>129080309</v>
       </c>
       <c r="B165" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17019,10 +17018,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436572</v>
+        <v>436571</v>
       </c>
       <c r="R165" t="n">
-        <v>6785762</v>
+        <v>6785936</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17063,6 +17062,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17084,7 +17084,7 @@
         <v>129080285</v>
       </c>
       <c r="B166" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058274</v>
+        <v>129058299</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436522</v>
+        <v>436545</v>
       </c>
       <c r="R2" t="n">
-        <v>6786062</v>
+        <v>6785800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058412</v>
+        <v>129058303</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436564</v>
+        <v>436818</v>
       </c>
       <c r="R3" t="n">
-        <v>6785776</v>
+        <v>6785831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058331</v>
+        <v>129058274</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436755</v>
+        <v>436522</v>
       </c>
       <c r="R4" t="n">
-        <v>6785905</v>
+        <v>6786062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058303</v>
+        <v>129058412</v>
       </c>
       <c r="B5" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436818</v>
+        <v>436564</v>
       </c>
       <c r="R5" t="n">
-        <v>6785831</v>
+        <v>6785776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058341</v>
+        <v>129058331</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1117,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436278</v>
+        <v>436755</v>
       </c>
       <c r="R6" t="n">
-        <v>6786206</v>
+        <v>6785905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,45 +1170,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058299</v>
+        <v>129058341</v>
       </c>
       <c r="B7" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436545</v>
+        <v>436278</v>
       </c>
       <c r="R7" t="n">
-        <v>6785800</v>
+        <v>6786206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,54 +1277,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058336</v>
+        <v>129058384</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436336</v>
+        <v>436265</v>
       </c>
       <c r="R8" t="n">
-        <v>6786183</v>
+        <v>6786123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,54 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058329</v>
+        <v>129058350</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436754</v>
+        <v>436465</v>
       </c>
       <c r="R9" t="n">
-        <v>6785822</v>
+        <v>6785855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,43 +1471,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058337</v>
+        <v>129058415</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436322</v>
+        <v>436527</v>
       </c>
       <c r="R10" t="n">
-        <v>6786198</v>
+        <v>6785990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1545,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,45 +1577,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058304</v>
+        <v>129058337</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436683</v>
+        <v>436322</v>
       </c>
       <c r="R11" t="n">
-        <v>6785939</v>
+        <v>6786198</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,6 +1665,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1695,45 +1684,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058321</v>
+        <v>129058329</v>
       </c>
       <c r="B12" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436377</v>
+        <v>436754</v>
       </c>
       <c r="R12" t="n">
-        <v>6786201</v>
+        <v>6785822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,6 +1772,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1792,45 +1791,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058350</v>
+        <v>129058336</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436465</v>
+        <v>436336</v>
       </c>
       <c r="R13" t="n">
-        <v>6785855</v>
+        <v>6786183</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,6 +1879,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1889,10 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058384</v>
+        <v>129058304</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,21 +1909,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436265</v>
+        <v>436683</v>
       </c>
       <c r="R14" t="n">
-        <v>6786123</v>
+        <v>6785939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,10 +1995,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129058415</v>
+        <v>129058321</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,37 +2006,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436527</v>
+        <v>436377</v>
       </c>
       <c r="R15" t="n">
-        <v>6785990</v>
+        <v>6786201</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,18 +2068,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058286</v>
+        <v>129058382</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,42 +2103,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436617</v>
+        <v>436214</v>
       </c>
       <c r="R16" t="n">
-        <v>6785749</v>
+        <v>6786180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2189,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058382</v>
+        <v>129058403</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2232,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436214</v>
+        <v>436259</v>
       </c>
       <c r="R17" t="n">
-        <v>6786180</v>
+        <v>6786285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058403</v>
+        <v>129058286</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2402,34 +2394,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436259</v>
+        <v>436617</v>
       </c>
       <c r="R19" t="n">
-        <v>6786285</v>
+        <v>6785749</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058288</v>
+        <v>129058369</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,42 +3612,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436458</v>
+        <v>436817</v>
       </c>
       <c r="R31" t="n">
-        <v>6786194</v>
+        <v>6785838</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3706,10 +3698,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058273</v>
+        <v>129058288</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,26 +3709,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3744,10 +3741,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436257</v>
+        <v>436458</v>
       </c>
       <c r="R32" t="n">
-        <v>6786288</v>
+        <v>6786194</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,7 +3785,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3807,10 +3803,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058369</v>
+        <v>129058273</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,34 +3814,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436817</v>
+        <v>436257</v>
       </c>
       <c r="R33" t="n">
-        <v>6785838</v>
+        <v>6786288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,6 +3885,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4005,10 +4005,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058404</v>
+        <v>129058262</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4016,21 +4016,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436229</v>
+        <v>436534</v>
       </c>
       <c r="R35" t="n">
-        <v>6786238</v>
+        <v>6785834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058357</v>
+        <v>129058277</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,34 +4210,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436686</v>
+        <v>436351</v>
       </c>
       <c r="R37" t="n">
-        <v>6785940</v>
+        <v>6786185</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,6 +4281,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058278</v>
+        <v>129058404</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4311,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436295</v>
+        <v>436229</v>
       </c>
       <c r="R38" t="n">
-        <v>6786172</v>
+        <v>6786238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4490,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058277</v>
+        <v>129058357</v>
       </c>
       <c r="B40" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4501,37 +4505,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436351</v>
+        <v>436686</v>
       </c>
       <c r="R40" t="n">
-        <v>6786185</v>
+        <v>6785940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,7 +4573,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058262</v>
+        <v>129058278</v>
       </c>
       <c r="B41" t="n">
         <v>79660</v>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436534</v>
+        <v>436295</v>
       </c>
       <c r="R41" t="n">
-        <v>6785834</v>
+        <v>6786172</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058386</v>
+        <v>129058395</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436505</v>
+        <v>436504</v>
       </c>
       <c r="R48" t="n">
-        <v>6785856</v>
+        <v>6786102</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058268</v>
+        <v>129058385</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R49" t="n">
-        <v>6786023</v>
+        <v>6786086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058395</v>
+        <v>129058268</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,21 +5489,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,7 +5516,7 @@
         <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6786102</v>
+        <v>6786023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058385</v>
+        <v>129058386</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436327</v>
+        <v>436505</v>
       </c>
       <c r="R51" t="n">
-        <v>6786086</v>
+        <v>6785856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129058399</v>
+        <v>129058402</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436303</v>
+        <v>436264</v>
       </c>
       <c r="R54" t="n">
-        <v>6786193</v>
+        <v>6786282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt med Garnlav inom en radie av 40 m</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5980,7 +5980,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058391</v>
+        <v>129058396</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6009,19 +6009,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436591</v>
+        <v>436491</v>
       </c>
       <c r="R55" t="n">
-        <v>6785966</v>
+        <v>6786189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,18 +6053,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6086,7 +6077,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129058402</v>
+        <v>129058392</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6124,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436264</v>
+        <v>436508</v>
       </c>
       <c r="R56" t="n">
-        <v>6786282</v>
+        <v>6786026</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6164,7 +6155,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6192,7 +6183,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129058392</v>
+        <v>129058391</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6230,10 +6221,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436508</v>
+        <v>436591</v>
       </c>
       <c r="R57" t="n">
-        <v>6786026</v>
+        <v>6785966</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6270,7 +6261,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6298,7 +6289,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129058396</v>
+        <v>129058399</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6327,16 +6318,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436491</v>
+        <v>436303</v>
       </c>
       <c r="R58" t="n">
-        <v>6786189</v>
+        <v>6786193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,12 +6365,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058271</v>
+        <v>129058389</v>
       </c>
       <c r="B61" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,34 +6608,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436493</v>
+        <v>436739</v>
       </c>
       <c r="R61" t="n">
-        <v>6786189</v>
+        <v>6785902</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6670,12 +6673,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6694,10 +6703,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058361</v>
+        <v>129058271</v>
       </c>
       <c r="B62" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6705,21 +6714,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6729,10 +6738,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436500</v>
+        <v>436493</v>
       </c>
       <c r="R62" t="n">
-        <v>6786018</v>
+        <v>6786189</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6791,7 +6800,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058353</v>
+        <v>129058361</v>
       </c>
       <c r="B63" t="n">
         <v>78798</v>
@@ -6826,10 +6835,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436551</v>
+        <v>436500</v>
       </c>
       <c r="R63" t="n">
-        <v>6785765</v>
+        <v>6786018</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6888,7 +6897,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058389</v>
+        <v>129058405</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -6917,19 +6926,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436739</v>
+        <v>436227</v>
       </c>
       <c r="R64" t="n">
-        <v>6785902</v>
+        <v>6786243</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6964,18 +6970,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058405</v>
+        <v>129058353</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7005,21 +7005,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436227</v>
+        <v>436551</v>
       </c>
       <c r="R65" t="n">
-        <v>6786243</v>
+        <v>6785765</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7091,41 +7091,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058335</v>
+        <v>129058291</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7135,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436360</v>
+        <v>436214</v>
       </c>
       <c r="R66" t="n">
-        <v>6786231</v>
+        <v>6786222</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7179,7 +7178,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7198,7 +7196,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058340</v>
+        <v>129058323</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7242,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436324</v>
+        <v>436241</v>
       </c>
       <c r="R67" t="n">
-        <v>6786220</v>
+        <v>6786159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7412,7 +7410,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058323</v>
+        <v>129058340</v>
       </c>
       <c r="B69" t="n">
         <v>8450</v>
@@ -7456,10 +7454,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436241</v>
+        <v>436324</v>
       </c>
       <c r="R69" t="n">
-        <v>6786159</v>
+        <v>6786220</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7519,40 +7517,41 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058291</v>
+        <v>129058335</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7562,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436214</v>
+        <v>436360</v>
       </c>
       <c r="R70" t="n">
-        <v>6786222</v>
+        <v>6786231</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7606,6 +7605,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7624,45 +7624,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058362</v>
+        <v>129058334</v>
       </c>
       <c r="B71" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436494</v>
+        <v>436373</v>
       </c>
       <c r="R71" t="n">
-        <v>6786028</v>
+        <v>6786190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7703,6 +7712,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7721,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058354</v>
+        <v>129058305</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7732,34 +7742,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436796</v>
+        <v>436680</v>
       </c>
       <c r="R72" t="n">
-        <v>6785778</v>
+        <v>6785902</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7800,6 +7813,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7818,10 +7832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058359</v>
+        <v>129058267</v>
       </c>
       <c r="B73" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7829,21 +7843,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7853,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436532</v>
+        <v>436524</v>
       </c>
       <c r="R73" t="n">
-        <v>6785994</v>
+        <v>6785977</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7915,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058264</v>
+        <v>129058362</v>
       </c>
       <c r="B74" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7926,21 +7940,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7950,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436599</v>
+        <v>436494</v>
       </c>
       <c r="R74" t="n">
-        <v>6785738</v>
+        <v>6786028</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8012,10 +8026,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058367</v>
+        <v>129058264</v>
       </c>
       <c r="B75" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8023,21 +8037,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8047,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436371</v>
+        <v>436599</v>
       </c>
       <c r="R75" t="n">
-        <v>6786199</v>
+        <v>6785738</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8109,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058267</v>
+        <v>129058354</v>
       </c>
       <c r="B76" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8120,21 +8134,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8144,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436524</v>
+        <v>436796</v>
       </c>
       <c r="R76" t="n">
-        <v>6785977</v>
+        <v>6785778</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,54 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058334</v>
+        <v>129058359</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436373</v>
+        <v>436532</v>
       </c>
       <c r="R77" t="n">
-        <v>6786190</v>
+        <v>6785994</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,7 +8299,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8313,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058305</v>
+        <v>129058367</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,37 +8328,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436680</v>
+        <v>436371</v>
       </c>
       <c r="R78" t="n">
-        <v>6785902</v>
+        <v>6786199</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8395,7 +8396,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058282</v>
+        <v>129058315</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,42 +8425,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436515</v>
+        <v>436445</v>
       </c>
       <c r="R79" t="n">
-        <v>6786055</v>
+        <v>6786210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8519,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058394</v>
+        <v>129058355</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8530,34 +8522,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436493</v>
+        <v>436825</v>
       </c>
       <c r="R80" t="n">
-        <v>6786075</v>
+        <v>6785764</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8598,6 +8593,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8616,10 +8612,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058355</v>
+        <v>129058394</v>
       </c>
       <c r="B81" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8627,37 +8623,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436825</v>
+        <v>436493</v>
       </c>
       <c r="R81" t="n">
-        <v>6785764</v>
+        <v>6786075</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8698,7 +8691,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8814,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058315</v>
+        <v>129058282</v>
       </c>
       <c r="B83" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8825,34 +8817,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436445</v>
+        <v>436515</v>
       </c>
       <c r="R83" t="n">
-        <v>6786210</v>
+        <v>6786055</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129058397</v>
+        <v>129058352</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8922,37 +8922,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436446</v>
+        <v>436515</v>
       </c>
       <c r="R84" t="n">
-        <v>6786249</v>
+        <v>6785847</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8993,7 +8990,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9012,10 +9008,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129058383</v>
+        <v>129058263</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9023,21 +9019,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9047,10 +9043,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436263</v>
+        <v>436559</v>
       </c>
       <c r="R85" t="n">
-        <v>6786145</v>
+        <v>6785783</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9109,10 +9105,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129058352</v>
+        <v>129058414</v>
       </c>
       <c r="B86" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9120,34 +9116,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436515</v>
+        <v>436671</v>
       </c>
       <c r="R86" t="n">
-        <v>6785847</v>
+        <v>6785810</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9182,12 +9181,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9206,10 +9211,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058263</v>
+        <v>129058397</v>
       </c>
       <c r="B87" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9217,34 +9222,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436559</v>
+        <v>436446</v>
       </c>
       <c r="R87" t="n">
-        <v>6785783</v>
+        <v>6786249</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9285,6 +9293,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9303,7 +9312,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129058414</v>
+        <v>129058383</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -9332,19 +9341,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436671</v>
+        <v>436263</v>
       </c>
       <c r="R88" t="n">
-        <v>6785810</v>
+        <v>6786145</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9379,18 +9385,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9506,7 +9506,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058387</v>
+        <v>129058411</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436805</v>
+        <v>436461</v>
       </c>
       <c r="R90" t="n">
-        <v>6785785</v>
+        <v>6785881</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058314</v>
+        <v>129058387</v>
       </c>
       <c r="B92" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9711,21 +9711,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436510</v>
+        <v>436805</v>
       </c>
       <c r="R92" t="n">
-        <v>6786074</v>
+        <v>6785785</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058411</v>
+        <v>129058346</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436461</v>
+        <v>436503</v>
       </c>
       <c r="R93" t="n">
-        <v>6785881</v>
+        <v>6786136</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058346</v>
+        <v>129058314</v>
       </c>
       <c r="B94" t="n">
-        <v>58097</v>
+        <v>78799</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436503</v>
+        <v>436510</v>
       </c>
       <c r="R94" t="n">
-        <v>6786136</v>
+        <v>6786074</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9991,54 +9991,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058345</v>
+        <v>129058407</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436269</v>
+        <v>436215</v>
       </c>
       <c r="R95" t="n">
-        <v>6786257</v>
+        <v>6786222</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,7 +10070,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10098,43 +10088,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058333</v>
+        <v>129058416</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10142,10 +10126,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436432</v>
+        <v>436491</v>
       </c>
       <c r="R96" t="n">
-        <v>6786210</v>
+        <v>6786146</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10178,6 +10162,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10205,7 +10194,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058300</v>
+        <v>129058298</v>
       </c>
       <c r="B97" t="n">
         <v>78799</v>
@@ -10240,10 +10229,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436554</v>
+        <v>436513</v>
       </c>
       <c r="R97" t="n">
-        <v>6785764</v>
+        <v>6785845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10302,10 +10291,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058407</v>
+        <v>129058300</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10313,21 +10302,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10337,10 +10326,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436215</v>
+        <v>436554</v>
       </c>
       <c r="R98" t="n">
-        <v>6786222</v>
+        <v>6785764</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10399,37 +10388,43 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058416</v>
+        <v>129058333</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10437,10 +10432,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436491</v>
+        <v>436432</v>
       </c>
       <c r="R99" t="n">
-        <v>6786146</v>
+        <v>6786210</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10473,11 +10468,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10505,45 +10495,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058298</v>
+        <v>129058345</v>
       </c>
       <c r="B100" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436513</v>
+        <v>436269</v>
       </c>
       <c r="R100" t="n">
-        <v>6785845</v>
+        <v>6786257</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10584,6 +10583,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129058390</v>
+        <v>129058364</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10710,21 +10710,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436700</v>
+        <v>436425</v>
       </c>
       <c r="R102" t="n">
-        <v>6785944</v>
+        <v>6786192</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129058364</v>
+        <v>129058401</v>
       </c>
       <c r="B103" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10807,21 +10807,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436425</v>
+        <v>436310</v>
       </c>
       <c r="R103" t="n">
-        <v>6786192</v>
+        <v>6786196</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10893,7 +10893,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129058401</v>
+        <v>129058390</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -10928,10 +10928,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436310</v>
+        <v>436700</v>
       </c>
       <c r="R104" t="n">
-        <v>6786196</v>
+        <v>6785944</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11087,54 +11087,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058324</v>
+        <v>129058406</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436254</v>
+        <v>436222</v>
       </c>
       <c r="R106" t="n">
-        <v>6786130</v>
+        <v>6786238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11175,7 +11166,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11194,7 +11184,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058358</v>
+        <v>129058366</v>
       </c>
       <c r="B107" t="n">
         <v>78798</v>
@@ -11229,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436550</v>
+        <v>436357</v>
       </c>
       <c r="R107" t="n">
-        <v>6785988</v>
+        <v>6786208</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11291,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058366</v>
+        <v>129058393</v>
       </c>
       <c r="B108" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11302,21 +11292,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11326,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436357</v>
+        <v>436507</v>
       </c>
       <c r="R108" t="n">
-        <v>6786208</v>
+        <v>6786023</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11388,45 +11378,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058406</v>
+        <v>129058324</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436222</v>
+        <v>436254</v>
       </c>
       <c r="R109" t="n">
-        <v>6786238</v>
+        <v>6786130</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11467,6 +11466,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11485,10 +11485,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129058393</v>
+        <v>129058358</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11496,21 +11496,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436507</v>
+        <v>436550</v>
       </c>
       <c r="R110" t="n">
-        <v>6786023</v>
+        <v>6785988</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11582,40 +11582,41 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058289</v>
+        <v>129058328</v>
       </c>
       <c r="B111" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11625,10 +11626,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436486</v>
+        <v>436701</v>
       </c>
       <c r="R111" t="n">
-        <v>6786231</v>
+        <v>6785838</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11669,6 +11670,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11784,41 +11786,40 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058328</v>
+        <v>129058289</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -11828,10 +11829,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436701</v>
+        <v>436486</v>
       </c>
       <c r="R113" t="n">
-        <v>6785838</v>
+        <v>6786231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11872,7 +11873,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129080323</v>
+        <v>129080292</v>
       </c>
       <c r="B116" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,21 +12105,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436382</v>
+        <v>436532</v>
       </c>
       <c r="R116" t="n">
-        <v>6786202</v>
+        <v>6785865</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12191,10 +12191,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080278</v>
+        <v>129080329</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12202,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436513</v>
+        <v>436247</v>
       </c>
       <c r="R117" t="n">
-        <v>6785962</v>
+        <v>6786289</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,6 +12262,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12288,10 +12293,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080329</v>
+        <v>129080323</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12299,21 +12304,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12323,10 +12328,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436247</v>
+        <v>436382</v>
       </c>
       <c r="R118" t="n">
-        <v>6786289</v>
+        <v>6786202</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,11 +12364,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12390,10 +12390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129080292</v>
+        <v>129080278</v>
       </c>
       <c r="B119" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,21 +12401,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436532</v>
+        <v>436513</v>
       </c>
       <c r="R119" t="n">
-        <v>6785865</v>
+        <v>6785962</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080295</v>
+        <v>129080302</v>
       </c>
       <c r="B120" t="n">
-        <v>78799</v>
+        <v>91562</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436815</v>
+        <v>436320</v>
       </c>
       <c r="R120" t="n">
-        <v>6785768</v>
+        <v>6786132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,6 +12566,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12584,10 +12585,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080291</v>
+        <v>129080277</v>
       </c>
       <c r="B121" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,21 +12596,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12619,10 +12620,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436524</v>
+        <v>436561</v>
       </c>
       <c r="R121" t="n">
-        <v>6785865</v>
+        <v>6785959</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12681,7 +12682,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129080294</v>
+        <v>129080295</v>
       </c>
       <c r="B122" t="n">
         <v>78799</v>
@@ -12716,10 +12717,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436659</v>
+        <v>436815</v>
       </c>
       <c r="R122" t="n">
-        <v>6785808</v>
+        <v>6785768</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12778,10 +12779,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080302</v>
+        <v>129080291</v>
       </c>
       <c r="B123" t="n">
-        <v>91562</v>
+        <v>78799</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12789,21 +12790,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12813,10 +12814,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436320</v>
+        <v>436524</v>
       </c>
       <c r="R123" t="n">
-        <v>6786132</v>
+        <v>6785865</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12857,7 +12858,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12876,10 +12876,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080277</v>
+        <v>129080294</v>
       </c>
       <c r="B124" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,21 +12887,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436561</v>
+        <v>436659</v>
       </c>
       <c r="R124" t="n">
-        <v>6785959</v>
+        <v>6785808</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129080301</v>
+        <v>129080279</v>
       </c>
       <c r="B134" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436246</v>
+        <v>436471</v>
       </c>
       <c r="R134" t="n">
-        <v>6786298</v>
+        <v>6786142</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129080279</v>
+        <v>129080301</v>
       </c>
       <c r="B135" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436471</v>
+        <v>436246</v>
       </c>
       <c r="R135" t="n">
-        <v>6786142</v>
+        <v>6786298</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14137,7 +14137,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080316</v>
+        <v>129080317</v>
       </c>
       <c r="B137" t="n">
         <v>78798</v>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436532</v>
+        <v>436816</v>
       </c>
       <c r="R137" t="n">
-        <v>6785867</v>
+        <v>6785768</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,7 +14234,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080317</v>
+        <v>129080316</v>
       </c>
       <c r="B138" t="n">
         <v>78798</v>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436816</v>
+        <v>436532</v>
       </c>
       <c r="R138" t="n">
-        <v>6785768</v>
+        <v>6785867</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14719,54 +14719,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080312</v>
+        <v>129080327</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436296</v>
+        <v>436653</v>
       </c>
       <c r="R143" t="n">
-        <v>6786185</v>
+        <v>6785861</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14807,7 +14798,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15020,45 +15010,54 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080327</v>
+        <v>129080312</v>
       </c>
       <c r="B146" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436653</v>
+        <v>436296</v>
       </c>
       <c r="R146" t="n">
-        <v>6785861</v>
+        <v>6786185</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15099,6 +15098,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080283</v>
+        <v>129080297</v>
       </c>
       <c r="B149" t="n">
-        <v>91542</v>
+        <v>78799</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436434</v>
+        <v>436449</v>
       </c>
       <c r="R149" t="n">
-        <v>6786112</v>
+        <v>6786210</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15384,18 +15384,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15414,10 +15408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080297</v>
+        <v>129080283</v>
       </c>
       <c r="B150" t="n">
-        <v>78799</v>
+        <v>91542</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15425,21 +15419,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15449,10 +15443,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436449</v>
+        <v>436434</v>
       </c>
       <c r="R150" t="n">
-        <v>6786210</v>
+        <v>6786112</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15487,12 +15481,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16336,41 +16336,40 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080310</v>
+        <v>129080287</v>
       </c>
       <c r="B159" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16380,10 +16379,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436472</v>
+        <v>436471</v>
       </c>
       <c r="R159" t="n">
-        <v>6786160</v>
+        <v>6786165</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16424,7 +16423,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16443,7 +16441,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080305</v>
+        <v>129080311</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16487,10 +16485,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436474</v>
+        <v>436449</v>
       </c>
       <c r="R160" t="n">
-        <v>6785946</v>
+        <v>6786212</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16550,7 +16548,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129080311</v>
+        <v>129080305</v>
       </c>
       <c r="B161" t="n">
         <v>8450</v>
@@ -16594,10 +16592,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>436449</v>
+        <v>436474</v>
       </c>
       <c r="R161" t="n">
-        <v>6786212</v>
+        <v>6785946</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16657,40 +16655,41 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080287</v>
+        <v>129080310</v>
       </c>
       <c r="B162" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16700,10 +16699,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436471</v>
+        <v>436472</v>
       </c>
       <c r="R162" t="n">
-        <v>6786165</v>
+        <v>6786160</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16744,6 +16743,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -16867,7 +16867,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080308</v>
+        <v>129080309</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16911,10 +16911,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436807</v>
+        <v>436571</v>
       </c>
       <c r="R164" t="n">
-        <v>6785797</v>
+        <v>6785936</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16974,7 +16974,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080309</v>
+        <v>129080308</v>
       </c>
       <c r="B165" t="n">
         <v>8450</v>
@@ -17018,10 +17018,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436571</v>
+        <v>436807</v>
       </c>
       <c r="R165" t="n">
-        <v>6785936</v>
+        <v>6785797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058299</v>
+        <v>129058331</v>
       </c>
       <c r="B2" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436545</v>
+        <v>436755</v>
       </c>
       <c r="R2" t="n">
-        <v>6785800</v>
+        <v>6785905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058303</v>
+        <v>129058341</v>
       </c>
       <c r="B3" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436818</v>
+        <v>436278</v>
       </c>
       <c r="R3" t="n">
-        <v>6785831</v>
+        <v>6786206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1063,54 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058331</v>
+        <v>129058299</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436755</v>
+        <v>436545</v>
       </c>
       <c r="R6" t="n">
-        <v>6785905</v>
+        <v>6785800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1170,54 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058341</v>
+        <v>129058303</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436278</v>
+        <v>436818</v>
       </c>
       <c r="R7" t="n">
-        <v>6786206</v>
+        <v>6785831</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,7 +1259,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -3084,43 +3084,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058343</v>
+        <v>129058272</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3128,10 +3122,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436269</v>
+        <v>436369</v>
       </c>
       <c r="R26" t="n">
-        <v>6786228</v>
+        <v>6786195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3191,41 +3185,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058327</v>
+        <v>129058287</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3235,10 +3228,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436674</v>
+        <v>436718</v>
       </c>
       <c r="R27" t="n">
-        <v>6785802</v>
+        <v>6785941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3279,7 +3272,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3298,45 +3290,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058311</v>
+        <v>129058343</v>
       </c>
       <c r="B28" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436530</v>
+        <v>436269</v>
       </c>
       <c r="R28" t="n">
-        <v>6785992</v>
+        <v>6786228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3377,6 +3378,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3395,37 +3397,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058272</v>
+        <v>129058327</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3433,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436369</v>
+        <v>436674</v>
       </c>
       <c r="R29" t="n">
-        <v>6786195</v>
+        <v>6785802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3496,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058287</v>
+        <v>129058311</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3507,42 +3515,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436718</v>
+        <v>436530</v>
       </c>
       <c r="R30" t="n">
-        <v>6785941</v>
+        <v>6785992</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4005,45 +4005,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058262</v>
+        <v>129058325</v>
       </c>
       <c r="B35" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436534</v>
+        <v>436443</v>
       </c>
       <c r="R35" t="n">
-        <v>6785834</v>
+        <v>6785940</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4084,6 +4093,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4102,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058269</v>
+        <v>129058318</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,34 +4123,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436483</v>
+        <v>436354</v>
       </c>
       <c r="R36" t="n">
-        <v>6786017</v>
+        <v>6786212</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4181,6 +4194,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4199,7 +4213,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058277</v>
+        <v>129058262</v>
       </c>
       <c r="B37" t="n">
         <v>79660</v>
@@ -4228,19 +4242,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436351</v>
+        <v>436534</v>
       </c>
       <c r="R37" t="n">
-        <v>6786185</v>
+        <v>6785834</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4292,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4300,10 +4310,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058404</v>
+        <v>129058269</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4311,21 +4321,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4345,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436229</v>
+        <v>436483</v>
       </c>
       <c r="R38" t="n">
-        <v>6786238</v>
+        <v>6786017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,10 +4407,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058348</v>
+        <v>129058277</v>
       </c>
       <c r="B39" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4408,34 +4418,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436266</v>
+        <v>436351</v>
       </c>
       <c r="R39" t="n">
-        <v>6786145</v>
+        <v>6786185</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,6 +4489,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4508,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058357</v>
+        <v>129058404</v>
       </c>
       <c r="B40" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,21 +4519,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4529,10 +4543,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436686</v>
+        <v>436229</v>
       </c>
       <c r="R40" t="n">
-        <v>6785940</v>
+        <v>6786238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,10 +4605,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058278</v>
+        <v>129058348</v>
       </c>
       <c r="B41" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4616,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4640,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436295</v>
+        <v>436266</v>
       </c>
       <c r="R41" t="n">
-        <v>6786172</v>
+        <v>6786145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4688,51 +4702,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058325</v>
+        <v>129058357</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436443</v>
+        <v>436686</v>
       </c>
       <c r="R42" t="n">
         <v>6785940</v>
@@ -4776,7 +4781,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4795,10 +4799,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058318</v>
+        <v>129058278</v>
       </c>
       <c r="B43" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4806,37 +4810,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436354</v>
+        <v>436295</v>
       </c>
       <c r="R43" t="n">
-        <v>6786212</v>
+        <v>6786172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4877,7 +4878,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058389</v>
+        <v>129058361</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,37 +6608,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436739</v>
+        <v>436500</v>
       </c>
       <c r="R61" t="n">
-        <v>6785902</v>
+        <v>6786018</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6673,18 +6670,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6703,10 +6694,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058271</v>
+        <v>129058389</v>
       </c>
       <c r="B62" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6714,34 +6705,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436493</v>
+        <v>436739</v>
       </c>
       <c r="R62" t="n">
-        <v>6786189</v>
+        <v>6785902</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6776,12 +6770,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058361</v>
+        <v>129058405</v>
       </c>
       <c r="B63" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6811,21 +6811,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436500</v>
+        <v>436227</v>
       </c>
       <c r="R63" t="n">
-        <v>6786018</v>
+        <v>6786243</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6897,10 +6897,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058405</v>
+        <v>129058353</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6908,21 +6908,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436227</v>
+        <v>436551</v>
       </c>
       <c r="R64" t="n">
-        <v>6786243</v>
+        <v>6785765</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058353</v>
+        <v>129058271</v>
       </c>
       <c r="B65" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7005,21 +7005,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436551</v>
+        <v>436493</v>
       </c>
       <c r="R65" t="n">
-        <v>6785765</v>
+        <v>6786189</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058411</v>
+        <v>129058346</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436461</v>
+        <v>436503</v>
       </c>
       <c r="R90" t="n">
-        <v>6785881</v>
+        <v>6786136</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058398</v>
+        <v>129058314</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436425</v>
+        <v>436510</v>
       </c>
       <c r="R91" t="n">
-        <v>6786210</v>
+        <v>6786074</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,7 +9700,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058387</v>
+        <v>129058411</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436805</v>
+        <v>436461</v>
       </c>
       <c r="R92" t="n">
-        <v>6785785</v>
+        <v>6785881</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058346</v>
+        <v>129058398</v>
       </c>
       <c r="B93" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436503</v>
+        <v>436425</v>
       </c>
       <c r="R93" t="n">
-        <v>6786136</v>
+        <v>6786210</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058314</v>
+        <v>129058387</v>
       </c>
       <c r="B94" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436510</v>
+        <v>436805</v>
       </c>
       <c r="R94" t="n">
-        <v>6786074</v>
+        <v>6785785</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9991,45 +9991,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058407</v>
+        <v>129058333</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436215</v>
+        <v>436432</v>
       </c>
       <c r="R95" t="n">
-        <v>6786222</v>
+        <v>6786210</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,6 +10079,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10088,37 +10098,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058416</v>
+        <v>129058345</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10126,10 +10142,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436491</v>
+        <v>436269</v>
       </c>
       <c r="R96" t="n">
-        <v>6786146</v>
+        <v>6786257</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10162,11 +10178,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10388,54 +10399,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058333</v>
+        <v>129058407</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436432</v>
+        <v>436215</v>
       </c>
       <c r="R99" t="n">
-        <v>6786210</v>
+        <v>6786222</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10476,7 +10478,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10495,43 +10496,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058345</v>
+        <v>129058416</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10539,10 +10534,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436269</v>
+        <v>436491</v>
       </c>
       <c r="R100" t="n">
-        <v>6786257</v>
+        <v>6786146</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10575,6 +10570,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12191,10 +12191,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080329</v>
+        <v>129080278</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12202,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436247</v>
+        <v>436513</v>
       </c>
       <c r="R117" t="n">
-        <v>6786289</v>
+        <v>6785962</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,11 +12262,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12293,10 +12288,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080323</v>
+        <v>129080329</v>
       </c>
       <c r="B118" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12304,21 +12299,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12328,10 +12323,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436382</v>
+        <v>436247</v>
       </c>
       <c r="R118" t="n">
-        <v>6786202</v>
+        <v>6786289</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,6 +12359,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12390,10 +12390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129080278</v>
+        <v>129080323</v>
       </c>
       <c r="B119" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,21 +12401,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436513</v>
+        <v>436382</v>
       </c>
       <c r="R119" t="n">
-        <v>6785962</v>
+        <v>6786202</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13167,10 +13167,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129080281</v>
+        <v>129080298</v>
       </c>
       <c r="B127" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436448</v>
+        <v>436428</v>
       </c>
       <c r="R127" t="n">
-        <v>6786211</v>
+        <v>6786194</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R128" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080298</v>
+        <v>129080281</v>
       </c>
       <c r="B129" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13372,21 +13372,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436428</v>
+        <v>436448</v>
       </c>
       <c r="R129" t="n">
-        <v>6786194</v>
+        <v>6786211</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B130" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R130" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B131" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R131" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B132" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R132" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14719,45 +14719,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080327</v>
+        <v>129080312</v>
       </c>
       <c r="B143" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436653</v>
+        <v>436296</v>
       </c>
       <c r="R143" t="n">
-        <v>6785861</v>
+        <v>6786185</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14798,6 +14807,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15010,54 +15020,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080312</v>
+        <v>129080327</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436296</v>
+        <v>436653</v>
       </c>
       <c r="R146" t="n">
-        <v>6786185</v>
+        <v>6785861</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15098,7 +15099,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16762,40 +16762,41 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080286</v>
+        <v>129080309</v>
       </c>
       <c r="B163" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16805,10 +16806,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436572</v>
+        <v>436571</v>
       </c>
       <c r="R163" t="n">
-        <v>6785762</v>
+        <v>6785936</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16849,6 +16850,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16867,7 +16869,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080309</v>
+        <v>129080308</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16911,10 +16913,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436571</v>
+        <v>436807</v>
       </c>
       <c r="R164" t="n">
-        <v>6785936</v>
+        <v>6785797</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16974,41 +16976,40 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080308</v>
+        <v>129080286</v>
       </c>
       <c r="B165" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17018,10 +17019,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436807</v>
+        <v>436572</v>
       </c>
       <c r="R165" t="n">
-        <v>6785797</v>
+        <v>6785762</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17062,7 +17063,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058331</v>
+        <v>129058274</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436755</v>
+        <v>436522</v>
       </c>
       <c r="R2" t="n">
-        <v>6785905</v>
+        <v>6786062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058341</v>
+        <v>129058412</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436278</v>
+        <v>436564</v>
       </c>
       <c r="R3" t="n">
-        <v>6786206</v>
+        <v>6785776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058274</v>
+        <v>129058331</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436522</v>
+        <v>436755</v>
       </c>
       <c r="R4" t="n">
-        <v>6786062</v>
+        <v>6785905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +957,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,45 +976,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058412</v>
+        <v>129058341</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436564</v>
+        <v>436278</v>
       </c>
       <c r="R5" t="n">
-        <v>6785776</v>
+        <v>6786206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1064,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1577,54 +1577,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058337</v>
+        <v>129058304</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436322</v>
+        <v>436683</v>
       </c>
       <c r="R11" t="n">
-        <v>6786198</v>
+        <v>6785939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1656,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,7 +1674,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058329</v>
+        <v>129058336</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1718,7 +1708,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1728,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436754</v>
+        <v>436336</v>
       </c>
       <c r="R12" t="n">
-        <v>6785822</v>
+        <v>6786183</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,7 +1781,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058336</v>
+        <v>129058329</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1825,7 +1815,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1835,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436336</v>
+        <v>436754</v>
       </c>
       <c r="R13" t="n">
-        <v>6786183</v>
+        <v>6785822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,45 +1888,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058304</v>
+        <v>129058337</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436683</v>
+        <v>436322</v>
       </c>
       <c r="R14" t="n">
-        <v>6785939</v>
+        <v>6786198</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,6 +1976,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2092,45 +2092,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058382</v>
+        <v>129058332</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436214</v>
+        <v>436648</v>
       </c>
       <c r="R16" t="n">
-        <v>6786180</v>
+        <v>6785874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,6 +2180,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2189,10 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058403</v>
+        <v>129058301</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2210,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436259</v>
+        <v>436796</v>
       </c>
       <c r="R17" t="n">
-        <v>6786285</v>
+        <v>6785778</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058365</v>
+        <v>129058317</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,34 +2307,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436467</v>
+        <v>436356</v>
       </c>
       <c r="R18" t="n">
-        <v>6786236</v>
+        <v>6786224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,6 +2378,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2383,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058286</v>
+        <v>129058307</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,42 +2408,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436617</v>
+        <v>436597</v>
       </c>
       <c r="R19" t="n">
-        <v>6785749</v>
+        <v>6785981</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,54 +2494,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058332</v>
+        <v>129058308</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436648</v>
+        <v>436545</v>
       </c>
       <c r="R20" t="n">
-        <v>6785874</v>
+        <v>6785997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2573,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2591,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058301</v>
+        <v>129058280</v>
       </c>
       <c r="B21" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2606,21 +2602,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2630,10 +2626,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436796</v>
+        <v>436519</v>
       </c>
       <c r="R21" t="n">
-        <v>6785778</v>
+        <v>6785988</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,10 +2688,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058317</v>
+        <v>129058382</v>
       </c>
       <c r="B22" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2703,37 +2699,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436356</v>
+        <v>436214</v>
       </c>
       <c r="R22" t="n">
-        <v>6786224</v>
+        <v>6786180</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,7 +2767,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2793,10 +2785,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058307</v>
+        <v>129058403</v>
       </c>
       <c r="B23" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,21 +2796,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2828,10 +2820,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436597</v>
+        <v>436259</v>
       </c>
       <c r="R23" t="n">
-        <v>6785981</v>
+        <v>6786285</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2890,10 +2882,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058308</v>
+        <v>129058365</v>
       </c>
       <c r="B24" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2901,21 +2893,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2925,10 +2917,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436545</v>
+        <v>436467</v>
       </c>
       <c r="R24" t="n">
-        <v>6785997</v>
+        <v>6786236</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,10 +2979,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058280</v>
+        <v>129058286</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2998,34 +2990,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436519</v>
+        <v>436617</v>
       </c>
       <c r="R25" t="n">
-        <v>6785988</v>
+        <v>6785749</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058369</v>
+        <v>129058288</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,34 +3612,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436817</v>
+        <v>436458</v>
       </c>
       <c r="R31" t="n">
-        <v>6785838</v>
+        <v>6786194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3698,10 +3706,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058288</v>
+        <v>129058273</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3709,31 +3717,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3741,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436458</v>
+        <v>436257</v>
       </c>
       <c r="R32" t="n">
-        <v>6786194</v>
+        <v>6786288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3785,6 +3788,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3803,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058273</v>
+        <v>129058369</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3814,37 +3818,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436257</v>
+        <v>436817</v>
       </c>
       <c r="R33" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,7 +3886,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4005,54 +4005,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058325</v>
+        <v>129058262</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436443</v>
+        <v>436534</v>
       </c>
       <c r="R35" t="n">
-        <v>6785940</v>
+        <v>6785834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,7 +4084,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4112,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058318</v>
+        <v>129058269</v>
       </c>
       <c r="B36" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,37 +4113,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436354</v>
+        <v>436483</v>
       </c>
       <c r="R36" t="n">
-        <v>6786212</v>
+        <v>6786017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,7 +4181,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4213,7 +4199,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058262</v>
+        <v>129058277</v>
       </c>
       <c r="B37" t="n">
         <v>79660</v>
@@ -4242,16 +4228,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436534</v>
+        <v>436351</v>
       </c>
       <c r="R37" t="n">
-        <v>6785834</v>
+        <v>6786185</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4292,6 +4281,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4310,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058269</v>
+        <v>129058404</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4321,21 +4311,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4345,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436483</v>
+        <v>436229</v>
       </c>
       <c r="R38" t="n">
-        <v>6786017</v>
+        <v>6786238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4407,10 +4397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058277</v>
+        <v>129058348</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4418,37 +4408,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436351</v>
+        <v>436266</v>
       </c>
       <c r="R39" t="n">
-        <v>6786185</v>
+        <v>6786145</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,7 +4476,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4508,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058404</v>
+        <v>129058357</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4519,21 +4505,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4543,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436229</v>
+        <v>436686</v>
       </c>
       <c r="R40" t="n">
-        <v>6786238</v>
+        <v>6785940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4605,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058348</v>
+        <v>129058278</v>
       </c>
       <c r="B41" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4616,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4640,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436266</v>
+        <v>436295</v>
       </c>
       <c r="R41" t="n">
-        <v>6786145</v>
+        <v>6786172</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4702,42 +4688,51 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058357</v>
+        <v>129058325</v>
       </c>
       <c r="B42" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436686</v>
+        <v>436443</v>
       </c>
       <c r="R42" t="n">
         <v>6785940</v>
@@ -4781,6 +4776,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4799,10 +4795,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058278</v>
+        <v>129058318</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4810,34 +4806,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436295</v>
+        <v>436354</v>
       </c>
       <c r="R43" t="n">
-        <v>6786172</v>
+        <v>6786212</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4878,6 +4877,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129058351</v>
+        <v>129058297</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436516</v>
+        <v>436509</v>
       </c>
       <c r="R45" t="n">
         <v>6785859</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129058297</v>
+        <v>129058313</v>
       </c>
       <c r="B46" t="n">
         <v>78799</v>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436509</v>
+        <v>436504</v>
       </c>
       <c r="R46" t="n">
-        <v>6785859</v>
+        <v>6786023</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129058313</v>
+        <v>129058351</v>
       </c>
       <c r="B47" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436504</v>
+        <v>436516</v>
       </c>
       <c r="R47" t="n">
-        <v>6786023</v>
+        <v>6785859</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058395</v>
+        <v>129058290</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,34 +5295,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436504</v>
+        <v>436601</v>
       </c>
       <c r="R48" t="n">
-        <v>6786102</v>
+        <v>6785947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5389,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058385</v>
+        <v>129058309</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,21 +5400,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5416,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436327</v>
+        <v>436532</v>
       </c>
       <c r="R49" t="n">
-        <v>6786086</v>
+        <v>6785994</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058268</v>
+        <v>129058395</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,7 +5524,7 @@
         <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6786023</v>
+        <v>6786102</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5583,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058386</v>
+        <v>129058385</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5610,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436505</v>
+        <v>436327</v>
       </c>
       <c r="R51" t="n">
-        <v>6785856</v>
+        <v>6786086</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058290</v>
+        <v>129058268</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,42 +5691,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436601</v>
+        <v>436504</v>
       </c>
       <c r="R52" t="n">
-        <v>6785947</v>
+        <v>6786023</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058309</v>
+        <v>129058386</v>
       </c>
       <c r="B53" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436532</v>
+        <v>436505</v>
       </c>
       <c r="R53" t="n">
-        <v>6785994</v>
+        <v>6785856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058323</v>
+        <v>129058335</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7240,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436241</v>
+        <v>436360</v>
       </c>
       <c r="R67" t="n">
-        <v>6786159</v>
+        <v>6786231</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,7 +7303,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058330</v>
+        <v>129058340</v>
       </c>
       <c r="B68" t="n">
         <v>8450</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436823</v>
+        <v>436324</v>
       </c>
       <c r="R68" t="n">
-        <v>6785756</v>
+        <v>6786220</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058340</v>
+        <v>129058330</v>
       </c>
       <c r="B69" t="n">
         <v>8450</v>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436324</v>
+        <v>436823</v>
       </c>
       <c r="R69" t="n">
-        <v>6786220</v>
+        <v>6785756</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058335</v>
+        <v>129058323</v>
       </c>
       <c r="B70" t="n">
         <v>8450</v>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436360</v>
+        <v>436241</v>
       </c>
       <c r="R70" t="n">
-        <v>6786231</v>
+        <v>6786159</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7624,54 +7624,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058334</v>
+        <v>129058267</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436373</v>
+        <v>436524</v>
       </c>
       <c r="R71" t="n">
-        <v>6786190</v>
+        <v>6785977</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7703,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7731,10 +7721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058305</v>
+        <v>129058362</v>
       </c>
       <c r="B72" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7742,37 +7732,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436680</v>
+        <v>436494</v>
       </c>
       <c r="R72" t="n">
-        <v>6785902</v>
+        <v>6786028</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7813,7 +7800,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7832,7 +7818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058267</v>
+        <v>129058264</v>
       </c>
       <c r="B73" t="n">
         <v>79660</v>
@@ -7867,10 +7853,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436524</v>
+        <v>436599</v>
       </c>
       <c r="R73" t="n">
-        <v>6785977</v>
+        <v>6785738</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,7 +7915,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058362</v>
+        <v>129058354</v>
       </c>
       <c r="B74" t="n">
         <v>78798</v>
@@ -7964,10 +7950,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436494</v>
+        <v>436796</v>
       </c>
       <c r="R74" t="n">
-        <v>6786028</v>
+        <v>6785778</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8026,10 +8012,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058264</v>
+        <v>129058359</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,21 +8023,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8047,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436599</v>
+        <v>436532</v>
       </c>
       <c r="R75" t="n">
-        <v>6785738</v>
+        <v>6785994</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,7 +8109,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058354</v>
+        <v>129058367</v>
       </c>
       <c r="B76" t="n">
         <v>78798</v>
@@ -8158,10 +8144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436796</v>
+        <v>436371</v>
       </c>
       <c r="R76" t="n">
-        <v>6785778</v>
+        <v>6786199</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8206,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058359</v>
+        <v>129058334</v>
       </c>
       <c r="B77" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436532</v>
+        <v>436373</v>
       </c>
       <c r="R77" t="n">
-        <v>6785994</v>
+        <v>6786190</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8299,6 +8294,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8317,10 +8313,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058367</v>
+        <v>129058305</v>
       </c>
       <c r="B78" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,34 +8324,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436371</v>
+        <v>436680</v>
       </c>
       <c r="R78" t="n">
-        <v>6786199</v>
+        <v>6785902</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8396,6 +8395,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058315</v>
+        <v>129058355</v>
       </c>
       <c r="B79" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,34 +8425,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436445</v>
+        <v>436825</v>
       </c>
       <c r="R79" t="n">
-        <v>6786210</v>
+        <v>6785764</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8493,6 +8496,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8511,10 +8515,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058355</v>
+        <v>129058394</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,37 +8526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436825</v>
+        <v>436493</v>
       </c>
       <c r="R80" t="n">
-        <v>6785764</v>
+        <v>6786075</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,7 +8594,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058394</v>
+        <v>129058356</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,21 +8623,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436493</v>
+        <v>436818</v>
       </c>
       <c r="R81" t="n">
-        <v>6786075</v>
+        <v>6785831</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058356</v>
+        <v>129058282</v>
       </c>
       <c r="B82" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,34 +8720,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436818</v>
+        <v>436515</v>
       </c>
       <c r="R82" t="n">
-        <v>6785831</v>
+        <v>6786055</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8806,10 +8814,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058282</v>
+        <v>129058315</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,42 +8825,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436515</v>
+        <v>436445</v>
       </c>
       <c r="R83" t="n">
-        <v>6786055</v>
+        <v>6786210</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058346</v>
+        <v>129058411</v>
       </c>
       <c r="B90" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436503</v>
+        <v>436461</v>
       </c>
       <c r="R90" t="n">
-        <v>6786136</v>
+        <v>6785881</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058314</v>
+        <v>129058398</v>
       </c>
       <c r="B91" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436510</v>
+        <v>436425</v>
       </c>
       <c r="R91" t="n">
-        <v>6786074</v>
+        <v>6786210</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,7 +9700,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058411</v>
+        <v>129058387</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436461</v>
+        <v>436805</v>
       </c>
       <c r="R92" t="n">
-        <v>6785881</v>
+        <v>6785785</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058398</v>
+        <v>129058346</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436425</v>
+        <v>436503</v>
       </c>
       <c r="R93" t="n">
-        <v>6786210</v>
+        <v>6786136</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058387</v>
+        <v>129058314</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436805</v>
+        <v>436510</v>
       </c>
       <c r="R94" t="n">
-        <v>6785785</v>
+        <v>6786074</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058333</v>
+        <v>129058345</v>
       </c>
       <c r="B95" t="n">
         <v>8450</v>
@@ -10025,7 +10025,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436432</v>
+        <v>436269</v>
       </c>
       <c r="R95" t="n">
-        <v>6786210</v>
+        <v>6786257</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10098,7 +10098,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058345</v>
+        <v>129058333</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10132,7 +10132,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10142,10 +10142,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436269</v>
+        <v>436432</v>
       </c>
       <c r="R96" t="n">
-        <v>6786257</v>
+        <v>6786210</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10205,10 +10205,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058298</v>
+        <v>129058407</v>
       </c>
       <c r="B97" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10216,21 +10216,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436513</v>
+        <v>436215</v>
       </c>
       <c r="R97" t="n">
-        <v>6785845</v>
+        <v>6786222</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10302,10 +10302,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058300</v>
+        <v>129058416</v>
       </c>
       <c r="B98" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10313,34 +10313,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436554</v>
+        <v>436491</v>
       </c>
       <c r="R98" t="n">
-        <v>6785764</v>
+        <v>6786146</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10375,12 +10378,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10399,10 +10408,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058407</v>
+        <v>129058298</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10410,21 +10419,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10434,10 +10443,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436215</v>
+        <v>436513</v>
       </c>
       <c r="R99" t="n">
-        <v>6786222</v>
+        <v>6785845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10496,10 +10505,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058416</v>
+        <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10507,37 +10516,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436491</v>
+        <v>436554</v>
       </c>
       <c r="R100" t="n">
-        <v>6786146</v>
+        <v>6785764</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10572,18 +10578,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11087,45 +11087,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058406</v>
+        <v>129058324</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436222</v>
+        <v>436254</v>
       </c>
       <c r="R106" t="n">
-        <v>6786238</v>
+        <v>6786130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11166,6 +11175,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11184,10 +11194,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058366</v>
+        <v>129058406</v>
       </c>
       <c r="B107" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11195,21 +11205,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11219,10 +11229,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436357</v>
+        <v>436222</v>
       </c>
       <c r="R107" t="n">
-        <v>6786208</v>
+        <v>6786238</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11281,10 +11291,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058393</v>
+        <v>129058366</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11292,21 +11302,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11316,10 +11326,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436507</v>
+        <v>436357</v>
       </c>
       <c r="R108" t="n">
-        <v>6786023</v>
+        <v>6786208</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11378,54 +11388,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058324</v>
+        <v>129058393</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436254</v>
+        <v>436507</v>
       </c>
       <c r="R109" t="n">
-        <v>6786130</v>
+        <v>6786023</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11466,7 +11467,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11582,41 +11582,40 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058328</v>
+        <v>129058289</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -11626,10 +11625,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436701</v>
+        <v>436486</v>
       </c>
       <c r="R111" t="n">
-        <v>6785838</v>
+        <v>6786231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11670,7 +11669,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11786,40 +11784,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058289</v>
+        <v>129058328</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -11829,10 +11828,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436486</v>
+        <v>436701</v>
       </c>
       <c r="R113" t="n">
-        <v>6786231</v>
+        <v>6785838</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11873,6 +11872,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129080292</v>
+        <v>129080278</v>
       </c>
       <c r="B116" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,21 +12105,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436532</v>
+        <v>436513</v>
       </c>
       <c r="R116" t="n">
-        <v>6785865</v>
+        <v>6785962</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12191,10 +12191,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080278</v>
+        <v>129080329</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12202,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436513</v>
+        <v>436247</v>
       </c>
       <c r="R117" t="n">
-        <v>6785962</v>
+        <v>6786289</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,6 +12262,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12288,10 +12293,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080329</v>
+        <v>129080323</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12299,21 +12304,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12323,10 +12328,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436247</v>
+        <v>436382</v>
       </c>
       <c r="R118" t="n">
-        <v>6786289</v>
+        <v>6786202</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,11 +12364,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12390,10 +12390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129080323</v>
+        <v>129080292</v>
       </c>
       <c r="B119" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,21 +12401,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436382</v>
+        <v>436532</v>
       </c>
       <c r="R119" t="n">
-        <v>6786202</v>
+        <v>6785865</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080302</v>
+        <v>129080277</v>
       </c>
       <c r="B120" t="n">
-        <v>91562</v>
+        <v>79660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436320</v>
+        <v>436561</v>
       </c>
       <c r="R120" t="n">
-        <v>6786132</v>
+        <v>6785959</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,7 +12566,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12585,10 +12584,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080277</v>
+        <v>129080302</v>
       </c>
       <c r="B121" t="n">
-        <v>79660</v>
+        <v>91560</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12596,21 +12595,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12620,10 +12619,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436561</v>
+        <v>436320</v>
       </c>
       <c r="R121" t="n">
-        <v>6785959</v>
+        <v>6786132</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12664,6 +12663,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13167,10 +13167,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129080298</v>
+        <v>129080281</v>
       </c>
       <c r="B127" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436428</v>
+        <v>436448</v>
       </c>
       <c r="R127" t="n">
-        <v>6786194</v>
+        <v>6786211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B128" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R128" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080281</v>
+        <v>129080298</v>
       </c>
       <c r="B129" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13372,21 +13372,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436448</v>
+        <v>436428</v>
       </c>
       <c r="R129" t="n">
-        <v>6786211</v>
+        <v>6786194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R130" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B131" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R131" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B132" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R132" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129080279</v>
+        <v>129080301</v>
       </c>
       <c r="B134" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436471</v>
+        <v>436246</v>
       </c>
       <c r="R134" t="n">
-        <v>6786142</v>
+        <v>6786298</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129080301</v>
+        <v>129080279</v>
       </c>
       <c r="B135" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436246</v>
+        <v>436471</v>
       </c>
       <c r="R135" t="n">
-        <v>6786298</v>
+        <v>6786142</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14043,7 +14043,7 @@
         <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080300</v>
+        <v>129080299</v>
       </c>
       <c r="B144" t="n">
         <v>78799</v>
@@ -14861,10 +14861,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436333</v>
+        <v>436384</v>
       </c>
       <c r="R144" t="n">
-        <v>6786167</v>
+        <v>6786203</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14923,10 +14923,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129080299</v>
+        <v>129080327</v>
       </c>
       <c r="B145" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14934,21 +14934,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14958,10 +14958,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>436384</v>
+        <v>436653</v>
       </c>
       <c r="R145" t="n">
-        <v>6786203</v>
+        <v>6785861</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15020,10 +15020,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080327</v>
+        <v>129080300</v>
       </c>
       <c r="B146" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15031,21 +15031,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436653</v>
+        <v>436333</v>
       </c>
       <c r="R146" t="n">
-        <v>6785861</v>
+        <v>6786167</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080297</v>
+        <v>129080282</v>
       </c>
       <c r="B149" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436449</v>
+        <v>436335</v>
       </c>
       <c r="R149" t="n">
-        <v>6786210</v>
+        <v>6786163</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15408,10 +15408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080283</v>
+        <v>129080297</v>
       </c>
       <c r="B150" t="n">
-        <v>91542</v>
+        <v>78799</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15419,21 +15419,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15443,10 +15443,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436434</v>
+        <v>436449</v>
       </c>
       <c r="R150" t="n">
-        <v>6786112</v>
+        <v>6786210</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15481,18 +15481,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15511,10 +15505,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080331</v>
+        <v>129080283</v>
       </c>
       <c r="B151" t="n">
-        <v>88939</v>
+        <v>91540</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15522,21 +15516,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15546,10 +15540,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436491</v>
+        <v>436434</v>
       </c>
       <c r="R151" t="n">
-        <v>6786094</v>
+        <v>6786112</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15582,6 +15576,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15609,10 +15608,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080282</v>
+        <v>129080331</v>
       </c>
       <c r="B152" t="n">
-        <v>79660</v>
+        <v>88940</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15619,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15643,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436335</v>
+        <v>436491</v>
       </c>
       <c r="R152" t="n">
-        <v>6786163</v>
+        <v>6786094</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15688,6 +15687,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16336,40 +16336,41 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080287</v>
+        <v>129080310</v>
       </c>
       <c r="B159" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16379,10 +16380,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436471</v>
+        <v>436472</v>
       </c>
       <c r="R159" t="n">
-        <v>6786165</v>
+        <v>6786160</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16423,6 +16424,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16441,7 +16443,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080311</v>
+        <v>129080305</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16485,10 +16487,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436449</v>
+        <v>436474</v>
       </c>
       <c r="R160" t="n">
-        <v>6786212</v>
+        <v>6785946</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16548,7 +16550,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129080305</v>
+        <v>129080311</v>
       </c>
       <c r="B161" t="n">
         <v>8450</v>
@@ -16592,10 +16594,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>436474</v>
+        <v>436449</v>
       </c>
       <c r="R161" t="n">
-        <v>6785946</v>
+        <v>6786212</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16655,41 +16657,40 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080310</v>
+        <v>129080287</v>
       </c>
       <c r="B162" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16699,10 +16700,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436472</v>
+        <v>436471</v>
       </c>
       <c r="R162" t="n">
-        <v>6786160</v>
+        <v>6786165</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16743,7 +16744,6 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -16762,41 +16762,40 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129080309</v>
+        <v>129080286</v>
       </c>
       <c r="B163" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -16806,10 +16805,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>436571</v>
+        <v>436572</v>
       </c>
       <c r="R163" t="n">
-        <v>6785936</v>
+        <v>6785762</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16850,7 +16849,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16869,7 +16867,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129080308</v>
+        <v>129080309</v>
       </c>
       <c r="B164" t="n">
         <v>8450</v>
@@ -16913,10 +16911,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>436807</v>
+        <v>436571</v>
       </c>
       <c r="R164" t="n">
-        <v>6785797</v>
+        <v>6785936</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16976,40 +16974,41 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129080286</v>
+        <v>129080308</v>
       </c>
       <c r="B165" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -17019,10 +17018,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>436572</v>
+        <v>436807</v>
       </c>
       <c r="R165" t="n">
-        <v>6785762</v>
+        <v>6785797</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17063,6 +17062,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -1277,45 +1277,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058384</v>
+        <v>129058337</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436265</v>
+        <v>436322</v>
       </c>
       <c r="R8" t="n">
-        <v>6786123</v>
+        <v>6786198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,6 +1365,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058350</v>
+        <v>129058384</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436465</v>
+        <v>436265</v>
       </c>
       <c r="R9" t="n">
-        <v>6785855</v>
+        <v>6786123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058415</v>
+        <v>129058350</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,37 +1492,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436527</v>
+        <v>436465</v>
       </c>
       <c r="R10" t="n">
-        <v>6785990</v>
+        <v>6785855</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,18 +1554,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1577,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058304</v>
+        <v>129058415</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,34 +1589,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436683</v>
+        <v>436527</v>
       </c>
       <c r="R11" t="n">
-        <v>6785939</v>
+        <v>6785990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,12 +1654,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1888,54 +1898,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129058337</v>
+        <v>129058304</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436322</v>
+        <v>436683</v>
       </c>
       <c r="R14" t="n">
-        <v>6786198</v>
+        <v>6785939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,7 +1977,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2092,41 +2092,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058332</v>
+        <v>129058286</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2136,10 +2135,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436648</v>
+        <v>436617</v>
       </c>
       <c r="R16" t="n">
-        <v>6785874</v>
+        <v>6785749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2199,45 +2197,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058301</v>
+        <v>129058332</v>
       </c>
       <c r="B17" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436796</v>
+        <v>436648</v>
       </c>
       <c r="R17" t="n">
-        <v>6785778</v>
+        <v>6785874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,6 +2285,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2296,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058317</v>
+        <v>129058382</v>
       </c>
       <c r="B18" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,37 +2315,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436356</v>
+        <v>436214</v>
       </c>
       <c r="R18" t="n">
-        <v>6786224</v>
+        <v>6786180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2383,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2397,10 +2401,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058307</v>
+        <v>129058403</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2412,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436597</v>
+        <v>436259</v>
       </c>
       <c r="R19" t="n">
-        <v>6785981</v>
+        <v>6786285</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058308</v>
+        <v>129058365</v>
       </c>
       <c r="B20" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2505,21 +2509,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2529,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436545</v>
+        <v>436467</v>
       </c>
       <c r="R20" t="n">
-        <v>6785997</v>
+        <v>6786236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,10 +2595,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058280</v>
+        <v>129058308</v>
       </c>
       <c r="B21" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2602,21 +2606,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2626,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436519</v>
+        <v>436545</v>
       </c>
       <c r="R21" t="n">
-        <v>6785988</v>
+        <v>6785997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,10 +2692,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058382</v>
+        <v>129058301</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2699,21 +2703,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2723,10 +2727,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436214</v>
+        <v>436796</v>
       </c>
       <c r="R22" t="n">
-        <v>6786180</v>
+        <v>6785778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,10 +2789,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058403</v>
+        <v>129058317</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2796,34 +2800,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436259</v>
+        <v>436356</v>
       </c>
       <c r="R23" t="n">
-        <v>6786285</v>
+        <v>6786224</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2864,6 +2871,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2882,10 +2890,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058365</v>
+        <v>129058307</v>
       </c>
       <c r="B24" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,21 +2901,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2917,10 +2925,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436467</v>
+        <v>436597</v>
       </c>
       <c r="R24" t="n">
-        <v>6786236</v>
+        <v>6785981</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,10 +2987,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058286</v>
+        <v>129058280</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2990,42 +2998,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436617</v>
+        <v>436519</v>
       </c>
       <c r="R25" t="n">
-        <v>6785749</v>
+        <v>6785988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3084,37 +3084,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058272</v>
+        <v>129058327</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3122,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436369</v>
+        <v>436674</v>
       </c>
       <c r="R26" t="n">
-        <v>6786195</v>
+        <v>6785802</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,40 +3191,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129058287</v>
+        <v>129058343</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3228,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436718</v>
+        <v>436269</v>
       </c>
       <c r="R27" t="n">
-        <v>6785941</v>
+        <v>6786228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,6 +3279,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3290,43 +3298,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058343</v>
+        <v>129058272</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3334,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436269</v>
+        <v>436369</v>
       </c>
       <c r="R28" t="n">
-        <v>6786228</v>
+        <v>6786195</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,41 +3399,40 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058327</v>
+        <v>129058287</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3441,10 +3442,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436674</v>
+        <v>436718</v>
       </c>
       <c r="R29" t="n">
-        <v>6785802</v>
+        <v>6785941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,7 +3486,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058288</v>
+        <v>129058319</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,31 +3612,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3644,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436458</v>
+        <v>436378</v>
       </c>
       <c r="R31" t="n">
-        <v>6786194</v>
+        <v>6786219</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,6 +3683,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3904,10 +3900,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058319</v>
+        <v>129058288</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,26 +3911,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3942,10 +3943,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436378</v>
+        <v>436458</v>
       </c>
       <c r="R34" t="n">
-        <v>6786219</v>
+        <v>6786194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,7 +3987,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4005,45 +4005,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058262</v>
+        <v>129058325</v>
       </c>
       <c r="B35" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436534</v>
+        <v>436443</v>
       </c>
       <c r="R35" t="n">
-        <v>6785834</v>
+        <v>6785940</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4084,6 +4093,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4102,10 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058269</v>
+        <v>129058318</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,34 +4123,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436483</v>
+        <v>436354</v>
       </c>
       <c r="R36" t="n">
-        <v>6786017</v>
+        <v>6786212</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4181,6 +4194,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4199,7 +4213,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058277</v>
+        <v>129058262</v>
       </c>
       <c r="B37" t="n">
         <v>79660</v>
@@ -4228,19 +4242,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436351</v>
+        <v>436534</v>
       </c>
       <c r="R37" t="n">
-        <v>6786185</v>
+        <v>6785834</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,7 +4292,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4300,10 +4310,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058404</v>
+        <v>129058269</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4311,21 +4321,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4335,10 +4345,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436229</v>
+        <v>436483</v>
       </c>
       <c r="R38" t="n">
-        <v>6786238</v>
+        <v>6786017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,10 +4407,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058348</v>
+        <v>129058277</v>
       </c>
       <c r="B39" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4408,34 +4418,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436266</v>
+        <v>436351</v>
       </c>
       <c r="R39" t="n">
-        <v>6786145</v>
+        <v>6786185</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,6 +4489,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4508,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058357</v>
+        <v>129058404</v>
       </c>
       <c r="B40" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4505,21 +4519,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4529,10 +4543,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436686</v>
+        <v>436229</v>
       </c>
       <c r="R40" t="n">
-        <v>6785940</v>
+        <v>6786238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,10 +4605,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058278</v>
+        <v>129058348</v>
       </c>
       <c r="B41" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4616,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4640,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436295</v>
+        <v>436266</v>
       </c>
       <c r="R41" t="n">
-        <v>6786172</v>
+        <v>6786145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4688,51 +4702,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058325</v>
+        <v>129058357</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436443</v>
+        <v>436686</v>
       </c>
       <c r="R42" t="n">
         <v>6785940</v>
@@ -4776,7 +4781,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4795,10 +4799,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058318</v>
+        <v>129058278</v>
       </c>
       <c r="B43" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4806,37 +4810,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436354</v>
+        <v>436295</v>
       </c>
       <c r="R43" t="n">
-        <v>6786212</v>
+        <v>6786172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4877,7 +4878,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5389,10 +5389,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058309</v>
+        <v>129058395</v>
       </c>
       <c r="B49" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5400,21 +5400,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436532</v>
+        <v>436504</v>
       </c>
       <c r="R49" t="n">
-        <v>6785994</v>
+        <v>6786102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058395</v>
+        <v>129058385</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R50" t="n">
-        <v>6786102</v>
+        <v>6786086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058385</v>
+        <v>129058268</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R51" t="n">
-        <v>6786086</v>
+        <v>6786023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058268</v>
+        <v>129058386</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5691,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436504</v>
+        <v>436505</v>
       </c>
       <c r="R52" t="n">
-        <v>6786023</v>
+        <v>6785856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129058386</v>
+        <v>129058309</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436505</v>
+        <v>436532</v>
       </c>
       <c r="R53" t="n">
-        <v>6785856</v>
+        <v>6785994</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7091,40 +7091,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058291</v>
+        <v>129058340</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7134,10 +7135,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436214</v>
+        <v>436324</v>
       </c>
       <c r="R66" t="n">
-        <v>6786222</v>
+        <v>6786220</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,6 +7179,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7196,7 +7198,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058335</v>
+        <v>129058323</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7240,10 +7242,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436360</v>
+        <v>436241</v>
       </c>
       <c r="R67" t="n">
-        <v>6786231</v>
+        <v>6786159</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7303,41 +7305,40 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058340</v>
+        <v>129058291</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7347,10 +7348,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436324</v>
+        <v>436214</v>
       </c>
       <c r="R68" t="n">
-        <v>6786220</v>
+        <v>6786222</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7391,7 +7392,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058323</v>
+        <v>129058335</v>
       </c>
       <c r="B70" t="n">
         <v>8450</v>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436241</v>
+        <v>436360</v>
       </c>
       <c r="R70" t="n">
-        <v>6786159</v>
+        <v>6786231</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7624,45 +7624,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058267</v>
+        <v>129058334</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436524</v>
+        <v>436373</v>
       </c>
       <c r="R71" t="n">
-        <v>6785977</v>
+        <v>6786190</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7703,6 +7712,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7721,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058362</v>
+        <v>129058305</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7732,34 +7742,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436494</v>
+        <v>436680</v>
       </c>
       <c r="R72" t="n">
-        <v>6786028</v>
+        <v>6785902</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7800,6 +7813,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7818,10 +7832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058264</v>
+        <v>129058362</v>
       </c>
       <c r="B73" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7829,21 +7843,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7853,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436599</v>
+        <v>436494</v>
       </c>
       <c r="R73" t="n">
-        <v>6785738</v>
+        <v>6786028</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7915,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058354</v>
+        <v>129058264</v>
       </c>
       <c r="B74" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7926,21 +7940,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7950,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436796</v>
+        <v>436599</v>
       </c>
       <c r="R74" t="n">
-        <v>6785778</v>
+        <v>6785738</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8012,7 +8026,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058359</v>
+        <v>129058354</v>
       </c>
       <c r="B75" t="n">
         <v>78798</v>
@@ -8047,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436532</v>
+        <v>436796</v>
       </c>
       <c r="R75" t="n">
-        <v>6785994</v>
+        <v>6785778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8109,7 +8123,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058367</v>
+        <v>129058359</v>
       </c>
       <c r="B76" t="n">
         <v>78798</v>
@@ -8144,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436371</v>
+        <v>436532</v>
       </c>
       <c r="R76" t="n">
-        <v>6786199</v>
+        <v>6785994</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,54 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058334</v>
+        <v>129058367</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436373</v>
+        <v>436371</v>
       </c>
       <c r="R77" t="n">
-        <v>6786190</v>
+        <v>6786199</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,7 +8299,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8313,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058305</v>
+        <v>129058267</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,37 +8328,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436680</v>
+        <v>436524</v>
       </c>
       <c r="R78" t="n">
-        <v>6785902</v>
+        <v>6785977</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8395,7 +8396,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -10098,54 +10098,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058333</v>
+        <v>129058300</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436432</v>
+        <v>436554</v>
       </c>
       <c r="R96" t="n">
-        <v>6786210</v>
+        <v>6785764</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10186,7 +10177,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10205,10 +10195,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058407</v>
+        <v>129058298</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10216,21 +10206,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10240,10 +10230,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436215</v>
+        <v>436513</v>
       </c>
       <c r="R97" t="n">
-        <v>6786222</v>
+        <v>6785845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10302,7 +10292,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058416</v>
+        <v>129058407</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10331,19 +10321,16 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436491</v>
+        <v>436215</v>
       </c>
       <c r="R98" t="n">
-        <v>6786146</v>
+        <v>6786222</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10378,18 +10365,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10408,10 +10389,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058298</v>
+        <v>129058416</v>
       </c>
       <c r="B99" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10419,34 +10400,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436513</v>
+        <v>436491</v>
       </c>
       <c r="R99" t="n">
-        <v>6785845</v>
+        <v>6786146</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10481,12 +10465,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10505,45 +10495,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058300</v>
+        <v>129058333</v>
       </c>
       <c r="B100" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436554</v>
+        <v>436432</v>
       </c>
       <c r="R100" t="n">
-        <v>6785764</v>
+        <v>6786210</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10584,6 +10583,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058289</v>
+        <v>129058368</v>
       </c>
       <c r="B111" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11593,42 +11593,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436486</v>
+        <v>436257</v>
       </c>
       <c r="R111" t="n">
-        <v>6786231</v>
+        <v>6786288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11687,10 +11679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058368</v>
+        <v>129058289</v>
       </c>
       <c r="B112" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11698,34 +11690,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436257</v>
+        <v>436486</v>
       </c>
       <c r="R112" t="n">
-        <v>6786288</v>
+        <v>6786231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12587,7 +12587,7 @@
         <v>129080302</v>
       </c>
       <c r="B121" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080291</v>
+        <v>129080294</v>
       </c>
       <c r="B123" t="n">
         <v>78799</v>
@@ -12814,10 +12814,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436524</v>
+        <v>436659</v>
       </c>
       <c r="R123" t="n">
-        <v>6785865</v>
+        <v>6785808</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080294</v>
+        <v>129080291</v>
       </c>
       <c r="B124" t="n">
         <v>78799</v>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436659</v>
+        <v>436524</v>
       </c>
       <c r="R124" t="n">
-        <v>6785808</v>
+        <v>6785865</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B125" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R125" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,10 +13070,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B126" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R126" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13167,10 +13167,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129080281</v>
+        <v>129080298</v>
       </c>
       <c r="B127" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436448</v>
+        <v>436428</v>
       </c>
       <c r="R127" t="n">
-        <v>6786211</v>
+        <v>6786194</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R128" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080298</v>
+        <v>129080281</v>
       </c>
       <c r="B129" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13372,21 +13372,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436428</v>
+        <v>436448</v>
       </c>
       <c r="R129" t="n">
-        <v>6786194</v>
+        <v>6786211</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B130" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R130" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B131" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R131" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B132" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R132" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129080301</v>
+        <v>129080279</v>
       </c>
       <c r="B134" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13857,21 +13857,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436246</v>
+        <v>436471</v>
       </c>
       <c r="R134" t="n">
-        <v>6786298</v>
+        <v>6786142</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129080279</v>
+        <v>129080301</v>
       </c>
       <c r="B135" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13954,21 +13954,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>436471</v>
+        <v>436246</v>
       </c>
       <c r="R135" t="n">
-        <v>6786142</v>
+        <v>6786298</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14040,10 +14040,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129080284</v>
+        <v>129080317</v>
       </c>
       <c r="B136" t="n">
-        <v>91560</v>
+        <v>78798</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>436494</v>
+        <v>436816</v>
       </c>
       <c r="R136" t="n">
-        <v>6785930</v>
+        <v>6785768</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14137,7 +14137,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080317</v>
+        <v>129080316</v>
       </c>
       <c r="B137" t="n">
         <v>78798</v>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436816</v>
+        <v>436532</v>
       </c>
       <c r="R137" t="n">
-        <v>6785768</v>
+        <v>6785867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,10 +14234,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080316</v>
+        <v>129080284</v>
       </c>
       <c r="B138" t="n">
-        <v>78798</v>
+        <v>91561</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436532</v>
+        <v>436494</v>
       </c>
       <c r="R138" t="n">
-        <v>6785867</v>
+        <v>6785930</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14719,54 +14719,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080312</v>
+        <v>129080299</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436296</v>
+        <v>436384</v>
       </c>
       <c r="R143" t="n">
-        <v>6786185</v>
+        <v>6786203</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14807,7 +14798,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14826,7 +14816,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080299</v>
+        <v>129080300</v>
       </c>
       <c r="B144" t="n">
         <v>78799</v>
@@ -14861,10 +14851,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436384</v>
+        <v>436333</v>
       </c>
       <c r="R144" t="n">
-        <v>6786203</v>
+        <v>6786167</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15020,45 +15010,54 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080300</v>
+        <v>129080312</v>
       </c>
       <c r="B146" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436333</v>
+        <v>436296</v>
       </c>
       <c r="R146" t="n">
-        <v>6786167</v>
+        <v>6786185</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15099,6 +15098,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080282</v>
+        <v>129080297</v>
       </c>
       <c r="B149" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436335</v>
+        <v>436449</v>
       </c>
       <c r="R149" t="n">
-        <v>6786163</v>
+        <v>6786210</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15408,10 +15408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080297</v>
+        <v>129080283</v>
       </c>
       <c r="B150" t="n">
-        <v>78799</v>
+        <v>91540</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15419,21 +15419,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15443,10 +15443,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436449</v>
+        <v>436434</v>
       </c>
       <c r="R150" t="n">
-        <v>6786210</v>
+        <v>6786112</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15481,12 +15481,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15505,10 +15511,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080283</v>
+        <v>129080331</v>
       </c>
       <c r="B151" t="n">
-        <v>91540</v>
+        <v>88940</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15516,21 +15522,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15540,10 +15546,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436434</v>
+        <v>436491</v>
       </c>
       <c r="R151" t="n">
-        <v>6786112</v>
+        <v>6786094</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15576,11 +15582,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15608,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080331</v>
+        <v>129080282</v>
       </c>
       <c r="B152" t="n">
-        <v>88940</v>
+        <v>79660</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15619,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15643,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436491</v>
+        <v>436335</v>
       </c>
       <c r="R152" t="n">
-        <v>6786094</v>
+        <v>6786163</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15687,7 +15688,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16336,41 +16336,40 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129080310</v>
+        <v>129080287</v>
       </c>
       <c r="B159" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16380,10 +16379,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>436472</v>
+        <v>436471</v>
       </c>
       <c r="R159" t="n">
-        <v>6786160</v>
+        <v>6786165</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16424,7 +16423,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16657,40 +16655,41 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080287</v>
+        <v>129080310</v>
       </c>
       <c r="B162" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -16700,10 +16699,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436471</v>
+        <v>436472</v>
       </c>
       <c r="R162" t="n">
-        <v>6786165</v>
+        <v>6786160</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16744,6 +16743,7 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -1277,54 +1277,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129058337</v>
+        <v>129058384</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436322</v>
+        <v>436265</v>
       </c>
       <c r="R8" t="n">
-        <v>6786198</v>
+        <v>6786123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129058384</v>
+        <v>129058350</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436265</v>
+        <v>436465</v>
       </c>
       <c r="R9" t="n">
-        <v>6786123</v>
+        <v>6785855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129058350</v>
+        <v>129058415</v>
       </c>
       <c r="B10" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,34 +1482,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436465</v>
+        <v>436527</v>
       </c>
       <c r="R10" t="n">
-        <v>6785855</v>
+        <v>6785990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,12 +1547,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,37 +1577,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129058415</v>
+        <v>129058336</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1616,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436527</v>
+        <v>436336</v>
       </c>
       <c r="R11" t="n">
-        <v>6785990</v>
+        <v>6786183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1652,11 +1657,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta barrträd inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1684,7 +1684,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129058336</v>
+        <v>129058329</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1718,7 +1718,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436336</v>
+        <v>436754</v>
       </c>
       <c r="R12" t="n">
-        <v>6786183</v>
+        <v>6785822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129058329</v>
+        <v>129058337</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436754</v>
+        <v>436322</v>
       </c>
       <c r="R13" t="n">
-        <v>6785822</v>
+        <v>6786198</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129058286</v>
+        <v>129058382</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,42 +2103,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436617</v>
+        <v>436214</v>
       </c>
       <c r="R16" t="n">
-        <v>6785749</v>
+        <v>6786180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,54 +2189,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129058332</v>
+        <v>129058403</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436648</v>
+        <v>436259</v>
       </c>
       <c r="R17" t="n">
-        <v>6785874</v>
+        <v>6786285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,7 +2268,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129058382</v>
+        <v>129058365</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2339,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436214</v>
+        <v>436467</v>
       </c>
       <c r="R18" t="n">
-        <v>6786180</v>
+        <v>6786236</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129058403</v>
+        <v>129058286</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2412,34 +2394,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436259</v>
+        <v>436617</v>
       </c>
       <c r="R19" t="n">
-        <v>6786285</v>
+        <v>6785749</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,45 +2488,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058365</v>
+        <v>129058332</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436467</v>
+        <v>436648</v>
       </c>
       <c r="R20" t="n">
-        <v>6786236</v>
+        <v>6785874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,6 +2576,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058308</v>
+        <v>129058301</v>
       </c>
       <c r="B21" t="n">
         <v>78799</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436545</v>
+        <v>436796</v>
       </c>
       <c r="R21" t="n">
-        <v>6785997</v>
+        <v>6785778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058301</v>
+        <v>129058317</v>
       </c>
       <c r="B22" t="n">
         <v>78799</v>
@@ -2721,16 +2721,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436796</v>
+        <v>436356</v>
       </c>
       <c r="R22" t="n">
-        <v>6785778</v>
+        <v>6786224</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2771,6 +2774,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2789,7 +2793,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058317</v>
+        <v>129058307</v>
       </c>
       <c r="B23" t="n">
         <v>78799</v>
@@ -2818,19 +2822,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436356</v>
+        <v>436597</v>
       </c>
       <c r="R23" t="n">
-        <v>6786224</v>
+        <v>6785981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2871,7 +2872,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058307</v>
+        <v>129058308</v>
       </c>
       <c r="B24" t="n">
         <v>78799</v>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436597</v>
+        <v>436545</v>
       </c>
       <c r="R24" t="n">
-        <v>6785981</v>
+        <v>6785997</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,41 +3084,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058327</v>
+        <v>129058287</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3128,10 +3127,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436674</v>
+        <v>436718</v>
       </c>
       <c r="R26" t="n">
-        <v>6785802</v>
+        <v>6785941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3172,7 +3171,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3298,37 +3296,43 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129058272</v>
+        <v>129058327</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3336,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436369</v>
+        <v>436674</v>
       </c>
       <c r="R28" t="n">
-        <v>6786195</v>
+        <v>6785802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,10 +3403,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058287</v>
+        <v>129058311</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3410,42 +3414,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436718</v>
+        <v>436530</v>
       </c>
       <c r="R29" t="n">
-        <v>6785941</v>
+        <v>6785992</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,10 +3500,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058311</v>
+        <v>129058272</v>
       </c>
       <c r="B30" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3515,34 +3511,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436530</v>
+        <v>436369</v>
       </c>
       <c r="R30" t="n">
-        <v>6785992</v>
+        <v>6786195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3583,6 +3582,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129058319</v>
+        <v>129058273</v>
       </c>
       <c r="B31" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436378</v>
+        <v>436257</v>
       </c>
       <c r="R31" t="n">
-        <v>6786219</v>
+        <v>6786288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129058273</v>
+        <v>129058369</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,37 +3713,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436257</v>
+        <v>436817</v>
       </c>
       <c r="R32" t="n">
-        <v>6786288</v>
+        <v>6785838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,7 +3781,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3803,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058369</v>
+        <v>129058319</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3814,34 +3810,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436817</v>
+        <v>436378</v>
       </c>
       <c r="R33" t="n">
-        <v>6785838</v>
+        <v>6786219</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3882,6 +3881,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129058297</v>
+        <v>129058351</v>
       </c>
       <c r="B45" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436509</v>
+        <v>436516</v>
       </c>
       <c r="R45" t="n">
         <v>6785859</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129058313</v>
+        <v>129058297</v>
       </c>
       <c r="B46" t="n">
         <v>78799</v>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436504</v>
+        <v>436509</v>
       </c>
       <c r="R46" t="n">
-        <v>6786023</v>
+        <v>6785859</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129058351</v>
+        <v>129058313</v>
       </c>
       <c r="B47" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436516</v>
+        <v>436504</v>
       </c>
       <c r="R47" t="n">
-        <v>6785859</v>
+        <v>6786023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058290</v>
+        <v>129058395</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,42 +5295,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436601</v>
+        <v>436504</v>
       </c>
       <c r="R48" t="n">
-        <v>6785947</v>
+        <v>6786102</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5389,7 +5381,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058395</v>
+        <v>129058385</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5424,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R49" t="n">
-        <v>6786102</v>
+        <v>6786086</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058385</v>
+        <v>129058268</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5497,21 +5489,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R50" t="n">
-        <v>6786086</v>
+        <v>6786023</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058268</v>
+        <v>129058386</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5586,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436504</v>
+        <v>436505</v>
       </c>
       <c r="R51" t="n">
-        <v>6786023</v>
+        <v>6785856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058386</v>
+        <v>129058290</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,34 +5683,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436505</v>
+        <v>436601</v>
       </c>
       <c r="R52" t="n">
-        <v>6785856</v>
+        <v>6785947</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058396</v>
+        <v>129058392</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6009,16 +6009,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436491</v>
+        <v>436508</v>
       </c>
       <c r="R55" t="n">
-        <v>6786189</v>
+        <v>6786026</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6053,12 +6056,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6077,7 +6086,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129058392</v>
+        <v>129058391</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6115,10 +6124,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436508</v>
+        <v>436591</v>
       </c>
       <c r="R56" t="n">
-        <v>6786026</v>
+        <v>6785966</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6155,7 +6164,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6183,7 +6192,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129058391</v>
+        <v>129058399</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6221,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436591</v>
+        <v>436303</v>
       </c>
       <c r="R57" t="n">
-        <v>6785966</v>
+        <v>6786193</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6261,7 +6270,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
+          <t>Rikligt med Garnlav inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6289,7 +6298,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129058399</v>
+        <v>129058396</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6318,19 +6327,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436303</v>
+        <v>436491</v>
       </c>
       <c r="R58" t="n">
-        <v>6786193</v>
+        <v>6786189</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6365,18 +6371,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7091,41 +7091,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058340</v>
+        <v>129058291</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7135,10 +7134,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436324</v>
+        <v>436214</v>
       </c>
       <c r="R66" t="n">
-        <v>6786220</v>
+        <v>6786222</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7179,7 +7178,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7198,7 +7196,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058323</v>
+        <v>129058335</v>
       </c>
       <c r="B67" t="n">
         <v>8450</v>
@@ -7242,10 +7240,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436241</v>
+        <v>436360</v>
       </c>
       <c r="R67" t="n">
-        <v>6786159</v>
+        <v>6786231</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7305,40 +7303,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058291</v>
+        <v>129058340</v>
       </c>
       <c r="B68" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7348,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436214</v>
+        <v>436324</v>
       </c>
       <c r="R68" t="n">
-        <v>6786222</v>
+        <v>6786220</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,6 +7391,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7517,7 +7517,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058335</v>
+        <v>129058323</v>
       </c>
       <c r="B70" t="n">
         <v>8450</v>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436360</v>
+        <v>436241</v>
       </c>
       <c r="R70" t="n">
-        <v>6786231</v>
+        <v>6786159</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7624,54 +7624,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058334</v>
+        <v>129058267</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436373</v>
+        <v>436524</v>
       </c>
       <c r="R71" t="n">
-        <v>6786190</v>
+        <v>6785977</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7703,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7731,10 +7721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058305</v>
+        <v>129058362</v>
       </c>
       <c r="B72" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7742,37 +7732,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436680</v>
+        <v>436494</v>
       </c>
       <c r="R72" t="n">
-        <v>6785902</v>
+        <v>6786028</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7813,7 +7800,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7832,10 +7818,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058362</v>
+        <v>129058264</v>
       </c>
       <c r="B73" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,21 +7829,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7853,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436494</v>
+        <v>436599</v>
       </c>
       <c r="R73" t="n">
-        <v>6786028</v>
+        <v>6785738</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,10 +7915,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058264</v>
+        <v>129058354</v>
       </c>
       <c r="B74" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,21 +7926,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7964,10 +7950,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436599</v>
+        <v>436796</v>
       </c>
       <c r="R74" t="n">
-        <v>6785738</v>
+        <v>6785778</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8026,7 +8012,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058354</v>
+        <v>129058359</v>
       </c>
       <c r="B75" t="n">
         <v>78798</v>
@@ -8061,10 +8047,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436796</v>
+        <v>436532</v>
       </c>
       <c r="R75" t="n">
-        <v>6785778</v>
+        <v>6785994</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,7 +8109,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058359</v>
+        <v>129058367</v>
       </c>
       <c r="B76" t="n">
         <v>78798</v>
@@ -8158,10 +8144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436532</v>
+        <v>436371</v>
       </c>
       <c r="R76" t="n">
-        <v>6785994</v>
+        <v>6786199</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8206,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058367</v>
+        <v>129058334</v>
       </c>
       <c r="B77" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436371</v>
+        <v>436373</v>
       </c>
       <c r="R77" t="n">
-        <v>6786199</v>
+        <v>6786190</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8299,6 +8294,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8317,10 +8313,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058267</v>
+        <v>129058305</v>
       </c>
       <c r="B78" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,34 +8324,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436524</v>
+        <v>436680</v>
       </c>
       <c r="R78" t="n">
-        <v>6785977</v>
+        <v>6785902</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8396,6 +8395,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129058355</v>
+        <v>129058282</v>
       </c>
       <c r="B79" t="n">
-        <v>78798</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,26 +8425,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8452,10 +8457,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436825</v>
+        <v>436515</v>
       </c>
       <c r="R79" t="n">
-        <v>6785764</v>
+        <v>6786055</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8496,7 +8501,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8515,10 +8519,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058394</v>
+        <v>129058355</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,34 +8530,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436493</v>
+        <v>436825</v>
       </c>
       <c r="R80" t="n">
-        <v>6786075</v>
+        <v>6785764</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8594,6 +8601,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8612,10 +8620,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058356</v>
+        <v>129058394</v>
       </c>
       <c r="B81" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8623,21 +8631,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8647,10 +8655,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436818</v>
+        <v>436493</v>
       </c>
       <c r="R81" t="n">
-        <v>6785831</v>
+        <v>6786075</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8717,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058282</v>
+        <v>129058356</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>78798</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,42 +8728,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436515</v>
+        <v>436818</v>
       </c>
       <c r="R82" t="n">
-        <v>6786055</v>
+        <v>6785831</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9506,32 +9506,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129058411</v>
+        <v>129058346</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436461</v>
+        <v>436503</v>
       </c>
       <c r="R90" t="n">
-        <v>6785881</v>
+        <v>6786136</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9603,7 +9603,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058398</v>
+        <v>129058411</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436425</v>
+        <v>436461</v>
       </c>
       <c r="R91" t="n">
-        <v>6786210</v>
+        <v>6785881</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,7 +9700,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058387</v>
+        <v>129058398</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436805</v>
+        <v>436425</v>
       </c>
       <c r="R92" t="n">
-        <v>6785785</v>
+        <v>6786210</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058346</v>
+        <v>129058387</v>
       </c>
       <c r="B93" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436503</v>
+        <v>436805</v>
       </c>
       <c r="R93" t="n">
-        <v>6786136</v>
+        <v>6785785</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9991,54 +9991,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129058345</v>
+        <v>129058407</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436269</v>
+        <v>436215</v>
       </c>
       <c r="R95" t="n">
-        <v>6786257</v>
+        <v>6786222</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,7 +10070,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10098,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129058300</v>
+        <v>129058416</v>
       </c>
       <c r="B96" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10109,34 +10099,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436554</v>
+        <v>436491</v>
       </c>
       <c r="R96" t="n">
-        <v>6785764</v>
+        <v>6786146</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10171,12 +10164,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10195,45 +10194,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129058298</v>
+        <v>129058345</v>
       </c>
       <c r="B97" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436513</v>
+        <v>436269</v>
       </c>
       <c r="R97" t="n">
-        <v>6785845</v>
+        <v>6786257</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10274,6 +10282,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10292,45 +10301,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129058407</v>
+        <v>129058333</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436215</v>
+        <v>436432</v>
       </c>
       <c r="R98" t="n">
-        <v>6786222</v>
+        <v>6786210</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10371,6 +10389,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10389,10 +10408,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129058416</v>
+        <v>129058298</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10400,37 +10419,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436491</v>
+        <v>436513</v>
       </c>
       <c r="R99" t="n">
-        <v>6786146</v>
+        <v>6785845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10465,18 +10481,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10495,54 +10505,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129058333</v>
+        <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436432</v>
+        <v>436554</v>
       </c>
       <c r="R100" t="n">
-        <v>6786210</v>
+        <v>6785764</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10583,7 +10584,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11087,54 +11087,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129058324</v>
+        <v>129058406</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436254</v>
+        <v>436222</v>
       </c>
       <c r="R106" t="n">
-        <v>6786130</v>
+        <v>6786238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11175,7 +11166,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11194,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129058406</v>
+        <v>129058366</v>
       </c>
       <c r="B107" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11205,21 +11195,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11229,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436222</v>
+        <v>436357</v>
       </c>
       <c r="R107" t="n">
-        <v>6786238</v>
+        <v>6786208</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11291,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129058366</v>
+        <v>129058393</v>
       </c>
       <c r="B108" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11302,21 +11292,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11326,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436357</v>
+        <v>436507</v>
       </c>
       <c r="R108" t="n">
-        <v>6786208</v>
+        <v>6786023</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11388,10 +11378,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129058393</v>
+        <v>129058358</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11399,21 +11389,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11423,10 +11413,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436507</v>
+        <v>436550</v>
       </c>
       <c r="R109" t="n">
-        <v>6786023</v>
+        <v>6785988</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11485,45 +11475,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129058358</v>
+        <v>129058324</v>
       </c>
       <c r="B110" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436550</v>
+        <v>436254</v>
       </c>
       <c r="R110" t="n">
-        <v>6785988</v>
+        <v>6786130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11564,6 +11563,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058368</v>
+        <v>129058289</v>
       </c>
       <c r="B111" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11593,34 +11593,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436257</v>
+        <v>436486</v>
       </c>
       <c r="R111" t="n">
-        <v>6786288</v>
+        <v>6786231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11679,40 +11687,41 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129058289</v>
+        <v>129058328</v>
       </c>
       <c r="B112" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11722,10 +11731,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436486</v>
+        <v>436701</v>
       </c>
       <c r="R112" t="n">
-        <v>6786231</v>
+        <v>6785838</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11766,6 +11775,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -11784,54 +11794,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058328</v>
+        <v>129058368</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436701</v>
+        <v>436257</v>
       </c>
       <c r="R113" t="n">
-        <v>6785838</v>
+        <v>6786288</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11872,7 +11873,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080277</v>
+        <v>129080302</v>
       </c>
       <c r="B120" t="n">
-        <v>79660</v>
+        <v>91561</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436561</v>
+        <v>436320</v>
       </c>
       <c r="R120" t="n">
-        <v>6785959</v>
+        <v>6786132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,6 +12566,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12584,10 +12585,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080302</v>
+        <v>129080277</v>
       </c>
       <c r="B121" t="n">
-        <v>91561</v>
+        <v>79660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12595,21 +12596,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12619,10 +12620,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436320</v>
+        <v>436561</v>
       </c>
       <c r="R121" t="n">
-        <v>6786132</v>
+        <v>6785959</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,7 +12664,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12779,7 +12779,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129080294</v>
+        <v>129080291</v>
       </c>
       <c r="B123" t="n">
         <v>78799</v>
@@ -12814,10 +12814,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436659</v>
+        <v>436524</v>
       </c>
       <c r="R123" t="n">
-        <v>6785808</v>
+        <v>6785865</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129080291</v>
+        <v>129080294</v>
       </c>
       <c r="B124" t="n">
         <v>78799</v>
@@ -12911,10 +12911,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436524</v>
+        <v>436659</v>
       </c>
       <c r="R124" t="n">
-        <v>6785865</v>
+        <v>6785808</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12973,10 +12973,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129080289</v>
+        <v>129080322</v>
       </c>
       <c r="B125" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12984,21 +12984,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436212</v>
+        <v>436428</v>
       </c>
       <c r="R125" t="n">
-        <v>6786207</v>
+        <v>6786194</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13070,10 +13070,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129080322</v>
+        <v>129080289</v>
       </c>
       <c r="B126" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13081,21 +13081,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436428</v>
+        <v>436212</v>
       </c>
       <c r="R126" t="n">
-        <v>6786194</v>
+        <v>6786207</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13167,10 +13167,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129080298</v>
+        <v>129080281</v>
       </c>
       <c r="B127" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13178,21 +13178,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436428</v>
+        <v>436448</v>
       </c>
       <c r="R127" t="n">
-        <v>6786194</v>
+        <v>6786211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13264,10 +13264,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129080290</v>
+        <v>129080328</v>
       </c>
       <c r="B128" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436545</v>
+        <v>436438</v>
       </c>
       <c r="R128" t="n">
-        <v>6785882</v>
+        <v>6786185</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129080281</v>
+        <v>129080298</v>
       </c>
       <c r="B129" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13372,21 +13372,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436448</v>
+        <v>436428</v>
       </c>
       <c r="R129" t="n">
-        <v>6786211</v>
+        <v>6786194</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13458,10 +13458,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129080328</v>
+        <v>129080290</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13469,21 +13469,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436438</v>
+        <v>436545</v>
       </c>
       <c r="R130" t="n">
-        <v>6786185</v>
+        <v>6785882</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B131" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R131" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B132" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R132" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14040,10 +14040,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129080317</v>
+        <v>129080284</v>
       </c>
       <c r="B136" t="n">
-        <v>78798</v>
+        <v>91561</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>436816</v>
+        <v>436494</v>
       </c>
       <c r="R136" t="n">
-        <v>6785768</v>
+        <v>6785930</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14137,7 +14137,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080316</v>
+        <v>129080317</v>
       </c>
       <c r="B137" t="n">
         <v>78798</v>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436532</v>
+        <v>436816</v>
       </c>
       <c r="R137" t="n">
-        <v>6785867</v>
+        <v>6785768</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,10 +14234,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080284</v>
+        <v>129080316</v>
       </c>
       <c r="B138" t="n">
-        <v>91561</v>
+        <v>78798</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436494</v>
+        <v>436532</v>
       </c>
       <c r="R138" t="n">
-        <v>6785930</v>
+        <v>6785867</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14719,10 +14719,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129080299</v>
+        <v>129080327</v>
       </c>
       <c r="B143" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14730,21 +14730,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14754,10 +14754,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>436384</v>
+        <v>436653</v>
       </c>
       <c r="R143" t="n">
-        <v>6786203</v>
+        <v>6785861</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14816,45 +14816,54 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129080300</v>
+        <v>129080312</v>
       </c>
       <c r="B144" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>436333</v>
+        <v>436296</v>
       </c>
       <c r="R144" t="n">
-        <v>6786167</v>
+        <v>6786185</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14895,6 +14904,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -14913,10 +14923,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129080327</v>
+        <v>129080300</v>
       </c>
       <c r="B145" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14924,21 +14934,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14948,10 +14958,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>436653</v>
+        <v>436333</v>
       </c>
       <c r="R145" t="n">
-        <v>6785861</v>
+        <v>6786167</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15010,54 +15020,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129080312</v>
+        <v>129080299</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gudfadertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436296</v>
+        <v>436384</v>
       </c>
       <c r="R146" t="n">
-        <v>6786185</v>
+        <v>6786203</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15098,7 +15099,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080297</v>
+        <v>129080283</v>
       </c>
       <c r="B149" t="n">
-        <v>78799</v>
+        <v>91540</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436449</v>
+        <v>436434</v>
       </c>
       <c r="R149" t="n">
-        <v>6786210</v>
+        <v>6786112</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15384,12 +15384,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15408,10 +15414,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080283</v>
+        <v>129080331</v>
       </c>
       <c r="B150" t="n">
-        <v>91540</v>
+        <v>88940</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15419,21 +15425,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15443,10 +15449,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436434</v>
+        <v>436491</v>
       </c>
       <c r="R150" t="n">
-        <v>6786112</v>
+        <v>6786094</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15479,11 +15485,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15511,10 +15512,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080331</v>
+        <v>129080282</v>
       </c>
       <c r="B151" t="n">
-        <v>88940</v>
+        <v>79660</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15522,21 +15523,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15546,10 +15547,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436491</v>
+        <v>436335</v>
       </c>
       <c r="R151" t="n">
-        <v>6786094</v>
+        <v>6786163</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15590,7 +15591,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15609,10 +15609,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080282</v>
+        <v>129080297</v>
       </c>
       <c r="B152" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15620,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436335</v>
+        <v>436449</v>
       </c>
       <c r="R152" t="n">
-        <v>6786163</v>
+        <v>6786210</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16441,7 +16441,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129080305</v>
+        <v>129080310</v>
       </c>
       <c r="B160" t="n">
         <v>8450</v>
@@ -16485,10 +16485,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>436474</v>
+        <v>436472</v>
       </c>
       <c r="R160" t="n">
-        <v>6785946</v>
+        <v>6786160</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129080311</v>
+        <v>129080305</v>
       </c>
       <c r="B161" t="n">
         <v>8450</v>
@@ -16592,10 +16592,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>436449</v>
+        <v>436474</v>
       </c>
       <c r="R161" t="n">
-        <v>6786212</v>
+        <v>6785946</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16655,7 +16655,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129080310</v>
+        <v>129080311</v>
       </c>
       <c r="B162" t="n">
         <v>8450</v>
@@ -16699,10 +16699,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>436472</v>
+        <v>436449</v>
       </c>
       <c r="R162" t="n">
-        <v>6786160</v>
+        <v>6786212</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129058274</v>
+        <v>129058299</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436522</v>
+        <v>436545</v>
       </c>
       <c r="R2" t="n">
-        <v>6786062</v>
+        <v>6785800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129058412</v>
+        <v>129058303</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436564</v>
+        <v>436818</v>
       </c>
       <c r="R3" t="n">
-        <v>6785776</v>
+        <v>6785831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,54 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129058331</v>
+        <v>129058274</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436755</v>
+        <v>436522</v>
       </c>
       <c r="R4" t="n">
-        <v>6785905</v>
+        <v>6786062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129058341</v>
+        <v>129058412</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436278</v>
+        <v>436564</v>
       </c>
       <c r="R5" t="n">
-        <v>6786206</v>
+        <v>6785776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,45 +1063,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129058299</v>
+        <v>129058331</v>
       </c>
       <c r="B6" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436545</v>
+        <v>436755</v>
       </c>
       <c r="R6" t="n">
-        <v>6785800</v>
+        <v>6785905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,45 +1170,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129058303</v>
+        <v>129058341</v>
       </c>
       <c r="B7" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436818</v>
+        <v>436278</v>
       </c>
       <c r="R7" t="n">
-        <v>6785831</v>
+        <v>6786206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>129058384</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129058350</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129058415</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>129058304</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>129058321</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129058382</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>129058403</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129058365</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,54 +2488,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129058332</v>
+        <v>129058301</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436648</v>
+        <v>436796</v>
       </c>
       <c r="R20" t="n">
-        <v>6785874</v>
+        <v>6785778</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2567,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2585,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129058301</v>
+        <v>129058317</v>
       </c>
       <c r="B21" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,16 +2614,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436796</v>
+        <v>436356</v>
       </c>
       <c r="R21" t="n">
-        <v>6785778</v>
+        <v>6786224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,6 +2667,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129058317</v>
+        <v>129058307</v>
       </c>
       <c r="B22" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,19 +2715,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436356</v>
+        <v>436597</v>
       </c>
       <c r="R22" t="n">
-        <v>6786224</v>
+        <v>6785981</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2774,7 +2765,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2793,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129058307</v>
+        <v>129058308</v>
       </c>
       <c r="B23" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436597</v>
+        <v>436545</v>
       </c>
       <c r="R23" t="n">
-        <v>6785981</v>
+        <v>6785997</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2890,10 +2880,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129058308</v>
+        <v>129058280</v>
       </c>
       <c r="B24" t="n">
-        <v>78799</v>
+        <v>79633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2901,21 +2891,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2925,10 +2915,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436545</v>
+        <v>436519</v>
       </c>
       <c r="R24" t="n">
-        <v>6785997</v>
+        <v>6785988</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,45 +2977,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129058280</v>
+        <v>129058332</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436519</v>
+        <v>436648</v>
       </c>
       <c r="R25" t="n">
-        <v>6785988</v>
+        <v>6785874</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,6 +3065,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129058287</v>
+        <v>129058272</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3095,31 +3095,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3127,10 +3122,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436718</v>
+        <v>436369</v>
       </c>
       <c r="R26" t="n">
-        <v>6785941</v>
+        <v>6786195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,6 +3166,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3403,10 +3399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129058311</v>
+        <v>129058287</v>
       </c>
       <c r="B29" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,34 +3410,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436530</v>
+        <v>436718</v>
       </c>
       <c r="R29" t="n">
-        <v>6785992</v>
+        <v>6785941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129058272</v>
+        <v>129058311</v>
       </c>
       <c r="B30" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,37 +3515,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436369</v>
+        <v>436530</v>
       </c>
       <c r="R30" t="n">
-        <v>6786195</v>
+        <v>6785992</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3582,7 +3583,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>129058273</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>129058369</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129058319</v>
+        <v>129058288</v>
       </c>
       <c r="B33" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3810,26 +3810,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3837,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436378</v>
+        <v>436458</v>
       </c>
       <c r="R33" t="n">
-        <v>6786219</v>
+        <v>6786194</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,7 +3886,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3900,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129058288</v>
+        <v>129058319</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,31 +3915,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3943,10 +3942,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436458</v>
+        <v>436378</v>
       </c>
       <c r="R34" t="n">
-        <v>6786194</v>
+        <v>6786219</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,6 +3986,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4005,54 +4005,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129058325</v>
+        <v>129058262</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436443</v>
+        <v>436534</v>
       </c>
       <c r="R35" t="n">
-        <v>6785940</v>
+        <v>6785834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,7 +4084,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4112,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129058318</v>
+        <v>129058269</v>
       </c>
       <c r="B36" t="n">
-        <v>78799</v>
+        <v>79662</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4123,37 +4113,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436354</v>
+        <v>436483</v>
       </c>
       <c r="R36" t="n">
-        <v>6786212</v>
+        <v>6786017</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,7 +4181,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4213,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129058262</v>
+        <v>129058277</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4242,16 +4228,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436534</v>
+        <v>436351</v>
       </c>
       <c r="R37" t="n">
-        <v>6785834</v>
+        <v>6786185</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4292,6 +4281,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4310,10 +4300,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129058269</v>
+        <v>129058404</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4321,21 +4311,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4345,10 +4335,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436483</v>
+        <v>436229</v>
       </c>
       <c r="R38" t="n">
-        <v>6786017</v>
+        <v>6786238</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4407,10 +4397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129058277</v>
+        <v>129058348</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>78800</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4418,37 +4408,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436351</v>
+        <v>436266</v>
       </c>
       <c r="R39" t="n">
-        <v>6786185</v>
+        <v>6786145</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,7 +4476,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4508,10 +4494,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129058404</v>
+        <v>129058357</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4519,21 +4505,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4543,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436229</v>
+        <v>436686</v>
       </c>
       <c r="R40" t="n">
-        <v>6786238</v>
+        <v>6785940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4605,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129058348</v>
+        <v>129058278</v>
       </c>
       <c r="B41" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4616,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4640,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436266</v>
+        <v>436295</v>
       </c>
       <c r="R41" t="n">
-        <v>6786145</v>
+        <v>6786172</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4702,42 +4688,51 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129058357</v>
+        <v>129058325</v>
       </c>
       <c r="B42" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436686</v>
+        <v>436443</v>
       </c>
       <c r="R42" t="n">
         <v>6785940</v>
@@ -4781,6 +4776,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4799,10 +4795,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129058278</v>
+        <v>129058318</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4810,34 +4806,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436295</v>
+        <v>436354</v>
       </c>
       <c r="R43" t="n">
-        <v>6786172</v>
+        <v>6786212</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4878,6 +4877,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>129058276</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129058351</v>
+        <v>129058297</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436516</v>
+        <v>436509</v>
       </c>
       <c r="R45" t="n">
         <v>6785859</v>
@@ -5090,10 +5090,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129058297</v>
+        <v>129058313</v>
       </c>
       <c r="B46" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436509</v>
+        <v>436504</v>
       </c>
       <c r="R46" t="n">
-        <v>6785859</v>
+        <v>6786023</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129058313</v>
+        <v>129058351</v>
       </c>
       <c r="B47" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436504</v>
+        <v>436516</v>
       </c>
       <c r="R47" t="n">
-        <v>6786023</v>
+        <v>6785859</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129058395</v>
+        <v>129058290</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,34 +5295,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436504</v>
+        <v>436601</v>
       </c>
       <c r="R48" t="n">
-        <v>6786102</v>
+        <v>6785947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5389,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129058385</v>
+        <v>129058395</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5416,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436327</v>
+        <v>436504</v>
       </c>
       <c r="R49" t="n">
-        <v>6786086</v>
+        <v>6786102</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129058268</v>
+        <v>129058385</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5513,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436504</v>
+        <v>436327</v>
       </c>
       <c r="R50" t="n">
-        <v>6786023</v>
+        <v>6786086</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129058386</v>
+        <v>129058268</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5610,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436505</v>
+        <v>436504</v>
       </c>
       <c r="R51" t="n">
-        <v>6785856</v>
+        <v>6786023</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129058290</v>
+        <v>129058386</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,42 +5691,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436601</v>
+        <v>436505</v>
       </c>
       <c r="R52" t="n">
-        <v>6785947</v>
+        <v>6785856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5780,7 +5780,7 @@
         <v>129058309</v>
       </c>
       <c r="B53" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>129058402</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129058392</v>
+        <v>129058396</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6009,19 +6009,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436508</v>
+        <v>436491</v>
       </c>
       <c r="R55" t="n">
-        <v>6786026</v>
+        <v>6786189</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,18 +6053,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6086,10 +6077,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129058391</v>
+        <v>129058392</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6124,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436591</v>
+        <v>436508</v>
       </c>
       <c r="R56" t="n">
-        <v>6785966</v>
+        <v>6786026</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6164,7 +6155,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
+          <t>Garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6192,10 +6183,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129058399</v>
+        <v>129058391</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6230,10 +6221,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436303</v>
+        <v>436591</v>
       </c>
       <c r="R57" t="n">
-        <v>6786193</v>
+        <v>6785966</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6270,7 +6261,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt med Garnlav inom en radie av 40 m</t>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6298,10 +6289,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129058396</v>
+        <v>129058399</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6327,16 +6318,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436491</v>
+        <v>436303</v>
       </c>
       <c r="R58" t="n">
-        <v>6786189</v>
+        <v>6786193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,12 +6365,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>129058279</v>
       </c>
       <c r="B59" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>129058306</v>
       </c>
       <c r="B60" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129058361</v>
+        <v>129058389</v>
       </c>
       <c r="B61" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6608,34 +6608,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436500</v>
+        <v>436739</v>
       </c>
       <c r="R61" t="n">
-        <v>6786018</v>
+        <v>6785902</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6670,12 +6673,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6694,10 +6703,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129058389</v>
+        <v>129058291</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6705,26 +6714,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6732,10 +6746,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436739</v>
+        <v>436214</v>
       </c>
       <c r="R62" t="n">
-        <v>6785902</v>
+        <v>6786222</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6770,18 +6784,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6800,45 +6808,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129058405</v>
+        <v>129058335</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436227</v>
+        <v>436360</v>
       </c>
       <c r="R63" t="n">
-        <v>6786243</v>
+        <v>6786231</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6879,6 +6896,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6897,45 +6915,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129058353</v>
+        <v>129058340</v>
       </c>
       <c r="B64" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436551</v>
+        <v>436324</v>
       </c>
       <c r="R64" t="n">
-        <v>6785765</v>
+        <v>6786220</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6976,6 +7003,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6994,45 +7022,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129058271</v>
+        <v>129058330</v>
       </c>
       <c r="B65" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436493</v>
+        <v>436823</v>
       </c>
       <c r="R65" t="n">
-        <v>6786189</v>
+        <v>6785756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,6 +7110,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7091,40 +7129,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129058291</v>
+        <v>129058323</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7134,10 +7173,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436214</v>
+        <v>436241</v>
       </c>
       <c r="R66" t="n">
-        <v>6786222</v>
+        <v>6786159</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,6 +7217,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7196,54 +7236,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129058335</v>
+        <v>129058361</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>78800</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436360</v>
+        <v>436500</v>
       </c>
       <c r="R67" t="n">
-        <v>6786231</v>
+        <v>6786018</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7284,7 +7315,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7303,54 +7333,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129058340</v>
+        <v>129058405</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436324</v>
+        <v>436227</v>
       </c>
       <c r="R68" t="n">
-        <v>6786220</v>
+        <v>6786243</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7391,7 +7412,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7410,54 +7430,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129058330</v>
+        <v>129058353</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>78800</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436823</v>
+        <v>436551</v>
       </c>
       <c r="R69" t="n">
-        <v>6785756</v>
+        <v>6785765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7509,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7517,54 +7527,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129058323</v>
+        <v>129058271</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436241</v>
+        <v>436493</v>
       </c>
       <c r="R70" t="n">
-        <v>6786159</v>
+        <v>6786189</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7605,7 +7606,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129058267</v>
+        <v>129058305</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7635,34 +7635,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436524</v>
+        <v>436680</v>
       </c>
       <c r="R71" t="n">
-        <v>6785977</v>
+        <v>6785902</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7703,6 +7706,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7721,45 +7725,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129058362</v>
+        <v>129058334</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436494</v>
+        <v>436373</v>
       </c>
       <c r="R72" t="n">
-        <v>6786028</v>
+        <v>6786190</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7800,6 +7813,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7818,10 +7832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129058264</v>
+        <v>129058267</v>
       </c>
       <c r="B73" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7853,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436599</v>
+        <v>436524</v>
       </c>
       <c r="R73" t="n">
-        <v>6785738</v>
+        <v>6785977</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7915,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129058354</v>
+        <v>129058362</v>
       </c>
       <c r="B74" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7950,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436796</v>
+        <v>436494</v>
       </c>
       <c r="R74" t="n">
-        <v>6785778</v>
+        <v>6786028</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8012,10 +8026,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129058359</v>
+        <v>129058264</v>
       </c>
       <c r="B75" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8023,21 +8037,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8047,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436532</v>
+        <v>436599</v>
       </c>
       <c r="R75" t="n">
-        <v>6785994</v>
+        <v>6785738</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8109,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129058367</v>
+        <v>129058354</v>
       </c>
       <c r="B76" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8144,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436371</v>
+        <v>436796</v>
       </c>
       <c r="R76" t="n">
-        <v>6786199</v>
+        <v>6785778</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,54 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129058334</v>
+        <v>129058359</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>78800</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436373</v>
+        <v>436532</v>
       </c>
       <c r="R77" t="n">
-        <v>6786190</v>
+        <v>6785994</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,7 +8299,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8313,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129058305</v>
+        <v>129058367</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,37 +8328,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436680</v>
+        <v>436371</v>
       </c>
       <c r="R78" t="n">
-        <v>6785902</v>
+        <v>6786199</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8395,7 +8396,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8519,10 +8519,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129058355</v>
+        <v>129058315</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>78801</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8530,37 +8530,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436825</v>
+        <v>436445</v>
       </c>
       <c r="R80" t="n">
-        <v>6785764</v>
+        <v>6786210</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8601,7 +8598,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8620,10 +8616,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129058394</v>
+        <v>129058355</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8631,34 +8627,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436493</v>
+        <v>436825</v>
       </c>
       <c r="R81" t="n">
-        <v>6786075</v>
+        <v>6785764</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8699,6 +8698,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8717,10 +8717,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129058356</v>
+        <v>129058394</v>
       </c>
       <c r="B82" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8728,21 +8728,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436818</v>
+        <v>436493</v>
       </c>
       <c r="R82" t="n">
-        <v>6785831</v>
+        <v>6786075</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8814,10 +8814,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129058315</v>
+        <v>129058356</v>
       </c>
       <c r="B83" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436445</v>
+        <v>436818</v>
       </c>
       <c r="R83" t="n">
-        <v>6786210</v>
+        <v>6785831</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129058352</v>
+        <v>129058397</v>
       </c>
       <c r="B84" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8922,34 +8922,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436515</v>
+        <v>436446</v>
       </c>
       <c r="R84" t="n">
-        <v>6785847</v>
+        <v>6786249</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8990,6 +8993,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9008,10 +9012,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129058263</v>
+        <v>129058383</v>
       </c>
       <c r="B85" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9019,21 +9023,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9043,10 +9047,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436559</v>
+        <v>436263</v>
       </c>
       <c r="R85" t="n">
-        <v>6785783</v>
+        <v>6786145</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9105,10 +9109,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129058414</v>
+        <v>129058352</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9116,37 +9120,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436671</v>
+        <v>436515</v>
       </c>
       <c r="R86" t="n">
-        <v>6785810</v>
+        <v>6785847</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9181,18 +9182,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9211,10 +9206,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129058397</v>
+        <v>129058263</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9222,37 +9217,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436446</v>
+        <v>436559</v>
       </c>
       <c r="R87" t="n">
-        <v>6786249</v>
+        <v>6785783</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9293,7 +9285,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9312,10 +9303,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129058383</v>
+        <v>129058414</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9341,16 +9332,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436263</v>
+        <v>436671</v>
       </c>
       <c r="R88" t="n">
-        <v>6786145</v>
+        <v>6785810</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9385,12 +9379,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>129058302</v>
       </c>
       <c r="B89" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129058411</v>
+        <v>129058314</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436461</v>
+        <v>436510</v>
       </c>
       <c r="R91" t="n">
-        <v>6785881</v>
+        <v>6786074</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9700,10 +9700,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129058398</v>
+        <v>129058411</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436425</v>
+        <v>436461</v>
       </c>
       <c r="R92" t="n">
-        <v>6786210</v>
+        <v>6785881</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9797,10 +9797,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129058387</v>
+        <v>129058398</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436805</v>
+        <v>436425</v>
       </c>
       <c r="R93" t="n">
-        <v>6785785</v>
+        <v>6786210</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129058314</v>
+        <v>129058387</v>
       </c>
       <c r="B94" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9905,21 +9905,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436510</v>
+        <v>436805</v>
       </c>
       <c r="R94" t="n">
-        <v>6786074</v>
+        <v>6785785</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9994,7 +9994,7 @@
         <v>129058407</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>129058416</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>129058298</v>
       </c>
       <c r="B99" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>129058300</v>
       </c>
       <c r="B100" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>129058417</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>129058364</v>
       </c>
       <c r="B102" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>129058401</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>129058390</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>129058266</v>
       </c>
       <c r="B105" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>129058406</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>129058366</v>
       </c>
       <c r="B107" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>129058393</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>129058358</v>
       </c>
       <c r="B109" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129058289</v>
+        <v>129058368</v>
       </c>
       <c r="B111" t="n">
-        <v>57724</v>
+        <v>78800</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11593,42 +11593,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436486</v>
+        <v>436257</v>
       </c>
       <c r="R111" t="n">
-        <v>6786231</v>
+        <v>6786288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11794,10 +11786,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129058368</v>
+        <v>129058289</v>
       </c>
       <c r="B113" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11805,34 +11797,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gudfarstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436257</v>
+        <v>436486</v>
       </c>
       <c r="R113" t="n">
-        <v>6786288</v>
+        <v>6786231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11894,7 +11894,7 @@
         <v>129058270</v>
       </c>
       <c r="B114" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>129058388</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129080278</v>
+        <v>129080329</v>
       </c>
       <c r="B116" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12105,21 +12105,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436513</v>
+        <v>436247</v>
       </c>
       <c r="R116" t="n">
-        <v>6785962</v>
+        <v>6786289</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,6 +12165,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12191,10 +12196,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129080329</v>
+        <v>129080292</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12202,21 +12207,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12226,10 +12231,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436247</v>
+        <v>436532</v>
       </c>
       <c r="R117" t="n">
-        <v>6786289</v>
+        <v>6785865</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,11 +12267,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12293,10 +12293,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129080323</v>
+        <v>129080278</v>
       </c>
       <c r="B118" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12304,21 +12304,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12328,10 +12328,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436382</v>
+        <v>436513</v>
       </c>
       <c r="R118" t="n">
-        <v>6786202</v>
+        <v>6785962</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12390,10 +12390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129080292</v>
+        <v>129080323</v>
       </c>
       <c r="B119" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12401,21 +12401,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436532</v>
+        <v>436382</v>
       </c>
       <c r="R119" t="n">
-        <v>6785865</v>
+        <v>6786202</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12487,10 +12487,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129080302</v>
+        <v>129080277</v>
       </c>
       <c r="B120" t="n">
-        <v>91561</v>
+        <v>79662</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12498,21 +12498,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436320</v>
+        <v>436561</v>
       </c>
       <c r="R120" t="n">
-        <v>6786132</v>
+        <v>6785959</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,7 +12566,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12585,10 +12584,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129080277</v>
+        <v>129080302</v>
       </c>
       <c r="B121" t="n">
-        <v>79660</v>
+        <v>91564</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12596,21 +12595,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12620,10 +12619,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436561</v>
+        <v>436320</v>
       </c>
       <c r="R121" t="n">
-        <v>6785959</v>
+        <v>6786132</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12664,6 +12663,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12685,7 +12685,7 @@
         <v>129080295</v>
       </c>
       <c r="B122" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>129080291</v>
       </c>
       <c r="B123" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>129080294</v>
       </c>
       <c r="B124" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>129080322</v>
       </c>
       <c r="B125" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>129080289</v>
       </c>
       <c r="B126" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>129080281</v>
       </c>
       <c r="B127" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>129080328</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>129080298</v>
       </c>
       <c r="B129" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>129080290</v>
       </c>
       <c r="B130" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13555,10 +13555,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129080313</v>
+        <v>129080296</v>
       </c>
       <c r="B131" t="n">
-        <v>78798</v>
+        <v>78801</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436211</v>
+        <v>436612</v>
       </c>
       <c r="R131" t="n">
-        <v>6786206</v>
+        <v>6785878</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13652,10 +13652,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129080296</v>
+        <v>129080313</v>
       </c>
       <c r="B132" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13663,21 +13663,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436612</v>
+        <v>436211</v>
       </c>
       <c r="R132" t="n">
-        <v>6785878</v>
+        <v>6786206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13752,7 +13752,7 @@
         <v>129080318</v>
       </c>
       <c r="B133" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>129080279</v>
       </c>
       <c r="B134" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>129080301</v>
       </c>
       <c r="B135" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14040,10 +14040,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129080284</v>
+        <v>129080317</v>
       </c>
       <c r="B136" t="n">
-        <v>91561</v>
+        <v>78800</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14051,21 +14051,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>436494</v>
+        <v>436816</v>
       </c>
       <c r="R136" t="n">
-        <v>6785930</v>
+        <v>6785768</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14137,10 +14137,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129080317</v>
+        <v>129080316</v>
       </c>
       <c r="B137" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14172,10 +14172,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>436816</v>
+        <v>436532</v>
       </c>
       <c r="R137" t="n">
-        <v>6785768</v>
+        <v>6785867</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14234,10 +14234,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129080316</v>
+        <v>129080284</v>
       </c>
       <c r="B138" t="n">
-        <v>78798</v>
+        <v>91564</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14269,10 +14269,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>436532</v>
+        <v>436494</v>
       </c>
       <c r="R138" t="n">
-        <v>6785867</v>
+        <v>6785930</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14334,7 +14334,7 @@
         <v>129080314</v>
       </c>
       <c r="B139" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>129080293</v>
       </c>
       <c r="B140" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>129080319</v>
       </c>
       <c r="B141" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>129080324</v>
       </c>
       <c r="B142" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>129080327</v>
       </c>
       <c r="B143" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>129080300</v>
       </c>
       <c r="B145" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>129080299</v>
       </c>
       <c r="B146" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>129080315</v>
       </c>
       <c r="B147" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>129080280</v>
       </c>
       <c r="B148" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15311,10 +15311,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129080283</v>
+        <v>129080282</v>
       </c>
       <c r="B149" t="n">
-        <v>91540</v>
+        <v>79662</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15322,21 +15322,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>436434</v>
+        <v>436335</v>
       </c>
       <c r="R149" t="n">
-        <v>6786112</v>
+        <v>6786163</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15384,18 +15384,12 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Växer på granlåga som har barken kvar</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15414,10 +15408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129080331</v>
+        <v>129080297</v>
       </c>
       <c r="B150" t="n">
-        <v>88940</v>
+        <v>78801</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15425,21 +15419,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>510</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15449,10 +15443,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>436491</v>
+        <v>436449</v>
       </c>
       <c r="R150" t="n">
-        <v>6786094</v>
+        <v>6786210</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15493,7 +15487,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15512,10 +15505,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129080282</v>
+        <v>129080283</v>
       </c>
       <c r="B151" t="n">
-        <v>79660</v>
+        <v>91543</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15523,21 +15516,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15547,10 +15540,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>436335</v>
+        <v>436434</v>
       </c>
       <c r="R151" t="n">
-        <v>6786163</v>
+        <v>6786112</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15585,12 +15578,18 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Växer på granlåga som har barken kvar</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15609,10 +15608,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129080297</v>
+        <v>129080331</v>
       </c>
       <c r="B152" t="n">
-        <v>78799</v>
+        <v>88943</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15620,21 +15619,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15644,10 +15643,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>436449</v>
+        <v>436491</v>
       </c>
       <c r="R152" t="n">
-        <v>6786210</v>
+        <v>6786094</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15688,6 +15687,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>129080320</v>
       </c>
       <c r="B153" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 49247-2025 artfynd.xlsx
+++ b/artfynd/A 49247-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY171"/>
+  <dimension ref="A1:AZ171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058383</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058384</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058399</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058401</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058402</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058403</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058406</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058407</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058348</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,6 +2123,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058368</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080313</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080324</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058273</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058278</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058291</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2657,6 +2757,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058323</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2764,6 +2869,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058324</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058341</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2978,6 +3093,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058343</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3085,6 +3205,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058345</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3192,6 +3317,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080312</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3289,6 +3419,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058322</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3386,6 +3521,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080289</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3483,6 +3623,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080301</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3581,6 +3726,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080331</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3684,6 +3834,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080283</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3781,6 +3936,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080284</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3879,6 +4039,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080302</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3976,6 +4141,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058385</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4073,6 +4243,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058386</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4170,6 +4345,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058387</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4276,6 +4456,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058388</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4382,6 +4567,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058389</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4479,6 +4669,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058390</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4585,6 +4780,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058391</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4691,6 +4891,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058392</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4788,6 +4993,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058393</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4885,6 +5095,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058394</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4982,6 +5197,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058395</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5079,6 +5299,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058396</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5180,6 +5405,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058397</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5277,6 +5507,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058398</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5374,6 +5609,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058411</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5471,6 +5711,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058412</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5577,6 +5822,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058414</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5683,6 +5933,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058415</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5789,6 +6044,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058416</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5886,6 +6146,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058417</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5983,6 +6248,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080327</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6080,6 +6350,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080328</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6177,6 +6452,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058349</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6274,6 +6554,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058350</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6371,6 +6656,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058351</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6468,6 +6758,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058352</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6565,6 +6860,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058353</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6662,6 +6962,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058354</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6763,6 +7068,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058355</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6860,6 +7170,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058356</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6957,6 +7272,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058357</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7054,6 +7374,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058358</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7151,6 +7476,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058359</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7248,6 +7578,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058361</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7345,6 +7680,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058362</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7442,6 +7782,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058364</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7539,6 +7884,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058365</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7636,6 +7986,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058366</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7733,6 +8088,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058367</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7830,6 +8190,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058369</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7927,6 +8292,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080314</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8024,6 +8394,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080315</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8121,6 +8496,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080316</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8218,6 +8598,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080317</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8315,6 +8700,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080318</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8412,6 +8802,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080319</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8509,6 +8904,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080320</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8606,6 +9006,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080322</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8703,6 +9108,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080323</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8800,6 +9210,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058261</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8897,6 +9312,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058262</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8994,6 +9414,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058263</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9091,6 +9516,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058264</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9188,6 +9618,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058266</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9285,6 +9720,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058267</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9382,6 +9822,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058268</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9479,6 +9924,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058269</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9576,6 +10026,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058270</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9673,6 +10128,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058271</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9774,6 +10234,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058272</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9871,6 +10336,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058274</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9968,6 +10438,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058276</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10069,6 +10544,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058277</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10166,6 +10646,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080277</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10263,6 +10748,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080278</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10360,6 +10850,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080279</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10457,6 +10952,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080280</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10554,6 +11054,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080281</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10651,6 +11156,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080282</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10756,6 +11266,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058285</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10861,6 +11376,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058286</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10966,6 +11486,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058287</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11071,6 +11596,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058288</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11176,6 +11706,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058289</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11281,6 +11816,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058290</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11386,6 +11926,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080285</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11491,6 +12036,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080286</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11596,6 +12146,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080287</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11701,6 +12256,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080288</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11806,6 +12366,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058282</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11903,6 +12468,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058346</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12010,6 +12580,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058325</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12117,6 +12692,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058327</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12224,6 +12804,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058328</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12331,6 +12916,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058329</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12438,6 +13028,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058330</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12545,6 +13140,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058331</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12652,6 +13252,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058332</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12759,6 +13364,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058333</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12866,6 +13476,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058334</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12973,6 +13588,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058335</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13080,6 +13700,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058336</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13187,6 +13812,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058337</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13294,6 +13924,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058340</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13401,6 +14036,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080303</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13508,6 +14148,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080304</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13615,6 +14260,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080305</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13722,6 +14372,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080306</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13829,6 +14484,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080307</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13936,6 +14596,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080308</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14043,6 +14708,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080309</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14150,6 +14820,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080310</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14257,6 +14932,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080311</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14354,6 +15034,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058294</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14451,6 +15136,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058297</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14548,6 +15238,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058298</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14645,6 +15340,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058299</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14742,6 +15442,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058300</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14839,6 +15544,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058301</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14936,6 +15646,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058302</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15033,6 +15748,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058303</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15130,6 +15850,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058304</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15231,6 +15956,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058305</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15332,6 +16062,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058306</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15429,6 +16164,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058307</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15526,6 +16266,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058308</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15623,6 +16368,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058309</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15720,6 +16470,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058311</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15817,6 +16572,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058313</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15914,6 +16674,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058314</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16011,6 +16776,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058315</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16112,6 +16882,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058317</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16213,6 +16988,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058318</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16314,6 +17094,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058319</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16411,6 +17196,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058321</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16508,6 +17298,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080290</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16605,6 +17400,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080291</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16702,6 +17502,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080292</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16799,6 +17604,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080293</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16896,6 +17706,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080294</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16993,6 +17808,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080295</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17090,6 +17910,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080296</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17187,6 +18012,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080297</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17284,6 +18114,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080298</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17381,6 +18216,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080299</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17478,6 +18318,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080300</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17579,6 +18424,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058279</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17676,8 +18526,185 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129058280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>